--- a/NetLabz_Project_Checklist.xlsx
+++ b/NetLabz_Project_Checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NetLabz_Enterprise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3177AD8-8A2A-452F-85A3-501AEB8EAB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FE6765-2FFE-44C5-A5DE-8E720BA083D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-86" yWindow="0" windowWidth="14915" windowHeight="11709" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="933">
   <si>
     <t>Overall Progress</t>
   </si>
@@ -2833,6 +2833,9 @@
   </si>
   <si>
     <t>NetLabz Enterprise  — Project Tracker</t>
+  </si>
+  <si>
+    <t>Used AI to list file types that are common with VM's so as not to miss any, creating vulnerability.</t>
   </si>
 </sst>
 </file>
@@ -3658,7 +3661,7 @@
       </c>
       <c r="B4" s="4">
         <f>IF(B5=0,0,B6/B5)</f>
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -3688,7 +3691,7 @@
       </c>
       <c r="B6" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -3733,7 +3736,7 @@
       </c>
       <c r="B9" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Not Started")</f>
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -3784,7 +3787,7 @@
       </c>
       <c r="E13">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A13,'Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F13">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A13,'Project Checklist'!$G$5:$G$220,"In Progress")</f>
@@ -3796,7 +3799,7 @@
       </c>
       <c r="H13" s="3">
         <f t="shared" ref="H13:H33" si="0">IF(D13=0,0,E13/D13)</f>
-        <v>0</v>
+        <v>0.6428571428571429</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4586,7 +4589,7 @@
         <v>53</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>54</v>
@@ -4613,7 +4616,7 @@
         <v>57</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>54</v>
@@ -4640,7 +4643,7 @@
         <v>61</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" s="17" t="s">
         <v>54</v>
@@ -4667,7 +4670,7 @@
         <v>64</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" s="17" t="s">
         <v>54</v>
@@ -4694,7 +4697,7 @@
         <v>68</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>69</v>
@@ -4721,7 +4724,7 @@
         <v>73</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -4748,7 +4751,7 @@
         <v>76</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>54</v>
@@ -4775,14 +4778,14 @@
         <v>79</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>54</v>
       </c>
       <c r="I12" s="18"/>
     </row>
-    <row r="13" spans="1:9" ht="28.3">
+    <row r="13" spans="1:9" ht="42.45">
       <c r="A13" s="15" t="s">
         <v>80</v>
       </c>
@@ -4802,12 +4805,14 @@
         <v>83</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="18"/>
+      <c r="I13" s="18" t="s">
+        <v>932</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="28.3">
       <c r="A14" s="15" t="s">
@@ -11391,6 +11396,7 @@
     <mergeCell ref="A1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/NetLabz_Project_Checklist.xlsx
+++ b/NetLabz_Project_Checklist.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NetLabz_Enterprise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FE6765-2FFE-44C5-A5DE-8E720BA083D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E31B397-A22C-4E88-870D-36F7719DAE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-86" yWindow="0" windowWidth="14915" windowHeight="11709" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
     <sheet name="Project Checklist" sheetId="2" r:id="rId2"/>
     <sheet name="Phase Guide" sheetId="3" r:id="rId3"/>
-    <sheet name="Standards" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="853">
   <si>
     <t>Overall Progress</t>
   </si>
@@ -2484,156 +2483,15 @@
     <t>Ten structured incidents plus one multi-fault capstone are completed; final architecture and recruiter-ready README are published.</t>
   </si>
   <si>
-    <t>Lab Standards &amp; Reference</t>
-  </si>
-  <si>
-    <t>Current Hardware</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Upgrade Trigger</t>
-  </si>
-  <si>
-    <t>Object Type</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>Examples</t>
-  </si>
-  <si>
-    <t>Dell OptiPlex 3060 SFF</t>
-  </si>
-  <si>
-    <t>Keep as primary Hyper-V lab host</t>
-  </si>
-  <si>
-    <t>Hyper-V Host</t>
-  </si>
-  <si>
-    <t>HYPV##</t>
-  </si>
-  <si>
-    <t>HYPV01</t>
-  </si>
-  <si>
-    <t>CPU</t>
-  </si>
-  <si>
-    <t>Intel Core i5-8500</t>
-  </si>
-  <si>
-    <t>Upgrade only if future workload proves CPU-bound</t>
-  </si>
-  <si>
-    <t>Firewall/Router</t>
-  </si>
-  <si>
-    <t>FW##</t>
-  </si>
-  <si>
-    <t>FW01</t>
-  </si>
-  <si>
-    <t>RAM</t>
-  </si>
-  <si>
-    <t>16 GB</t>
-  </si>
-  <si>
-    <t>First recommended upgrade: 32 GB if concurrent VMs become restrictive</t>
-  </si>
-  <si>
-    <t>Domain Controller</t>
-  </si>
-  <si>
-    <t>DC##</t>
-  </si>
-  <si>
-    <t>DC01, DC02</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>1 TB</t>
-  </si>
-  <si>
-    <t>Expand only if VM disks/backups consume available space</t>
-  </si>
-  <si>
-    <t>ROLE##</t>
-  </si>
-  <si>
-    <t>FILE01, APP01</t>
-  </si>
-  <si>
-    <t>Physical NICs</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Add second NIC when physical VLAN/trunk experiments justify it</t>
-  </si>
-  <si>
-    <t>Windows Client</t>
-  </si>
-  <si>
-    <t>CLIENT##</t>
-  </si>
-  <si>
-    <t>CLIENT01</t>
-  </si>
-  <si>
-    <t>Network gear</t>
-  </si>
-  <si>
-    <t>ISP router + Nighthawk MR70</t>
-  </si>
-  <si>
-    <t>Buy managed switch when Phase 10 makes physical VLAN practice worthwhile</t>
-  </si>
-  <si>
-    <t>LINUX##</t>
-  </si>
-  <si>
-    <t>LINUX01</t>
-  </si>
-  <si>
-    <t>Docker Host</t>
-  </si>
-  <si>
-    <t>DOCKER##</t>
-  </si>
-  <si>
-    <t>DOCKER01</t>
-  </si>
-  <si>
     <t>Management</t>
   </si>
   <si>
-    <t>MGMT##</t>
-  </si>
-  <si>
-    <t>MGMT01</t>
-  </si>
-  <si>
     <t>Subnet</t>
   </si>
   <si>
     <t>Gateway</t>
   </si>
   <si>
-    <t>MON##</t>
-  </si>
-  <si>
-    <t>MON01</t>
-  </si>
-  <si>
     <t>Server</t>
   </si>
   <si>
@@ -2643,12 +2501,6 @@
     <t>10.10.10.1</t>
   </si>
   <si>
-    <t>SEC##</t>
-  </si>
-  <si>
-    <t>SEC01</t>
-  </si>
-  <si>
     <t>Client</t>
   </si>
   <si>
@@ -2658,15 +2510,6 @@
     <t>10.10.20.1</t>
   </si>
   <si>
-    <t>Hyper-V Switch</t>
-  </si>
-  <si>
-    <t>vSW-ROLE</t>
-  </si>
-  <si>
-    <t>vSW-EXT, vSW-SERVER, vSW-CLIENT, vSW-DMZ, vSW-MGMT</t>
-  </si>
-  <si>
     <t>DMZ</t>
   </si>
   <si>
@@ -2676,136 +2519,52 @@
     <t>10.10.30.1</t>
   </si>
   <si>
-    <t>Public-facing/test services</t>
-  </si>
-  <si>
     <t>10.10.40.0/24</t>
   </si>
   <si>
     <t>10.10.40.1</t>
   </si>
   <si>
-    <t>Administrative traffic</t>
-  </si>
-  <si>
     <t>10.10.50.0/24</t>
   </si>
   <si>
     <t>10.10.50.1</t>
   </si>
   <si>
-    <t>Project Rule</t>
-  </si>
-  <si>
-    <t>Why It Matters</t>
-  </si>
-  <si>
-    <t>Evidence</t>
-  </si>
-  <si>
     <t>10.10.60.0/24</t>
   </si>
   <si>
     <t>10.10.60.1</t>
   </si>
   <si>
-    <t>Observe → Record → Hypothesize → Test → Change → Validate</t>
-  </si>
-  <si>
-    <t>Prevents blind troubleshooting and creates interview-ready stories.</t>
-  </si>
-  <si>
-    <t>Incident notes and test results</t>
-  </si>
-  <si>
     <t>10.10.70.0/24</t>
   </si>
   <si>
     <t>10.10.70.1</t>
   </si>
   <si>
-    <t>Do not commit secrets, private keys, tokens, or real sensitive data.</t>
-  </si>
-  <si>
-    <t>Public GitHub must stay safe.</t>
-  </si>
-  <si>
-    <t>.gitignore + repo review</t>
-  </si>
-  <si>
-    <t>Use checkpoints for experiments, but do not treat checkpoints as backups.</t>
-  </si>
-  <si>
-    <t>Snapshots are convenient; recovery requires a real backup plan.</t>
-  </si>
-  <si>
-    <t>Keep resource usage conservative on 16 GB RAM.</t>
-  </si>
-  <si>
-    <t>Allows a useful lab without unnecessary hardware purchases.</t>
-  </si>
-  <si>
-    <t>VM sizing notes</t>
-  </si>
-  <si>
     <t>Address Range</t>
   </si>
   <si>
     <t>Use</t>
   </si>
   <si>
-    <t>Power on only the VMs needed for the current experiment.</t>
-  </si>
-  <si>
-    <t>Reduces host pressure and mirrors capacity planning.</t>
-  </si>
-  <si>
-    <t>Lab runbooks</t>
-  </si>
-  <si>
     <t>.1</t>
   </si>
   <si>
     <t>Default gateway</t>
   </si>
   <si>
-    <t>Every phase gets at least one meaningful Git commit.</t>
-  </si>
-  <si>
-    <t>Shows progression and version-control habits.</t>
-  </si>
-  <si>
-    <t>Git history</t>
-  </si>
-  <si>
     <t>.2-.9</t>
   </si>
   <si>
     <t>Network infrastructure</t>
   </si>
   <si>
-    <t>Every failure should produce a root cause and validation step.</t>
-  </si>
-  <si>
-    <t>Troubleshooting is more valuable than perfect screenshots.</t>
-  </si>
-  <si>
-    <t>incidents/</t>
-  </si>
-  <si>
     <t>.10-.29</t>
   </si>
   <si>
     <t>Servers</t>
-  </si>
-  <si>
-    <t>Sanitize screenshots/configs before publishing.</t>
-  </si>
-  <si>
-    <t>Protects home network and account information.</t>
-  </si>
-  <si>
-    <t>Final repo review</t>
   </si>
   <si>
     <t>.30-.49</t>
@@ -3065,12 +2824,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3107,11 +2860,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF666666"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3159,9 +2961,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3317,47 +3116,7 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF666666"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF7F6000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF375623"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3373,17 +3132,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectChecklistTable" displayName="ProjectChecklistTable" ref="A4:I220" totalsRowShown="0" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectChecklistTable" displayName="ProjectChecklistTable" ref="A4:I220" totalsRowShown="0" dataDxfId="15">
+  <autoFilter ref="A4:I220" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="Not Started"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phase #" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Phase" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Category" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Task" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Deliverable / Evidence" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Priority" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Notes" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phase #" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Phase" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Category" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Task" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Deliverable / Evidence" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Priority" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Notes" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3404,7 +3170,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0DFA51D1-C4E7-4297-A332-2A07FE6908A6}" name="Table3" displayName="Table3" ref="A1:C8" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0DFA51D1-C4E7-4297-A332-2A07FE6908A6}" name="Table3" displayName="Table3" ref="A1:C8" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:C8" xr:uid="{0DFA51D1-C4E7-4297-A332-2A07FE6908A6}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{84782901-9C62-43D0-9F45-B6BDD25C78B2}" name="Network"/>
@@ -3416,7 +3182,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A49B7CAB-322A-4674-B078-48D9A820176E}" name="Table4" displayName="Table4" ref="A11:B18" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A49B7CAB-322A-4674-B078-48D9A820176E}" name="Table4" displayName="Table4" ref="A11:B18" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A11:B18" xr:uid="{A49B7CAB-322A-4674-B078-48D9A820176E}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{E986A977-7F13-4F5C-AB41-2E2F4CECF81A}" name="Address Range"/>
@@ -3634,26 +3400,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.75" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>931</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="A1" s="21" t="s">
+        <v>851</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="13.75" customHeight="1">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="4" spans="1:8" ht="15.45">
       <c r="A4" s="2" t="s">
@@ -3661,7 +3427,7 @@
       </c>
       <c r="B4" s="4">
         <f>IF(B5=0,0,B6/B5)</f>
-        <v>4.1666666666666664E-2</v>
+        <v>6.9444444444444448E-2</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -3691,7 +3457,7 @@
       </c>
       <c r="B6" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -3736,7 +3502,7 @@
       </c>
       <c r="B9" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Not Started")</f>
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -3787,7 +3553,7 @@
       </c>
       <c r="E13">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A13,'Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F13">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A13,'Project Checklist'!$G$5:$G$220,"In Progress")</f>
@@ -3799,7 +3565,7 @@
       </c>
       <c r="H13" s="3">
         <f t="shared" ref="H13:H33" si="0">IF(D13=0,0,E13/D13)</f>
-        <v>0.6428571428571429</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3818,7 +3584,7 @@
       </c>
       <c r="E14">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A14,'Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A14,'Project Checklist'!$G$5:$G$220,"In Progress")</f>
@@ -3830,7 +3596,7 @@
       </c>
       <c r="H14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4517,30 +4283,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-    </row>
-    <row r="4" spans="1:9" ht="28.75" thickBot="1">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+    </row>
+    <row r="4" spans="1:9" ht="28.3">
       <c r="A4" s="6" t="s">
         <v>44</v>
       </c>
@@ -4569,5855 +4335,5855 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="28.3">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:9" ht="28.3" hidden="1">
+      <c r="A5" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>0</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" spans="1:9" ht="28.3">
-      <c r="A6" s="15" t="s">
+      <c r="H5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="12"/>
+    </row>
+    <row r="6" spans="1:9" ht="28.3" hidden="1">
+      <c r="A6" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="14">
         <v>0</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="18"/>
-    </row>
-    <row r="7" spans="1:9" ht="28.3">
-      <c r="A7" s="15" t="s">
+      <c r="H6" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="16"/>
+    </row>
+    <row r="7" spans="1:9" ht="28.3" hidden="1">
+      <c r="A7" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="14">
         <v>0</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="18"/>
-    </row>
-    <row r="8" spans="1:9" ht="28.3">
-      <c r="A8" s="15" t="s">
+      <c r="H7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="16"/>
+    </row>
+    <row r="8" spans="1:9" ht="28.3" hidden="1">
+      <c r="A8" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="14">
         <v>0</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="18"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="15" t="s">
+      <c r="H8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="1:9" hidden="1">
+      <c r="A9" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="14">
         <v>0</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="18"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="15" t="s">
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" spans="1:9" hidden="1">
+      <c r="A10" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="14">
         <v>0</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I10" s="18"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="15" t="s">
+      <c r="H10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="16"/>
+    </row>
+    <row r="11" spans="1:9" hidden="1">
+      <c r="A11" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="14">
         <v>0</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="17" t="s">
+      <c r="G11" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="18"/>
-    </row>
-    <row r="12" spans="1:9" ht="28.3">
-      <c r="A12" s="15" t="s">
+      <c r="H11" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" spans="1:9" ht="28.3" hidden="1">
+      <c r="A12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="14">
         <v>0</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" s="18"/>
-    </row>
-    <row r="13" spans="1:9" ht="42.45">
-      <c r="A13" s="15" t="s">
+      <c r="H12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" spans="1:9" ht="42.45" hidden="1">
+      <c r="A13" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="14">
         <v>0</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="28.3">
-      <c r="A14" s="15" t="s">
+      <c r="H13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="28.3" hidden="1">
+      <c r="A14" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="14">
         <v>0</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="18"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="15" t="s">
+      <c r="G14" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" spans="1:9" hidden="1">
+      <c r="A15" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="14">
         <v>0</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I15" s="18"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="15" t="s">
+      <c r="G15" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" spans="1:9" hidden="1">
+      <c r="A16" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="14">
         <v>0</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="G16" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I16" s="18"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="15" t="s">
+      <c r="G16" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I16" s="16"/>
+    </row>
+    <row r="17" spans="1:9" hidden="1">
+      <c r="A17" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="14">
         <v>0</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I17" s="18"/>
-    </row>
-    <row r="18" spans="1:9" ht="28.3">
-      <c r="A18" s="15" t="s">
+      <c r="G17" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="16"/>
+    </row>
+    <row r="18" spans="1:9" ht="28.3" hidden="1">
+      <c r="A18" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="14">
         <v>0</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="G18" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="17" t="s">
+      <c r="G18" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="18"/>
-    </row>
-    <row r="19" spans="1:9" ht="28.3">
-      <c r="A19" s="15" t="s">
+      <c r="I18" s="16"/>
+    </row>
+    <row r="19" spans="1:9" ht="28.3" hidden="1">
+      <c r="A19" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="14">
         <v>1</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="G19" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I19" s="18"/>
+      <c r="G19" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="16"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="14">
         <v>1</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="18"/>
+      <c r="G20" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" s="16"/>
     </row>
     <row r="21" spans="1:9" ht="28.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="14">
         <v>1</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="G21" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I21" s="18"/>
+      <c r="G21" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="16"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="14">
         <v>1</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="G22" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I22" s="18"/>
+      <c r="G22" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I22" s="16"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="14">
         <v>1</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="G23" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="18"/>
+      <c r="G23" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" s="16"/>
     </row>
     <row r="24" spans="1:9" ht="28.3">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="14">
         <v>1</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="17" t="s">
+      <c r="G24" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="18"/>
+      <c r="I24" s="16"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="14">
         <v>1</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="G25" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="17" t="s">
+      <c r="G25" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I25" s="18"/>
+      <c r="I25" s="16"/>
     </row>
     <row r="26" spans="1:9" ht="28.3">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="14">
         <v>1</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G26" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="17" t="s">
+      <c r="G26" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I26" s="18"/>
+      <c r="I26" s="16"/>
     </row>
     <row r="27" spans="1:9" ht="28.3">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="14">
         <v>1</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="G27" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I27" s="18"/>
+      <c r="G27" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I27" s="16"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="14">
         <v>2</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="G28" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" s="18"/>
+      <c r="G28" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" s="16"/>
     </row>
     <row r="29" spans="1:9" ht="28.3">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="14">
         <v>2</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="G29" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I29" s="18"/>
+      <c r="G29" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I29" s="16"/>
     </row>
     <row r="30" spans="1:9" ht="28.3">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="14">
         <v>2</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="G30" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I30" s="18"/>
+      <c r="G30" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I30" s="16"/>
     </row>
     <row r="31" spans="1:9" ht="28.3">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="14">
         <v>2</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="G31" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I31" s="18"/>
+      <c r="G31" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I31" s="16"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="14">
         <v>2</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="G32" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I32" s="18"/>
+      <c r="G32" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I32" s="16"/>
     </row>
     <row r="33" spans="1:9" ht="28.3">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="14">
         <v>2</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="G33" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I33" s="18"/>
+      <c r="G33" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I33" s="16"/>
     </row>
     <row r="34" spans="1:9" ht="28.3">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="14">
         <v>2</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="G34" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I34" s="18"/>
+      <c r="G34" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I34" s="16"/>
     </row>
     <row r="35" spans="1:9" ht="28.3">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="14">
         <v>2</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="G35" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I35" s="18"/>
+      <c r="G35" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I35" s="16"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="14">
         <v>2</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="G36" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H36" s="17" t="s">
+      <c r="G36" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H36" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="18"/>
+      <c r="I36" s="16"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="14">
         <v>2</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G37" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I37" s="18"/>
+      <c r="G37" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I37" s="16"/>
     </row>
     <row r="38" spans="1:9" ht="28.3">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="14">
         <v>3</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="G38" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H38" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I38" s="18"/>
+      <c r="G38" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I38" s="16"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="14">
         <v>3</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="G39" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I39" s="18"/>
+      <c r="G39" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I39" s="16"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="14">
         <v>3</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="G40" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H40" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I40" s="18"/>
+      <c r="G40" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I40" s="16"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="14">
         <v>3</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="G41" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="17" t="s">
+      <c r="G41" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="18"/>
+      <c r="I41" s="16"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="14">
         <v>3</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="G42" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H42" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I42" s="18"/>
+      <c r="G42" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I42" s="16"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="14">
         <v>3</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="G43" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I43" s="18"/>
+      <c r="G43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I43" s="16"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="14">
         <v>3</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F44" s="17" t="s">
+      <c r="F44" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="G44" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H44" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I44" s="18"/>
+      <c r="G44" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I44" s="16"/>
     </row>
     <row r="45" spans="1:9" ht="28.3">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="14">
         <v>3</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="F45" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="G45" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I45" s="18"/>
+      <c r="G45" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I45" s="16"/>
     </row>
     <row r="46" spans="1:9" ht="28.3">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="14">
         <v>3</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="F46" s="17" t="s">
+      <c r="F46" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="G46" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H46" s="17" t="s">
+      <c r="G46" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I46" s="18"/>
+      <c r="I46" s="16"/>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="14">
         <v>3</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="G47" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H47" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I47" s="18"/>
+      <c r="G47" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I47" s="16"/>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="B48" s="16">
-        <v>4</v>
-      </c>
-      <c r="C48" s="17" t="s">
+      <c r="B48" s="14">
+        <v>4</v>
+      </c>
+      <c r="C48" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="F48" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="G48" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I48" s="18"/>
+      <c r="G48" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I48" s="16"/>
     </row>
     <row r="49" spans="1:9" ht="28.3">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B49" s="16">
-        <v>4</v>
-      </c>
-      <c r="C49" s="17" t="s">
+      <c r="B49" s="14">
+        <v>4</v>
+      </c>
+      <c r="C49" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="F49" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="G49" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H49" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I49" s="18"/>
+      <c r="G49" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I49" s="16"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B50" s="16">
-        <v>4</v>
-      </c>
-      <c r="C50" s="17" t="s">
+      <c r="B50" s="14">
+        <v>4</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D50" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="F50" s="17" t="s">
+      <c r="F50" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="G50" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H50" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I50" s="18"/>
+      <c r="G50" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H50" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I50" s="16"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="15" t="s">
+      <c r="A51" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="B51" s="16">
-        <v>4</v>
-      </c>
-      <c r="C51" s="17" t="s">
+      <c r="B51" s="14">
+        <v>4</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="F51" s="17" t="s">
+      <c r="F51" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="G51" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H51" s="17" t="s">
+      <c r="G51" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H51" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I51" s="18"/>
+      <c r="I51" s="16"/>
     </row>
     <row r="52" spans="1:9" ht="28.3">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="B52" s="16">
-        <v>4</v>
-      </c>
-      <c r="C52" s="17" t="s">
+      <c r="B52" s="14">
+        <v>4</v>
+      </c>
+      <c r="C52" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="F52" s="17" t="s">
+      <c r="F52" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="G52" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="17" t="s">
+      <c r="G52" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I52" s="18"/>
+      <c r="I52" s="16"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="B53" s="16">
-        <v>4</v>
-      </c>
-      <c r="C53" s="17" t="s">
+      <c r="B53" s="14">
+        <v>4</v>
+      </c>
+      <c r="C53" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="F53" s="17" t="s">
+      <c r="F53" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="G53" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H53" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I53" s="18"/>
+      <c r="G53" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H53" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I53" s="16"/>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="B54" s="16">
-        <v>4</v>
-      </c>
-      <c r="C54" s="17" t="s">
+      <c r="B54" s="14">
+        <v>4</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D54" s="17" t="s">
+      <c r="D54" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="F54" s="17" t="s">
+      <c r="F54" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="G54" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="17" t="s">
+      <c r="G54" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I54" s="18"/>
+      <c r="I54" s="16"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B55" s="16">
-        <v>4</v>
-      </c>
-      <c r="C55" s="17" t="s">
+      <c r="B55" s="14">
+        <v>4</v>
+      </c>
+      <c r="C55" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="F55" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="G55" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H55" s="17" t="s">
+      <c r="G55" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H55" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I55" s="18"/>
+      <c r="I55" s="16"/>
     </row>
     <row r="56" spans="1:9" ht="28.3">
-      <c r="A56" s="15" t="s">
+      <c r="A56" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="B56" s="16">
-        <v>4</v>
-      </c>
-      <c r="C56" s="17" t="s">
+      <c r="B56" s="14">
+        <v>4</v>
+      </c>
+      <c r="C56" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F56" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="G56" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H56" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I56" s="18"/>
+      <c r="G56" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H56" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I56" s="16"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="15" t="s">
+      <c r="A57" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="B57" s="16">
-        <v>4</v>
-      </c>
-      <c r="C57" s="17" t="s">
+      <c r="B57" s="14">
+        <v>4</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="F57" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="G57" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I57" s="18"/>
+      <c r="G57" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I57" s="16"/>
     </row>
     <row r="58" spans="1:9" ht="28.3">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="14">
         <v>5</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="F58" s="17" t="s">
+      <c r="F58" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="G58" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I58" s="18"/>
+      <c r="G58" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I58" s="16"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="14">
         <v>5</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="F59" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="G59" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="17" t="s">
+      <c r="G59" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I59" s="18"/>
+      <c r="I59" s="16"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="14">
         <v>5</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="F60" s="17" t="s">
+      <c r="F60" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="G60" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I60" s="18"/>
+      <c r="G60" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I60" s="16"/>
     </row>
     <row r="61" spans="1:9" ht="28.3">
-      <c r="A61" s="15" t="s">
+      <c r="A61" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="14">
         <v>5</v>
       </c>
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="F61" s="17" t="s">
+      <c r="F61" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="G61" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H61" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I61" s="18"/>
+      <c r="G61" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H61" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I61" s="16"/>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="14">
         <v>5</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="F62" s="17" t="s">
+      <c r="F62" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="G62" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I62" s="18"/>
+      <c r="G62" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I62" s="16"/>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="14">
         <v>5</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="F63" s="17" t="s">
+      <c r="F63" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="G63" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H63" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I63" s="18"/>
+      <c r="G63" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I63" s="16"/>
     </row>
     <row r="64" spans="1:9" ht="28.3">
-      <c r="A64" s="15" t="s">
+      <c r="A64" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="14">
         <v>5</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="F64" s="17" t="s">
+      <c r="F64" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="G64" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H64" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I64" s="18"/>
+      <c r="G64" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I64" s="16"/>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="14">
         <v>5</v>
       </c>
-      <c r="C65" s="17" t="s">
+      <c r="C65" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="F65" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="G65" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H65" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I65" s="18"/>
+      <c r="G65" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I65" s="16"/>
     </row>
     <row r="66" spans="1:9" ht="28.3">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="14">
         <v>5</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="F66" s="17" t="s">
+      <c r="F66" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="G66" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I66" s="18"/>
+      <c r="G66" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I66" s="16"/>
     </row>
     <row r="67" spans="1:9" ht="28.3">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="14">
         <v>5</v>
       </c>
-      <c r="C67" s="17" t="s">
+      <c r="C67" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="F67" s="17" t="s">
+      <c r="F67" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="G67" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H67" s="17" t="s">
+      <c r="G67" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H67" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I67" s="18"/>
+      <c r="I67" s="16"/>
     </row>
     <row r="68" spans="1:9" ht="28.3">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="14">
         <v>6</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C68" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="E68" s="17" t="s">
+      <c r="E68" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="F68" s="17" t="s">
+      <c r="F68" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="G68" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H68" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I68" s="18"/>
+      <c r="G68" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I68" s="16"/>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="14">
         <v>6</v>
       </c>
-      <c r="C69" s="17" t="s">
+      <c r="C69" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E69" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="F69" s="17" t="s">
+      <c r="F69" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="G69" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H69" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I69" s="18"/>
+      <c r="G69" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H69" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I69" s="16"/>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="14">
         <v>6</v>
       </c>
-      <c r="C70" s="17" t="s">
+      <c r="C70" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E70" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="F70" s="17" t="s">
+      <c r="F70" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="G70" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H70" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I70" s="18"/>
+      <c r="G70" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I70" s="16"/>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="15" t="s">
+      <c r="A71" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="B71" s="16">
+      <c r="B71" s="14">
         <v>6</v>
       </c>
-      <c r="C71" s="17" t="s">
+      <c r="C71" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D71" s="17" t="s">
+      <c r="D71" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E71" s="17" t="s">
+      <c r="E71" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="F71" s="17" t="s">
+      <c r="F71" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="G71" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H71" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I71" s="18"/>
+      <c r="G71" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H71" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I71" s="16"/>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="15" t="s">
+      <c r="A72" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="14">
         <v>6</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E72" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="G72" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I72" s="18"/>
+      <c r="G72" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I72" s="16"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="15" t="s">
+      <c r="A73" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="B73" s="16">
+      <c r="B73" s="14">
         <v>6</v>
       </c>
-      <c r="C73" s="17" t="s">
+      <c r="C73" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D73" s="17" t="s">
+      <c r="D73" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="E73" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="F73" s="17" t="s">
+      <c r="F73" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G73" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H73" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I73" s="18"/>
+      <c r="G73" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I73" s="16"/>
     </row>
     <row r="74" spans="1:9" ht="28.3">
-      <c r="A74" s="15" t="s">
+      <c r="A74" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="B74" s="16">
+      <c r="B74" s="14">
         <v>6</v>
       </c>
-      <c r="C74" s="17" t="s">
+      <c r="C74" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D74" s="17" t="s">
+      <c r="D74" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E74" s="17" t="s">
+      <c r="E74" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="F74" s="17" t="s">
+      <c r="F74" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="G74" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H74" s="17" t="s">
+      <c r="G74" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H74" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I74" s="18"/>
+      <c r="I74" s="16"/>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="15" t="s">
+      <c r="A75" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="B75" s="16">
+      <c r="B75" s="14">
         <v>6</v>
       </c>
-      <c r="C75" s="17" t="s">
+      <c r="C75" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D75" s="17" t="s">
+      <c r="D75" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E75" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="F75" s="17" t="s">
+      <c r="F75" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="G75" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H75" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I75" s="18"/>
+      <c r="G75" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H75" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I75" s="16"/>
     </row>
     <row r="76" spans="1:9">
-      <c r="A76" s="15" t="s">
+      <c r="A76" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="B76" s="16">
+      <c r="B76" s="14">
         <v>6</v>
       </c>
-      <c r="C76" s="17" t="s">
+      <c r="C76" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D76" s="17" t="s">
+      <c r="D76" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="E76" s="17" t="s">
+      <c r="E76" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="F76" s="17" t="s">
+      <c r="F76" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="G76" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H76" s="17" t="s">
+      <c r="G76" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I76" s="18"/>
+      <c r="I76" s="16"/>
     </row>
     <row r="77" spans="1:9">
-      <c r="A77" s="15" t="s">
+      <c r="A77" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="B77" s="16">
+      <c r="B77" s="14">
         <v>6</v>
       </c>
-      <c r="C77" s="17" t="s">
+      <c r="C77" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D77" s="17" t="s">
+      <c r="D77" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E77" s="17" t="s">
+      <c r="E77" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="F77" s="17" t="s">
+      <c r="F77" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="G77" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H77" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I77" s="18"/>
+      <c r="G77" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H77" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I77" s="16"/>
     </row>
     <row r="78" spans="1:9" ht="28.3">
-      <c r="A78" s="15" t="s">
+      <c r="A78" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="B78" s="16">
+      <c r="B78" s="14">
         <v>7</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="C78" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D78" s="17" t="s">
+      <c r="D78" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E78" s="17" t="s">
+      <c r="E78" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="F78" s="17" t="s">
+      <c r="F78" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="G78" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H78" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I78" s="18"/>
+      <c r="G78" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H78" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I78" s="16"/>
     </row>
     <row r="79" spans="1:9" ht="28.3">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="B79" s="16">
+      <c r="B79" s="14">
         <v>7</v>
       </c>
-      <c r="C79" s="17" t="s">
+      <c r="C79" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D79" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E79" s="17" t="s">
+      <c r="E79" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="F79" s="17" t="s">
+      <c r="F79" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="G79" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H79" s="17" t="s">
+      <c r="G79" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H79" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I79" s="18"/>
+      <c r="I79" s="16"/>
     </row>
     <row r="80" spans="1:9" ht="28.3">
-      <c r="A80" s="15" t="s">
+      <c r="A80" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="B80" s="16">
+      <c r="B80" s="14">
         <v>7</v>
       </c>
-      <c r="C80" s="17" t="s">
+      <c r="C80" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D80" s="17" t="s">
+      <c r="D80" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E80" s="17" t="s">
+      <c r="E80" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="F80" s="17" t="s">
+      <c r="F80" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="G80" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H80" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I80" s="18"/>
+      <c r="G80" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H80" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I80" s="16"/>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" s="15" t="s">
+      <c r="A81" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="14">
         <v>7</v>
       </c>
-      <c r="C81" s="17" t="s">
+      <c r="C81" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="17" t="s">
+      <c r="D81" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E81" s="17" t="s">
+      <c r="E81" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="F81" s="17" t="s">
+      <c r="F81" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="G81" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I81" s="18"/>
+      <c r="G81" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I81" s="16"/>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="15" t="s">
+      <c r="A82" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="14">
         <v>7</v>
       </c>
-      <c r="C82" s="17" t="s">
+      <c r="C82" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="17" t="s">
+      <c r="D82" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E82" s="17" t="s">
+      <c r="E82" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="F82" s="17" t="s">
+      <c r="F82" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="G82" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H82" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I82" s="18"/>
+      <c r="G82" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H82" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I82" s="16"/>
     </row>
     <row r="83" spans="1:9">
-      <c r="A83" s="15" t="s">
+      <c r="A83" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="B83" s="16">
+      <c r="B83" s="14">
         <v>7</v>
       </c>
-      <c r="C83" s="17" t="s">
+      <c r="C83" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D83" s="17" t="s">
+      <c r="D83" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E83" s="17" t="s">
+      <c r="E83" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="F83" s="17" t="s">
+      <c r="F83" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="G83" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I83" s="18"/>
+      <c r="G83" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I83" s="16"/>
     </row>
     <row r="84" spans="1:9" ht="28.3">
-      <c r="A84" s="15" t="s">
+      <c r="A84" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="B84" s="16">
+      <c r="B84" s="14">
         <v>7</v>
       </c>
-      <c r="C84" s="17" t="s">
+      <c r="C84" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E84" s="17" t="s">
+      <c r="E84" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="F84" s="17" t="s">
+      <c r="F84" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="G84" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H84" s="17" t="s">
+      <c r="G84" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H84" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I84" s="18"/>
+      <c r="I84" s="16"/>
     </row>
     <row r="85" spans="1:9" ht="28.3">
-      <c r="A85" s="15" t="s">
+      <c r="A85" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="B85" s="16">
+      <c r="B85" s="14">
         <v>7</v>
       </c>
-      <c r="C85" s="17" t="s">
+      <c r="C85" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D85" s="17" t="s">
+      <c r="D85" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E85" s="17" t="s">
+      <c r="E85" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="F85" s="17" t="s">
+      <c r="F85" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="G85" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H85" s="17" t="s">
+      <c r="G85" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H85" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I85" s="18"/>
+      <c r="I85" s="16"/>
     </row>
     <row r="86" spans="1:9">
-      <c r="A86" s="15" t="s">
+      <c r="A86" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="B86" s="16">
+      <c r="B86" s="14">
         <v>7</v>
       </c>
-      <c r="C86" s="17" t="s">
+      <c r="C86" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D86" s="17" t="s">
+      <c r="D86" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E86" s="17" t="s">
+      <c r="E86" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="F86" s="17" t="s">
+      <c r="F86" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="G86" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H86" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I86" s="18"/>
+      <c r="G86" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H86" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I86" s="16"/>
     </row>
     <row r="87" spans="1:9">
-      <c r="A87" s="15" t="s">
+      <c r="A87" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="B87" s="16">
+      <c r="B87" s="14">
         <v>7</v>
       </c>
-      <c r="C87" s="17" t="s">
+      <c r="C87" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D87" s="17" t="s">
+      <c r="D87" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E87" s="17" t="s">
+      <c r="E87" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="F87" s="17" t="s">
+      <c r="F87" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="G87" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H87" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I87" s="18"/>
+      <c r="G87" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I87" s="16"/>
     </row>
     <row r="88" spans="1:9" ht="28.3">
-      <c r="A88" s="15" t="s">
+      <c r="A88" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="B88" s="16">
+      <c r="B88" s="14">
         <v>8</v>
       </c>
-      <c r="C88" s="17" t="s">
+      <c r="C88" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D88" s="17" t="s">
+      <c r="D88" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E88" s="17" t="s">
+      <c r="E88" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="F88" s="17" t="s">
+      <c r="F88" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="G88" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H88" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I88" s="18"/>
+      <c r="G88" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H88" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I88" s="16"/>
     </row>
     <row r="89" spans="1:9">
-      <c r="A89" s="15" t="s">
+      <c r="A89" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="B89" s="16">
+      <c r="B89" s="14">
         <v>8</v>
       </c>
-      <c r="C89" s="17" t="s">
+      <c r="C89" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D89" s="17" t="s">
+      <c r="D89" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="E89" s="17" t="s">
+      <c r="E89" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="F89" s="17" t="s">
+      <c r="F89" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="G89" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H89" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I89" s="18"/>
+      <c r="G89" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I89" s="16"/>
     </row>
     <row r="90" spans="1:9">
-      <c r="A90" s="15" t="s">
+      <c r="A90" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="B90" s="16">
+      <c r="B90" s="14">
         <v>8</v>
       </c>
-      <c r="C90" s="17" t="s">
+      <c r="C90" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D90" s="17" t="s">
+      <c r="D90" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="E90" s="17" t="s">
+      <c r="E90" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="F90" s="17" t="s">
+      <c r="F90" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="G90" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H90" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I90" s="18"/>
+      <c r="G90" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H90" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I90" s="16"/>
     </row>
     <row r="91" spans="1:9">
-      <c r="A91" s="15" t="s">
+      <c r="A91" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="B91" s="16">
+      <c r="B91" s="14">
         <v>8</v>
       </c>
-      <c r="C91" s="17" t="s">
+      <c r="C91" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D91" s="17" t="s">
+      <c r="D91" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="E91" s="17" t="s">
+      <c r="E91" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="F91" s="17" t="s">
+      <c r="F91" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="G91" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H91" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I91" s="18"/>
+      <c r="G91" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I91" s="16"/>
     </row>
     <row r="92" spans="1:9" ht="28.3">
-      <c r="A92" s="15" t="s">
+      <c r="A92" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="B92" s="16">
+      <c r="B92" s="14">
         <v>8</v>
       </c>
-      <c r="C92" s="17" t="s">
+      <c r="C92" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D92" s="17" t="s">
+      <c r="D92" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="E92" s="17" t="s">
+      <c r="E92" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="F92" s="17" t="s">
+      <c r="F92" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="G92" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H92" s="17" t="s">
+      <c r="G92" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H92" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I92" s="18"/>
+      <c r="I92" s="16"/>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="15" t="s">
+      <c r="A93" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="B93" s="16">
+      <c r="B93" s="14">
         <v>8</v>
       </c>
-      <c r="C93" s="17" t="s">
+      <c r="C93" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D93" s="17" t="s">
+      <c r="D93" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="E93" s="17" t="s">
+      <c r="E93" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="F93" s="17" t="s">
+      <c r="F93" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="G93" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H93" s="17" t="s">
+      <c r="G93" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H93" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I93" s="18"/>
+      <c r="I93" s="16"/>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="15" t="s">
+      <c r="A94" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="B94" s="16">
+      <c r="B94" s="14">
         <v>8</v>
       </c>
-      <c r="C94" s="17" t="s">
+      <c r="C94" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D94" s="17" t="s">
+      <c r="D94" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="E94" s="17" t="s">
+      <c r="E94" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="F94" s="17" t="s">
+      <c r="F94" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="G94" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H94" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I94" s="18"/>
+      <c r="G94" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I94" s="16"/>
     </row>
     <row r="95" spans="1:9" ht="28.3">
-      <c r="A95" s="15" t="s">
+      <c r="A95" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B95" s="14">
         <v>8</v>
       </c>
-      <c r="C95" s="17" t="s">
+      <c r="C95" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D95" s="17" t="s">
+      <c r="D95" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E95" s="17" t="s">
+      <c r="E95" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="F95" s="17" t="s">
+      <c r="F95" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="G95" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H95" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I95" s="18"/>
+      <c r="G95" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H95" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I95" s="16"/>
     </row>
     <row r="96" spans="1:9">
-      <c r="A96" s="15" t="s">
+      <c r="A96" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B96" s="14">
         <v>8</v>
       </c>
-      <c r="C96" s="17" t="s">
+      <c r="C96" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D96" s="17" t="s">
+      <c r="D96" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E96" s="17" t="s">
+      <c r="E96" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="F96" s="17" t="s">
+      <c r="F96" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="G96" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="17" t="s">
+      <c r="G96" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I96" s="18"/>
+      <c r="I96" s="16"/>
     </row>
     <row r="97" spans="1:9">
-      <c r="A97" s="15" t="s">
+      <c r="A97" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B97" s="14">
         <v>8</v>
       </c>
-      <c r="C97" s="17" t="s">
+      <c r="C97" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D97" s="17" t="s">
+      <c r="D97" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E97" s="17" t="s">
+      <c r="E97" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="F97" s="17" t="s">
+      <c r="F97" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="G97" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H97" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I97" s="18"/>
+      <c r="G97" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H97" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I97" s="16"/>
     </row>
     <row r="98" spans="1:9" ht="28.3">
-      <c r="A98" s="15" t="s">
+      <c r="A98" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B98" s="14">
         <v>9</v>
       </c>
-      <c r="C98" s="17" t="s">
+      <c r="C98" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D98" s="17" t="s">
+      <c r="D98" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="E98" s="17" t="s">
+      <c r="E98" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="F98" s="17" t="s">
+      <c r="F98" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="G98" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H98" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I98" s="18"/>
+      <c r="G98" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H98" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I98" s="16"/>
     </row>
     <row r="99" spans="1:9">
-      <c r="A99" s="15" t="s">
+      <c r="A99" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B99" s="14">
         <v>9</v>
       </c>
-      <c r="C99" s="17" t="s">
+      <c r="C99" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D99" s="17" t="s">
+      <c r="D99" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E99" s="17" t="s">
+      <c r="E99" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="F99" s="17" t="s">
+      <c r="F99" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="G99" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H99" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I99" s="18"/>
+      <c r="G99" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H99" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I99" s="16"/>
     </row>
     <row r="100" spans="1:9">
-      <c r="A100" s="15" t="s">
+      <c r="A100" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B100" s="14">
         <v>9</v>
       </c>
-      <c r="C100" s="17" t="s">
+      <c r="C100" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D100" s="17" t="s">
+      <c r="D100" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="E100" s="17" t="s">
+      <c r="E100" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="F100" s="17" t="s">
+      <c r="F100" s="15" t="s">
         <v>372</v>
       </c>
-      <c r="G100" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H100" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I100" s="18"/>
+      <c r="G100" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I100" s="16"/>
     </row>
     <row r="101" spans="1:9" ht="28.3">
-      <c r="A101" s="15" t="s">
+      <c r="A101" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B101" s="14">
         <v>9</v>
       </c>
-      <c r="C101" s="17" t="s">
+      <c r="C101" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D101" s="17" t="s">
+      <c r="D101" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E101" s="17" t="s">
+      <c r="E101" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="F101" s="17" t="s">
+      <c r="F101" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="G101" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H101" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I101" s="18"/>
+      <c r="G101" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I101" s="16"/>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="15" t="s">
+      <c r="A102" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B102" s="14">
         <v>9</v>
       </c>
-      <c r="C102" s="17" t="s">
+      <c r="C102" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D102" s="17" t="s">
+      <c r="D102" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E102" s="17" t="s">
+      <c r="E102" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="F102" s="17" t="s">
+      <c r="F102" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="G102" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H102" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I102" s="18"/>
+      <c r="G102" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H102" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I102" s="16"/>
     </row>
     <row r="103" spans="1:9" ht="28.3">
-      <c r="A103" s="15" t="s">
+      <c r="A103" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B103" s="14">
         <v>9</v>
       </c>
-      <c r="C103" s="17" t="s">
+      <c r="C103" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D103" s="17" t="s">
+      <c r="D103" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E103" s="17" t="s">
+      <c r="E103" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="F103" s="17" t="s">
+      <c r="F103" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="G103" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H103" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I103" s="18"/>
+      <c r="G103" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H103" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I103" s="16"/>
     </row>
     <row r="104" spans="1:9">
-      <c r="A104" s="15" t="s">
+      <c r="A104" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B104" s="14">
         <v>9</v>
       </c>
-      <c r="C104" s="17" t="s">
+      <c r="C104" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D104" s="17" t="s">
+      <c r="D104" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="E104" s="17" t="s">
+      <c r="E104" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="F104" s="17" t="s">
+      <c r="F104" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="G104" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H104" s="17" t="s">
+      <c r="G104" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H104" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I104" s="18"/>
+      <c r="I104" s="16"/>
     </row>
     <row r="105" spans="1:9">
-      <c r="A105" s="15" t="s">
+      <c r="A105" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B105" s="14">
         <v>9</v>
       </c>
-      <c r="C105" s="17" t="s">
+      <c r="C105" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D105" s="17" t="s">
+      <c r="D105" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E105" s="17" t="s">
+      <c r="E105" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="F105" s="17" t="s">
+      <c r="F105" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="G105" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H105" s="17" t="s">
+      <c r="G105" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H105" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I105" s="18"/>
+      <c r="I105" s="16"/>
     </row>
     <row r="106" spans="1:9">
-      <c r="A106" s="15" t="s">
+      <c r="A106" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B106" s="14">
         <v>9</v>
       </c>
-      <c r="C106" s="17" t="s">
+      <c r="C106" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D106" s="17" t="s">
+      <c r="D106" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E106" s="17" t="s">
+      <c r="E106" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="F106" s="17" t="s">
+      <c r="F106" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="G106" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H106" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I106" s="18"/>
+      <c r="G106" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H106" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I106" s="16"/>
     </row>
     <row r="107" spans="1:9">
-      <c r="A107" s="15" t="s">
+      <c r="A107" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B107" s="14">
         <v>9</v>
       </c>
-      <c r="C107" s="17" t="s">
+      <c r="C107" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D107" s="17" t="s">
+      <c r="D107" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E107" s="17" t="s">
+      <c r="E107" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="F107" s="17" t="s">
+      <c r="F107" s="15" t="s">
         <v>392</v>
       </c>
-      <c r="G107" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H107" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I107" s="18"/>
+      <c r="G107" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H107" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I107" s="16"/>
     </row>
     <row r="108" spans="1:9" ht="28.3">
-      <c r="A108" s="15" t="s">
+      <c r="A108" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B108" s="14">
         <v>10</v>
       </c>
-      <c r="C108" s="17" t="s">
+      <c r="C108" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D108" s="17" t="s">
+      <c r="D108" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E108" s="17" t="s">
+      <c r="E108" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="F108" s="17" t="s">
+      <c r="F108" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="G108" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H108" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I108" s="18"/>
+      <c r="G108" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H108" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I108" s="16"/>
     </row>
     <row r="109" spans="1:9" ht="28.3">
-      <c r="A109" s="15" t="s">
+      <c r="A109" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B109" s="14">
         <v>10</v>
       </c>
-      <c r="C109" s="17" t="s">
+      <c r="C109" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D109" s="17" t="s">
+      <c r="D109" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="E109" s="17" t="s">
+      <c r="E109" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="F109" s="17" t="s">
+      <c r="F109" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="G109" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H109" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I109" s="18"/>
+      <c r="G109" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H109" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I109" s="16"/>
     </row>
     <row r="110" spans="1:9">
-      <c r="A110" s="15" t="s">
+      <c r="A110" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B110" s="14">
         <v>10</v>
       </c>
-      <c r="C110" s="17" t="s">
+      <c r="C110" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D110" s="17" t="s">
+      <c r="D110" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E110" s="17" t="s">
+      <c r="E110" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="F110" s="17" t="s">
+      <c r="F110" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="G110" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H110" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I110" s="18"/>
+      <c r="G110" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H110" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I110" s="16"/>
     </row>
     <row r="111" spans="1:9">
-      <c r="A111" s="15" t="s">
+      <c r="A111" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B111" s="14">
         <v>10</v>
       </c>
-      <c r="C111" s="17" t="s">
+      <c r="C111" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D111" s="17" t="s">
+      <c r="D111" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E111" s="17" t="s">
+      <c r="E111" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="F111" s="17" t="s">
+      <c r="F111" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="G111" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H111" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I111" s="18"/>
+      <c r="G111" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I111" s="16"/>
     </row>
     <row r="112" spans="1:9">
-      <c r="A112" s="15" t="s">
+      <c r="A112" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B112" s="14">
         <v>10</v>
       </c>
-      <c r="C112" s="17" t="s">
+      <c r="C112" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D112" s="17" t="s">
+      <c r="D112" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E112" s="17" t="s">
+      <c r="E112" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="F112" s="17" t="s">
+      <c r="F112" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="G112" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H112" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I112" s="18"/>
+      <c r="G112" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H112" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I112" s="16"/>
     </row>
     <row r="113" spans="1:9">
-      <c r="A113" s="15" t="s">
+      <c r="A113" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B113" s="14">
         <v>10</v>
       </c>
-      <c r="C113" s="17" t="s">
+      <c r="C113" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D113" s="17" t="s">
+      <c r="D113" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E113" s="17" t="s">
+      <c r="E113" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="F113" s="17" t="s">
+      <c r="F113" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="G113" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H113" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I113" s="18"/>
+      <c r="G113" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H113" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I113" s="16"/>
     </row>
     <row r="114" spans="1:9">
-      <c r="A114" s="15" t="s">
+      <c r="A114" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B114" s="14">
         <v>10</v>
       </c>
-      <c r="C114" s="17" t="s">
+      <c r="C114" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D114" s="17" t="s">
+      <c r="D114" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E114" s="17" t="s">
+      <c r="E114" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="F114" s="17" t="s">
+      <c r="F114" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="G114" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H114" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I114" s="18"/>
+      <c r="G114" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H114" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I114" s="16"/>
     </row>
     <row r="115" spans="1:9">
-      <c r="A115" s="15" t="s">
+      <c r="A115" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="14">
         <v>10</v>
       </c>
-      <c r="C115" s="17" t="s">
+      <c r="C115" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D115" s="17" t="s">
+      <c r="D115" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="E115" s="17" t="s">
+      <c r="E115" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="F115" s="17" t="s">
+      <c r="F115" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="G115" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H115" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I115" s="18"/>
+      <c r="G115" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H115" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I115" s="16"/>
     </row>
     <row r="116" spans="1:9">
-      <c r="A116" s="15" t="s">
+      <c r="A116" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="B116" s="16">
+      <c r="B116" s="14">
         <v>10</v>
       </c>
-      <c r="C116" s="17" t="s">
+      <c r="C116" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D116" s="17" t="s">
+      <c r="D116" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E116" s="17" t="s">
+      <c r="E116" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="F116" s="17" t="s">
+      <c r="F116" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="G116" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H116" s="17" t="s">
+      <c r="G116" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H116" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I116" s="18"/>
+      <c r="I116" s="16"/>
     </row>
     <row r="117" spans="1:9" ht="28.3">
-      <c r="A117" s="15" t="s">
+      <c r="A117" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="B117" s="16">
+      <c r="B117" s="14">
         <v>10</v>
       </c>
-      <c r="C117" s="17" t="s">
+      <c r="C117" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D117" s="17" t="s">
+      <c r="D117" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="E117" s="17" t="s">
+      <c r="E117" s="15" t="s">
         <v>421</v>
       </c>
-      <c r="F117" s="17" t="s">
+      <c r="F117" s="15" t="s">
         <v>422</v>
       </c>
-      <c r="G117" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H117" s="17" t="s">
+      <c r="G117" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H117" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I117" s="18"/>
+      <c r="I117" s="16"/>
     </row>
     <row r="118" spans="1:9">
-      <c r="A118" s="15" t="s">
+      <c r="A118" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="B118" s="16">
+      <c r="B118" s="14">
         <v>10</v>
       </c>
-      <c r="C118" s="17" t="s">
+      <c r="C118" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D118" s="17" t="s">
+      <c r="D118" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E118" s="17" t="s">
+      <c r="E118" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="F118" s="17" t="s">
+      <c r="F118" s="15" t="s">
         <v>425</v>
       </c>
-      <c r="G118" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H118" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I118" s="18"/>
+      <c r="G118" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H118" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I118" s="16"/>
     </row>
     <row r="119" spans="1:9" ht="28.3">
-      <c r="A119" s="15" t="s">
+      <c r="A119" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="B119" s="16">
+      <c r="B119" s="14">
         <v>11</v>
       </c>
-      <c r="C119" s="17" t="s">
+      <c r="C119" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D119" s="17" t="s">
+      <c r="D119" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E119" s="17" t="s">
+      <c r="E119" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="F119" s="17" t="s">
+      <c r="F119" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="G119" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H119" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I119" s="18"/>
+      <c r="G119" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H119" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I119" s="16"/>
     </row>
     <row r="120" spans="1:9" ht="28.3">
-      <c r="A120" s="15" t="s">
+      <c r="A120" s="13" t="s">
         <v>429</v>
       </c>
-      <c r="B120" s="16">
+      <c r="B120" s="14">
         <v>11</v>
       </c>
-      <c r="C120" s="17" t="s">
+      <c r="C120" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D120" s="17" t="s">
+      <c r="D120" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E120" s="17" t="s">
+      <c r="E120" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="F120" s="17" t="s">
+      <c r="F120" s="15" t="s">
         <v>431</v>
       </c>
-      <c r="G120" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H120" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I120" s="18"/>
+      <c r="G120" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H120" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I120" s="16"/>
     </row>
     <row r="121" spans="1:9" ht="28.3">
-      <c r="A121" s="15" t="s">
+      <c r="A121" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="B121" s="16">
+      <c r="B121" s="14">
         <v>11</v>
       </c>
-      <c r="C121" s="17" t="s">
+      <c r="C121" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D121" s="17" t="s">
+      <c r="D121" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E121" s="17" t="s">
+      <c r="E121" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="F121" s="17" t="s">
+      <c r="F121" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="G121" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H121" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I121" s="18"/>
+      <c r="G121" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H121" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I121" s="16"/>
     </row>
     <row r="122" spans="1:9">
-      <c r="A122" s="15" t="s">
+      <c r="A122" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="B122" s="16">
+      <c r="B122" s="14">
         <v>11</v>
       </c>
-      <c r="C122" s="17" t="s">
+      <c r="C122" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D122" s="17" t="s">
+      <c r="D122" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E122" s="17" t="s">
+      <c r="E122" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="F122" s="17" t="s">
+      <c r="F122" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="G122" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H122" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I122" s="18"/>
+      <c r="G122" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H122" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I122" s="16"/>
     </row>
     <row r="123" spans="1:9">
-      <c r="A123" s="15" t="s">
+      <c r="A123" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="B123" s="16">
+      <c r="B123" s="14">
         <v>11</v>
       </c>
-      <c r="C123" s="17" t="s">
+      <c r="C123" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D123" s="17" t="s">
+      <c r="D123" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E123" s="17" t="s">
+      <c r="E123" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="F123" s="17" t="s">
+      <c r="F123" s="15" t="s">
         <v>440</v>
       </c>
-      <c r="G123" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H123" s="17" t="s">
+      <c r="G123" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H123" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I123" s="18"/>
+      <c r="I123" s="16"/>
     </row>
     <row r="124" spans="1:9" ht="28.3">
-      <c r="A124" s="15" t="s">
+      <c r="A124" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="B124" s="16">
+      <c r="B124" s="14">
         <v>11</v>
       </c>
-      <c r="C124" s="17" t="s">
+      <c r="C124" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D124" s="17" t="s">
+      <c r="D124" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="E124" s="17" t="s">
+      <c r="E124" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="F124" s="17" t="s">
+      <c r="F124" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="G124" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H124" s="17" t="s">
+      <c r="G124" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H124" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I124" s="18"/>
+      <c r="I124" s="16"/>
     </row>
     <row r="125" spans="1:9">
-      <c r="A125" s="15" t="s">
+      <c r="A125" s="13" t="s">
         <v>444</v>
       </c>
-      <c r="B125" s="16">
+      <c r="B125" s="14">
         <v>11</v>
       </c>
-      <c r="C125" s="17" t="s">
+      <c r="C125" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D125" s="17" t="s">
+      <c r="D125" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E125" s="17" t="s">
+      <c r="E125" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="F125" s="17" t="s">
+      <c r="F125" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="G125" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H125" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I125" s="18"/>
+      <c r="G125" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H125" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I125" s="16"/>
     </row>
     <row r="126" spans="1:9" ht="28.3">
-      <c r="A126" s="15" t="s">
+      <c r="A126" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="B126" s="16">
+      <c r="B126" s="14">
         <v>11</v>
       </c>
-      <c r="C126" s="17" t="s">
+      <c r="C126" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D126" s="17" t="s">
+      <c r="D126" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E126" s="17" t="s">
+      <c r="E126" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="F126" s="17" t="s">
+      <c r="F126" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="G126" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H126" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I126" s="18"/>
+      <c r="G126" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H126" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I126" s="16"/>
     </row>
     <row r="127" spans="1:9">
-      <c r="A127" s="15" t="s">
+      <c r="A127" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="B127" s="16">
+      <c r="B127" s="14">
         <v>11</v>
       </c>
-      <c r="C127" s="17" t="s">
+      <c r="C127" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D127" s="17" t="s">
+      <c r="D127" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E127" s="17" t="s">
+      <c r="E127" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="F127" s="17" t="s">
+      <c r="F127" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="G127" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H127" s="17" t="s">
+      <c r="G127" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H127" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I127" s="18"/>
+      <c r="I127" s="16"/>
     </row>
     <row r="128" spans="1:9">
-      <c r="A128" s="15" t="s">
+      <c r="A128" s="13" t="s">
         <v>452</v>
       </c>
-      <c r="B128" s="16">
+      <c r="B128" s="14">
         <v>11</v>
       </c>
-      <c r="C128" s="17" t="s">
+      <c r="C128" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D128" s="17" t="s">
+      <c r="D128" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E128" s="17" t="s">
+      <c r="E128" s="15" t="s">
         <v>453</v>
       </c>
-      <c r="F128" s="17" t="s">
+      <c r="F128" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="G128" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H128" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I128" s="18"/>
+      <c r="G128" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H128" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I128" s="16"/>
     </row>
     <row r="129" spans="1:9" ht="28.3">
-      <c r="A129" s="15" t="s">
+      <c r="A129" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="B129" s="16">
+      <c r="B129" s="14">
         <v>12</v>
       </c>
-      <c r="C129" s="17" t="s">
+      <c r="C129" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D129" s="17" t="s">
+      <c r="D129" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="E129" s="17" t="s">
+      <c r="E129" s="15" t="s">
         <v>456</v>
       </c>
-      <c r="F129" s="17" t="s">
+      <c r="F129" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="G129" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H129" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I129" s="18"/>
+      <c r="G129" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H129" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I129" s="16"/>
     </row>
     <row r="130" spans="1:9" ht="28.3">
-      <c r="A130" s="15" t="s">
+      <c r="A130" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="B130" s="16">
+      <c r="B130" s="14">
         <v>12</v>
       </c>
-      <c r="C130" s="17" t="s">
+      <c r="C130" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D130" s="17" t="s">
+      <c r="D130" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="E130" s="17" t="s">
+      <c r="E130" s="15" t="s">
         <v>460</v>
       </c>
-      <c r="F130" s="17" t="s">
+      <c r="F130" s="15" t="s">
         <v>461</v>
       </c>
-      <c r="G130" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H130" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I130" s="18"/>
+      <c r="G130" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H130" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I130" s="16"/>
     </row>
     <row r="131" spans="1:9">
-      <c r="A131" s="15" t="s">
+      <c r="A131" s="13" t="s">
         <v>462</v>
       </c>
-      <c r="B131" s="16">
+      <c r="B131" s="14">
         <v>12</v>
       </c>
-      <c r="C131" s="17" t="s">
+      <c r="C131" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D131" s="17" t="s">
+      <c r="D131" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="E131" s="17" t="s">
+      <c r="E131" s="15" t="s">
         <v>464</v>
       </c>
-      <c r="F131" s="17" t="s">
+      <c r="F131" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="G131" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H131" s="17" t="s">
+      <c r="G131" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H131" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I131" s="18"/>
+      <c r="I131" s="16"/>
     </row>
     <row r="132" spans="1:9">
-      <c r="A132" s="15" t="s">
+      <c r="A132" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="B132" s="16">
+      <c r="B132" s="14">
         <v>12</v>
       </c>
-      <c r="C132" s="17" t="s">
+      <c r="C132" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D132" s="17" t="s">
+      <c r="D132" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E132" s="17" t="s">
+      <c r="E132" s="15" t="s">
         <v>467</v>
       </c>
-      <c r="F132" s="17" t="s">
+      <c r="F132" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="G132" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H132" s="17" t="s">
+      <c r="G132" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H132" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I132" s="18"/>
+      <c r="I132" s="16"/>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="15" t="s">
+      <c r="A133" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="B133" s="16">
+      <c r="B133" s="14">
         <v>12</v>
       </c>
-      <c r="C133" s="17" t="s">
+      <c r="C133" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="17" t="s">
+      <c r="D133" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E133" s="17" t="s">
+      <c r="E133" s="15" t="s">
         <v>470</v>
       </c>
-      <c r="F133" s="17" t="s">
+      <c r="F133" s="15" t="s">
         <v>471</v>
       </c>
-      <c r="G133" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H133" s="17" t="s">
+      <c r="G133" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H133" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I133" s="18"/>
+      <c r="I133" s="16"/>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="15" t="s">
+      <c r="A134" s="13" t="s">
         <v>472</v>
       </c>
-      <c r="B134" s="16">
+      <c r="B134" s="14">
         <v>12</v>
       </c>
-      <c r="C134" s="17" t="s">
+      <c r="C134" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D134" s="17" t="s">
+      <c r="D134" s="15" t="s">
         <v>473</v>
       </c>
-      <c r="E134" s="17" t="s">
+      <c r="E134" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="F134" s="17" t="s">
+      <c r="F134" s="15" t="s">
         <v>475</v>
       </c>
-      <c r="G134" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H134" s="17" t="s">
+      <c r="G134" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H134" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I134" s="18"/>
+      <c r="I134" s="16"/>
     </row>
     <row r="135" spans="1:9" ht="28.3">
-      <c r="A135" s="15" t="s">
+      <c r="A135" s="13" t="s">
         <v>476</v>
       </c>
-      <c r="B135" s="16">
+      <c r="B135" s="14">
         <v>12</v>
       </c>
-      <c r="C135" s="17" t="s">
+      <c r="C135" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D135" s="17" t="s">
+      <c r="D135" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="E135" s="17" t="s">
+      <c r="E135" s="15" t="s">
         <v>478</v>
       </c>
-      <c r="F135" s="17" t="s">
+      <c r="F135" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="G135" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H135" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I135" s="18"/>
+      <c r="G135" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H135" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I135" s="16"/>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="15" t="s">
+      <c r="A136" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="B136" s="16">
+      <c r="B136" s="14">
         <v>12</v>
       </c>
-      <c r="C136" s="17" t="s">
+      <c r="C136" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D136" s="17" t="s">
+      <c r="D136" s="15" t="s">
         <v>481</v>
       </c>
-      <c r="E136" s="17" t="s">
+      <c r="E136" s="15" t="s">
         <v>482</v>
       </c>
-      <c r="F136" s="17" t="s">
+      <c r="F136" s="15" t="s">
         <v>483</v>
       </c>
-      <c r="G136" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H136" s="17" t="s">
+      <c r="G136" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H136" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I136" s="18"/>
+      <c r="I136" s="16"/>
     </row>
     <row r="137" spans="1:9" ht="28.3">
-      <c r="A137" s="15" t="s">
+      <c r="A137" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="B137" s="16">
+      <c r="B137" s="14">
         <v>12</v>
       </c>
-      <c r="C137" s="17" t="s">
+      <c r="C137" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D137" s="17" t="s">
+      <c r="D137" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="E137" s="17" t="s">
+      <c r="E137" s="15" t="s">
         <v>486</v>
       </c>
-      <c r="F137" s="17" t="s">
+      <c r="F137" s="15" t="s">
         <v>487</v>
       </c>
-      <c r="G137" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H137" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I137" s="18"/>
+      <c r="G137" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H137" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I137" s="16"/>
     </row>
     <row r="138" spans="1:9" ht="28.3">
-      <c r="A138" s="15" t="s">
+      <c r="A138" s="13" t="s">
         <v>488</v>
       </c>
-      <c r="B138" s="16">
+      <c r="B138" s="14">
         <v>12</v>
       </c>
-      <c r="C138" s="17" t="s">
+      <c r="C138" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D138" s="17" t="s">
+      <c r="D138" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E138" s="17" t="s">
+      <c r="E138" s="15" t="s">
         <v>489</v>
       </c>
-      <c r="F138" s="17" t="s">
+      <c r="F138" s="15" t="s">
         <v>490</v>
       </c>
-      <c r="G138" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H138" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I138" s="18"/>
+      <c r="G138" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H138" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I138" s="16"/>
     </row>
     <row r="139" spans="1:9" ht="28.3">
-      <c r="A139" s="15" t="s">
+      <c r="A139" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="B139" s="16">
+      <c r="B139" s="14">
         <v>13</v>
       </c>
-      <c r="C139" s="17" t="s">
+      <c r="C139" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D139" s="17" t="s">
+      <c r="D139" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="E139" s="17" t="s">
+      <c r="E139" s="15" t="s">
         <v>493</v>
       </c>
-      <c r="F139" s="17" t="s">
+      <c r="F139" s="15" t="s">
         <v>494</v>
       </c>
-      <c r="G139" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H139" s="17" t="s">
+      <c r="G139" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H139" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I139" s="18"/>
+      <c r="I139" s="16"/>
     </row>
     <row r="140" spans="1:9" ht="28.3">
-      <c r="A140" s="15" t="s">
+      <c r="A140" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="B140" s="16">
+      <c r="B140" s="14">
         <v>13</v>
       </c>
-      <c r="C140" s="17" t="s">
+      <c r="C140" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D140" s="17" t="s">
+      <c r="D140" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="E140" s="17" t="s">
+      <c r="E140" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="F140" s="17" t="s">
+      <c r="F140" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="G140" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H140" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I140" s="18"/>
+      <c r="G140" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H140" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I140" s="16"/>
     </row>
     <row r="141" spans="1:9" ht="28.3">
-      <c r="A141" s="15" t="s">
+      <c r="A141" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="B141" s="16">
+      <c r="B141" s="14">
         <v>13</v>
       </c>
-      <c r="C141" s="17" t="s">
+      <c r="C141" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D141" s="17" t="s">
+      <c r="D141" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="E141" s="17" t="s">
+      <c r="E141" s="15" t="s">
         <v>499</v>
       </c>
-      <c r="F141" s="17" t="s">
+      <c r="F141" s="15" t="s">
         <v>500</v>
       </c>
-      <c r="G141" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H141" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I141" s="18"/>
+      <c r="G141" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H141" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I141" s="16"/>
     </row>
     <row r="142" spans="1:9" ht="28.3">
-      <c r="A142" s="15" t="s">
+      <c r="A142" s="13" t="s">
         <v>501</v>
       </c>
-      <c r="B142" s="16">
+      <c r="B142" s="14">
         <v>13</v>
       </c>
-      <c r="C142" s="17" t="s">
+      <c r="C142" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D142" s="17" t="s">
+      <c r="D142" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="E142" s="17" t="s">
+      <c r="E142" s="15" t="s">
         <v>502</v>
       </c>
-      <c r="F142" s="17" t="s">
+      <c r="F142" s="15" t="s">
         <v>503</v>
       </c>
-      <c r="G142" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H142" s="17" t="s">
+      <c r="G142" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H142" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I142" s="18"/>
+      <c r="I142" s="16"/>
     </row>
     <row r="143" spans="1:9">
-      <c r="A143" s="15" t="s">
+      <c r="A143" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="B143" s="16">
+      <c r="B143" s="14">
         <v>13</v>
       </c>
-      <c r="C143" s="17" t="s">
+      <c r="C143" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D143" s="17" t="s">
+      <c r="D143" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="E143" s="17" t="s">
+      <c r="E143" s="15" t="s">
         <v>505</v>
       </c>
-      <c r="F143" s="17" t="s">
+      <c r="F143" s="15" t="s">
         <v>506</v>
       </c>
-      <c r="G143" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H143" s="17" t="s">
+      <c r="G143" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H143" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I143" s="18"/>
+      <c r="I143" s="16"/>
     </row>
     <row r="144" spans="1:9" ht="28.3">
-      <c r="A144" s="15" t="s">
+      <c r="A144" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="B144" s="16">
+      <c r="B144" s="14">
         <v>13</v>
       </c>
-      <c r="C144" s="17" t="s">
+      <c r="C144" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D144" s="17" t="s">
+      <c r="D144" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="E144" s="17" t="s">
+      <c r="E144" s="15" t="s">
         <v>508</v>
       </c>
-      <c r="F144" s="17" t="s">
+      <c r="F144" s="15" t="s">
         <v>509</v>
       </c>
-      <c r="G144" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H144" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I144" s="18"/>
+      <c r="G144" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H144" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I144" s="16"/>
     </row>
     <row r="145" spans="1:9">
-      <c r="A145" s="15" t="s">
+      <c r="A145" s="13" t="s">
         <v>510</v>
       </c>
-      <c r="B145" s="16">
+      <c r="B145" s="14">
         <v>13</v>
       </c>
-      <c r="C145" s="17" t="s">
+      <c r="C145" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D145" s="17" t="s">
+      <c r="D145" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E145" s="17" t="s">
+      <c r="E145" s="15" t="s">
         <v>511</v>
       </c>
-      <c r="F145" s="17" t="s">
+      <c r="F145" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="G145" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H145" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I145" s="18"/>
+      <c r="G145" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H145" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I145" s="16"/>
     </row>
     <row r="146" spans="1:9">
-      <c r="A146" s="15" t="s">
+      <c r="A146" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="B146" s="16">
+      <c r="B146" s="14">
         <v>13</v>
       </c>
-      <c r="C146" s="17" t="s">
+      <c r="C146" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D146" s="17" t="s">
+      <c r="D146" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E146" s="17" t="s">
+      <c r="E146" s="15" t="s">
         <v>514</v>
       </c>
-      <c r="F146" s="17" t="s">
+      <c r="F146" s="15" t="s">
         <v>515</v>
       </c>
-      <c r="G146" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H146" s="17" t="s">
+      <c r="G146" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H146" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I146" s="18"/>
+      <c r="I146" s="16"/>
     </row>
     <row r="147" spans="1:9" ht="28.3">
-      <c r="A147" s="15" t="s">
+      <c r="A147" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="B147" s="16">
+      <c r="B147" s="14">
         <v>13</v>
       </c>
-      <c r="C147" s="17" t="s">
+      <c r="C147" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D147" s="17" t="s">
+      <c r="D147" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E147" s="17" t="s">
+      <c r="E147" s="15" t="s">
         <v>517</v>
       </c>
-      <c r="F147" s="17" t="s">
+      <c r="F147" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="G147" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H147" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I147" s="18"/>
+      <c r="G147" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H147" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I147" s="16"/>
     </row>
     <row r="148" spans="1:9">
-      <c r="A148" s="15" t="s">
+      <c r="A148" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="B148" s="16">
+      <c r="B148" s="14">
         <v>13</v>
       </c>
-      <c r="C148" s="17" t="s">
+      <c r="C148" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D148" s="17" t="s">
+      <c r="D148" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E148" s="17" t="s">
+      <c r="E148" s="15" t="s">
         <v>520</v>
       </c>
-      <c r="F148" s="17" t="s">
+      <c r="F148" s="15" t="s">
         <v>521</v>
       </c>
-      <c r="G148" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H148" s="17" t="s">
+      <c r="G148" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H148" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I148" s="18"/>
+      <c r="I148" s="16"/>
     </row>
     <row r="149" spans="1:9">
-      <c r="A149" s="15" t="s">
+      <c r="A149" s="13" t="s">
         <v>522</v>
       </c>
-      <c r="B149" s="16">
+      <c r="B149" s="14">
         <v>14</v>
       </c>
-      <c r="C149" s="17" t="s">
+      <c r="C149" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D149" s="17" t="s">
+      <c r="D149" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="E149" s="17" t="s">
+      <c r="E149" s="15" t="s">
         <v>524</v>
       </c>
-      <c r="F149" s="17" t="s">
+      <c r="F149" s="15" t="s">
         <v>525</v>
       </c>
-      <c r="G149" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H149" s="17" t="s">
+      <c r="G149" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H149" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I149" s="18"/>
+      <c r="I149" s="16"/>
     </row>
     <row r="150" spans="1:9">
-      <c r="A150" s="15" t="s">
+      <c r="A150" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="B150" s="16">
+      <c r="B150" s="14">
         <v>14</v>
       </c>
-      <c r="C150" s="17" t="s">
+      <c r="C150" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D150" s="17" t="s">
+      <c r="D150" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="E150" s="17" t="s">
+      <c r="E150" s="15" t="s">
         <v>527</v>
       </c>
-      <c r="F150" s="17" t="s">
+      <c r="F150" s="15" t="s">
         <v>528</v>
       </c>
-      <c r="G150" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H150" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I150" s="18"/>
+      <c r="G150" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H150" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I150" s="16"/>
     </row>
     <row r="151" spans="1:9">
-      <c r="A151" s="15" t="s">
+      <c r="A151" s="13" t="s">
         <v>529</v>
       </c>
-      <c r="B151" s="16">
+      <c r="B151" s="14">
         <v>14</v>
       </c>
-      <c r="C151" s="17" t="s">
+      <c r="C151" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D151" s="17" t="s">
+      <c r="D151" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="E151" s="17" t="s">
+      <c r="E151" s="15" t="s">
         <v>530</v>
       </c>
-      <c r="F151" s="17" t="s">
+      <c r="F151" s="15" t="s">
         <v>531</v>
       </c>
-      <c r="G151" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H151" s="17" t="s">
+      <c r="G151" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H151" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I151" s="18"/>
+      <c r="I151" s="16"/>
     </row>
     <row r="152" spans="1:9">
-      <c r="A152" s="15" t="s">
+      <c r="A152" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="B152" s="16">
+      <c r="B152" s="14">
         <v>14</v>
       </c>
-      <c r="C152" s="17" t="s">
+      <c r="C152" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D152" s="17" t="s">
+      <c r="D152" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="E152" s="17" t="s">
+      <c r="E152" s="15" t="s">
         <v>533</v>
       </c>
-      <c r="F152" s="17" t="s">
+      <c r="F152" s="15" t="s">
         <v>534</v>
       </c>
-      <c r="G152" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H152" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I152" s="18"/>
+      <c r="G152" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H152" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I152" s="16"/>
     </row>
     <row r="153" spans="1:9">
-      <c r="A153" s="15" t="s">
+      <c r="A153" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="B153" s="16">
+      <c r="B153" s="14">
         <v>14</v>
       </c>
-      <c r="C153" s="17" t="s">
+      <c r="C153" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D153" s="17" t="s">
+      <c r="D153" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="E153" s="17" t="s">
+      <c r="E153" s="15" t="s">
         <v>536</v>
       </c>
-      <c r="F153" s="17" t="s">
+      <c r="F153" s="15" t="s">
         <v>506</v>
       </c>
-      <c r="G153" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H153" s="17" t="s">
+      <c r="G153" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H153" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I153" s="18"/>
+      <c r="I153" s="16"/>
     </row>
     <row r="154" spans="1:9">
-      <c r="A154" s="15" t="s">
+      <c r="A154" s="13" t="s">
         <v>537</v>
       </c>
-      <c r="B154" s="16">
+      <c r="B154" s="14">
         <v>14</v>
       </c>
-      <c r="C154" s="17" t="s">
+      <c r="C154" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D154" s="17" t="s">
+      <c r="D154" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="E154" s="17" t="s">
+      <c r="E154" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="F154" s="17" t="s">
+      <c r="F154" s="15" t="s">
         <v>539</v>
       </c>
-      <c r="G154" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H154" s="17" t="s">
+      <c r="G154" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H154" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I154" s="18"/>
+      <c r="I154" s="16"/>
     </row>
     <row r="155" spans="1:9">
-      <c r="A155" s="15" t="s">
+      <c r="A155" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="B155" s="16">
+      <c r="B155" s="14">
         <v>14</v>
       </c>
-      <c r="C155" s="17" t="s">
+      <c r="C155" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D155" s="17" t="s">
+      <c r="D155" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E155" s="17" t="s">
+      <c r="E155" s="15" t="s">
         <v>541</v>
       </c>
-      <c r="F155" s="17" t="s">
+      <c r="F155" s="15" t="s">
         <v>542</v>
       </c>
-      <c r="G155" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H155" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I155" s="18"/>
+      <c r="G155" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H155" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I155" s="16"/>
     </row>
     <row r="156" spans="1:9">
-      <c r="A156" s="15" t="s">
+      <c r="A156" s="13" t="s">
         <v>543</v>
       </c>
-      <c r="B156" s="16">
+      <c r="B156" s="14">
         <v>14</v>
       </c>
-      <c r="C156" s="17" t="s">
+      <c r="C156" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D156" s="17" t="s">
+      <c r="D156" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E156" s="17" t="s">
+      <c r="E156" s="15" t="s">
         <v>544</v>
       </c>
-      <c r="F156" s="17" t="s">
+      <c r="F156" s="15" t="s">
         <v>545</v>
       </c>
-      <c r="G156" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H156" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I156" s="18"/>
+      <c r="G156" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H156" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I156" s="16"/>
     </row>
     <row r="157" spans="1:9">
-      <c r="A157" s="15" t="s">
+      <c r="A157" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="B157" s="16">
+      <c r="B157" s="14">
         <v>15</v>
       </c>
-      <c r="C157" s="17" t="s">
+      <c r="C157" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D157" s="17" t="s">
+      <c r="D157" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="E157" s="17" t="s">
+      <c r="E157" s="15" t="s">
         <v>548</v>
       </c>
-      <c r="F157" s="17" t="s">
+      <c r="F157" s="15" t="s">
         <v>549</v>
       </c>
-      <c r="G157" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H157" s="17" t="s">
+      <c r="G157" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H157" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I157" s="18"/>
+      <c r="I157" s="16"/>
     </row>
     <row r="158" spans="1:9">
-      <c r="A158" s="15" t="s">
+      <c r="A158" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="B158" s="16">
+      <c r="B158" s="14">
         <v>15</v>
       </c>
-      <c r="C158" s="17" t="s">
+      <c r="C158" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D158" s="17" t="s">
+      <c r="D158" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="E158" s="17" t="s">
+      <c r="E158" s="15" t="s">
         <v>551</v>
       </c>
-      <c r="F158" s="17" t="s">
+      <c r="F158" s="15" t="s">
         <v>552</v>
       </c>
-      <c r="G158" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H158" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I158" s="18"/>
+      <c r="G158" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H158" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I158" s="16"/>
     </row>
     <row r="159" spans="1:9" ht="28.3">
-      <c r="A159" s="15" t="s">
+      <c r="A159" s="13" t="s">
         <v>553</v>
       </c>
-      <c r="B159" s="16">
+      <c r="B159" s="14">
         <v>15</v>
       </c>
-      <c r="C159" s="17" t="s">
+      <c r="C159" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D159" s="17" t="s">
+      <c r="D159" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="E159" s="17" t="s">
+      <c r="E159" s="15" t="s">
         <v>554</v>
       </c>
-      <c r="F159" s="17" t="s">
+      <c r="F159" s="15" t="s">
         <v>555</v>
       </c>
-      <c r="G159" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H159" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I159" s="18"/>
+      <c r="G159" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H159" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I159" s="16"/>
     </row>
     <row r="160" spans="1:9" ht="28.3">
-      <c r="A160" s="15" t="s">
+      <c r="A160" s="13" t="s">
         <v>556</v>
       </c>
-      <c r="B160" s="16">
+      <c r="B160" s="14">
         <v>15</v>
       </c>
-      <c r="C160" s="17" t="s">
+      <c r="C160" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D160" s="17" t="s">
+      <c r="D160" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="E160" s="17" t="s">
+      <c r="E160" s="15" t="s">
         <v>557</v>
       </c>
-      <c r="F160" s="17" t="s">
+      <c r="F160" s="15" t="s">
         <v>558</v>
       </c>
-      <c r="G160" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H160" s="17" t="s">
+      <c r="G160" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H160" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I160" s="18"/>
+      <c r="I160" s="16"/>
     </row>
     <row r="161" spans="1:9">
-      <c r="A161" s="15" t="s">
+      <c r="A161" s="13" t="s">
         <v>559</v>
       </c>
-      <c r="B161" s="16">
+      <c r="B161" s="14">
         <v>15</v>
       </c>
-      <c r="C161" s="17" t="s">
+      <c r="C161" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D161" s="17" t="s">
+      <c r="D161" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="E161" s="17" t="s">
+      <c r="E161" s="15" t="s">
         <v>560</v>
       </c>
-      <c r="F161" s="17" t="s">
+      <c r="F161" s="15" t="s">
         <v>561</v>
       </c>
-      <c r="G161" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H161" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I161" s="18"/>
+      <c r="G161" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H161" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I161" s="16"/>
     </row>
     <row r="162" spans="1:9">
-      <c r="A162" s="15" t="s">
+      <c r="A162" s="13" t="s">
         <v>562</v>
       </c>
-      <c r="B162" s="16">
+      <c r="B162" s="14">
         <v>15</v>
       </c>
-      <c r="C162" s="17" t="s">
+      <c r="C162" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D162" s="17" t="s">
+      <c r="D162" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="E162" s="17" t="s">
+      <c r="E162" s="15" t="s">
         <v>563</v>
       </c>
-      <c r="F162" s="17" t="s">
+      <c r="F162" s="15" t="s">
         <v>564</v>
       </c>
-      <c r="G162" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H162" s="17" t="s">
+      <c r="G162" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H162" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I162" s="18"/>
+      <c r="I162" s="16"/>
     </row>
     <row r="163" spans="1:9">
-      <c r="A163" s="15" t="s">
+      <c r="A163" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="B163" s="16">
+      <c r="B163" s="14">
         <v>15</v>
       </c>
-      <c r="C163" s="17" t="s">
+      <c r="C163" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D163" s="17" t="s">
+      <c r="D163" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E163" s="17" t="s">
+      <c r="E163" s="15" t="s">
         <v>566</v>
       </c>
-      <c r="F163" s="17" t="s">
+      <c r="F163" s="15" t="s">
         <v>567</v>
       </c>
-      <c r="G163" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H163" s="17" t="s">
+      <c r="G163" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H163" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I163" s="18"/>
+      <c r="I163" s="16"/>
     </row>
     <row r="164" spans="1:9">
-      <c r="A164" s="15" t="s">
+      <c r="A164" s="13" t="s">
         <v>568</v>
       </c>
-      <c r="B164" s="16">
+      <c r="B164" s="14">
         <v>15</v>
       </c>
-      <c r="C164" s="17" t="s">
+      <c r="C164" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D164" s="17" t="s">
+      <c r="D164" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E164" s="17" t="s">
+      <c r="E164" s="15" t="s">
         <v>569</v>
       </c>
-      <c r="F164" s="17" t="s">
+      <c r="F164" s="15" t="s">
         <v>570</v>
       </c>
-      <c r="G164" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H164" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I164" s="18"/>
+      <c r="G164" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H164" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I164" s="16"/>
     </row>
     <row r="165" spans="1:9">
-      <c r="A165" s="15" t="s">
+      <c r="A165" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="B165" s="16">
+      <c r="B165" s="14">
         <v>15</v>
       </c>
-      <c r="C165" s="17" t="s">
+      <c r="C165" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D165" s="17" t="s">
+      <c r="D165" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E165" s="17" t="s">
+      <c r="E165" s="15" t="s">
         <v>572</v>
       </c>
-      <c r="F165" s="17" t="s">
+      <c r="F165" s="15" t="s">
         <v>573</v>
       </c>
-      <c r="G165" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H165" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I165" s="18"/>
+      <c r="G165" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H165" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I165" s="16"/>
     </row>
     <row r="166" spans="1:9">
-      <c r="A166" s="15" t="s">
+      <c r="A166" s="13" t="s">
         <v>574</v>
       </c>
-      <c r="B166" s="16">
+      <c r="B166" s="14">
         <v>16</v>
       </c>
-      <c r="C166" s="17" t="s">
+      <c r="C166" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D166" s="17" t="s">
+      <c r="D166" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E166" s="17" t="s">
+      <c r="E166" s="15" t="s">
         <v>575</v>
       </c>
-      <c r="F166" s="17" t="s">
+      <c r="F166" s="15" t="s">
         <v>576</v>
       </c>
-      <c r="G166" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H166" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I166" s="18"/>
+      <c r="G166" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H166" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I166" s="16"/>
     </row>
     <row r="167" spans="1:9">
-      <c r="A167" s="15" t="s">
+      <c r="A167" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="B167" s="16">
+      <c r="B167" s="14">
         <v>16</v>
       </c>
-      <c r="C167" s="17" t="s">
+      <c r="C167" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D167" s="17" t="s">
+      <c r="D167" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E167" s="17" t="s">
+      <c r="E167" s="15" t="s">
         <v>578</v>
       </c>
-      <c r="F167" s="17" t="s">
+      <c r="F167" s="15" t="s">
         <v>579</v>
       </c>
-      <c r="G167" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H167" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I167" s="18"/>
+      <c r="G167" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H167" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I167" s="16"/>
     </row>
     <row r="168" spans="1:9">
-      <c r="A168" s="15" t="s">
+      <c r="A168" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="B168" s="16">
+      <c r="B168" s="14">
         <v>16</v>
       </c>
-      <c r="C168" s="17" t="s">
+      <c r="C168" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D168" s="17" t="s">
+      <c r="D168" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E168" s="17" t="s">
+      <c r="E168" s="15" t="s">
         <v>581</v>
       </c>
-      <c r="F168" s="17" t="s">
+      <c r="F168" s="15" t="s">
         <v>582</v>
       </c>
-      <c r="G168" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H168" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I168" s="18"/>
+      <c r="G168" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H168" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I168" s="16"/>
     </row>
     <row r="169" spans="1:9" ht="28.3">
-      <c r="A169" s="15" t="s">
+      <c r="A169" s="13" t="s">
         <v>583</v>
       </c>
-      <c r="B169" s="16">
+      <c r="B169" s="14">
         <v>16</v>
       </c>
-      <c r="C169" s="17" t="s">
+      <c r="C169" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D169" s="17" t="s">
+      <c r="D169" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E169" s="17" t="s">
+      <c r="E169" s="15" t="s">
         <v>584</v>
       </c>
-      <c r="F169" s="17" t="s">
+      <c r="F169" s="15" t="s">
         <v>585</v>
       </c>
-      <c r="G169" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H169" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I169" s="18"/>
+      <c r="G169" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H169" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I169" s="16"/>
     </row>
     <row r="170" spans="1:9" ht="28.3">
-      <c r="A170" s="15" t="s">
+      <c r="A170" s="13" t="s">
         <v>586</v>
       </c>
-      <c r="B170" s="16">
+      <c r="B170" s="14">
         <v>16</v>
       </c>
-      <c r="C170" s="17" t="s">
+      <c r="C170" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D170" s="17" t="s">
+      <c r="D170" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E170" s="17" t="s">
+      <c r="E170" s="15" t="s">
         <v>587</v>
       </c>
-      <c r="F170" s="17" t="s">
+      <c r="F170" s="15" t="s">
         <v>588</v>
       </c>
-      <c r="G170" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H170" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I170" s="18"/>
+      <c r="G170" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H170" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I170" s="16"/>
     </row>
     <row r="171" spans="1:9">
-      <c r="A171" s="15" t="s">
+      <c r="A171" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="B171" s="16">
+      <c r="B171" s="14">
         <v>16</v>
       </c>
-      <c r="C171" s="17" t="s">
+      <c r="C171" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D171" s="17" t="s">
+      <c r="D171" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E171" s="17" t="s">
+      <c r="E171" s="15" t="s">
         <v>590</v>
       </c>
-      <c r="F171" s="17" t="s">
+      <c r="F171" s="15" t="s">
         <v>591</v>
       </c>
-      <c r="G171" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H171" s="17" t="s">
+      <c r="G171" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H171" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I171" s="18"/>
+      <c r="I171" s="16"/>
     </row>
     <row r="172" spans="1:9" ht="28.3">
-      <c r="A172" s="15" t="s">
+      <c r="A172" s="13" t="s">
         <v>592</v>
       </c>
-      <c r="B172" s="16">
+      <c r="B172" s="14">
         <v>16</v>
       </c>
-      <c r="C172" s="17" t="s">
+      <c r="C172" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D172" s="17" t="s">
+      <c r="D172" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E172" s="17" t="s">
+      <c r="E172" s="15" t="s">
         <v>593</v>
       </c>
-      <c r="F172" s="17" t="s">
+      <c r="F172" s="15" t="s">
         <v>594</v>
       </c>
-      <c r="G172" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H172" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I172" s="18"/>
+      <c r="G172" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H172" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I172" s="16"/>
     </row>
     <row r="173" spans="1:9" ht="28.3">
-      <c r="A173" s="15" t="s">
+      <c r="A173" s="13" t="s">
         <v>595</v>
       </c>
-      <c r="B173" s="16">
+      <c r="B173" s="14">
         <v>16</v>
       </c>
-      <c r="C173" s="17" t="s">
+      <c r="C173" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D173" s="17" t="s">
+      <c r="D173" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E173" s="17" t="s">
+      <c r="E173" s="15" t="s">
         <v>596</v>
       </c>
-      <c r="F173" s="17" t="s">
+      <c r="F173" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="G173" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H173" s="17" t="s">
+      <c r="G173" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H173" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I173" s="18"/>
+      <c r="I173" s="16"/>
     </row>
     <row r="174" spans="1:9">
-      <c r="A174" s="15" t="s">
+      <c r="A174" s="13" t="s">
         <v>598</v>
       </c>
-      <c r="B174" s="16">
+      <c r="B174" s="14">
         <v>16</v>
       </c>
-      <c r="C174" s="17" t="s">
+      <c r="C174" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D174" s="17" t="s">
+      <c r="D174" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E174" s="17" t="s">
+      <c r="E174" s="15" t="s">
         <v>599</v>
       </c>
-      <c r="F174" s="17" t="s">
+      <c r="F174" s="15" t="s">
         <v>600</v>
       </c>
-      <c r="G174" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H174" s="17" t="s">
+      <c r="G174" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H174" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I174" s="18"/>
+      <c r="I174" s="16"/>
     </row>
     <row r="175" spans="1:9">
-      <c r="A175" s="15" t="s">
+      <c r="A175" s="13" t="s">
         <v>601</v>
       </c>
-      <c r="B175" s="16">
+      <c r="B175" s="14">
         <v>16</v>
       </c>
-      <c r="C175" s="17" t="s">
+      <c r="C175" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D175" s="17" t="s">
+      <c r="D175" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E175" s="17" t="s">
+      <c r="E175" s="15" t="s">
         <v>602</v>
       </c>
-      <c r="F175" s="17" t="s">
+      <c r="F175" s="15" t="s">
         <v>603</v>
       </c>
-      <c r="G175" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H175" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I175" s="18"/>
+      <c r="G175" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H175" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I175" s="16"/>
     </row>
     <row r="176" spans="1:9">
-      <c r="A176" s="15" t="s">
+      <c r="A176" s="13" t="s">
         <v>604</v>
       </c>
-      <c r="B176" s="16">
+      <c r="B176" s="14">
         <v>17</v>
       </c>
-      <c r="C176" s="17" t="s">
+      <c r="C176" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D176" s="17" t="s">
+      <c r="D176" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="E176" s="17" t="s">
+      <c r="E176" s="15" t="s">
         <v>605</v>
       </c>
-      <c r="F176" s="17" t="s">
+      <c r="F176" s="15" t="s">
         <v>606</v>
       </c>
-      <c r="G176" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H176" s="17" t="s">
+      <c r="G176" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H176" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I176" s="18"/>
+      <c r="I176" s="16"/>
     </row>
     <row r="177" spans="1:9">
-      <c r="A177" s="15" t="s">
+      <c r="A177" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="B177" s="16">
+      <c r="B177" s="14">
         <v>17</v>
       </c>
-      <c r="C177" s="17" t="s">
+      <c r="C177" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="17" t="s">
+      <c r="D177" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E177" s="17" t="s">
+      <c r="E177" s="15" t="s">
         <v>608</v>
       </c>
-      <c r="F177" s="17" t="s">
+      <c r="F177" s="15" t="s">
         <v>609</v>
       </c>
-      <c r="G177" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H177" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I177" s="18"/>
+      <c r="G177" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H177" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I177" s="16"/>
     </row>
     <row r="178" spans="1:9" ht="28.3">
-      <c r="A178" s="15" t="s">
+      <c r="A178" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="B178" s="16">
+      <c r="B178" s="14">
         <v>17</v>
       </c>
-      <c r="C178" s="17" t="s">
+      <c r="C178" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D178" s="17" t="s">
+      <c r="D178" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E178" s="17" t="s">
+      <c r="E178" s="15" t="s">
         <v>611</v>
       </c>
-      <c r="F178" s="17" t="s">
+      <c r="F178" s="15" t="s">
         <v>612</v>
       </c>
-      <c r="G178" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H178" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I178" s="18"/>
+      <c r="G178" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H178" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I178" s="16"/>
     </row>
     <row r="179" spans="1:9">
-      <c r="A179" s="15" t="s">
+      <c r="A179" s="13" t="s">
         <v>613</v>
       </c>
-      <c r="B179" s="16">
+      <c r="B179" s="14">
         <v>17</v>
       </c>
-      <c r="C179" s="17" t="s">
+      <c r="C179" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D179" s="17" t="s">
+      <c r="D179" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E179" s="17" t="s">
+      <c r="E179" s="15" t="s">
         <v>614</v>
       </c>
-      <c r="F179" s="17" t="s">
+      <c r="F179" s="15" t="s">
         <v>615</v>
       </c>
-      <c r="G179" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H179" s="17" t="s">
+      <c r="G179" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H179" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I179" s="18"/>
+      <c r="I179" s="16"/>
     </row>
     <row r="180" spans="1:9">
-      <c r="A180" s="15" t="s">
+      <c r="A180" s="13" t="s">
         <v>616</v>
       </c>
-      <c r="B180" s="16">
+      <c r="B180" s="14">
         <v>17</v>
       </c>
-      <c r="C180" s="17" t="s">
+      <c r="C180" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D180" s="17" t="s">
+      <c r="D180" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="E180" s="17" t="s">
+      <c r="E180" s="15" t="s">
         <v>617</v>
       </c>
-      <c r="F180" s="17" t="s">
+      <c r="F180" s="15" t="s">
         <v>618</v>
       </c>
-      <c r="G180" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H180" s="17" t="s">
+      <c r="G180" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H180" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I180" s="18"/>
+      <c r="I180" s="16"/>
     </row>
     <row r="181" spans="1:9" ht="28.3">
-      <c r="A181" s="15" t="s">
+      <c r="A181" s="13" t="s">
         <v>619</v>
       </c>
-      <c r="B181" s="16">
+      <c r="B181" s="14">
         <v>17</v>
       </c>
-      <c r="C181" s="17" t="s">
+      <c r="C181" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D181" s="17" t="s">
+      <c r="D181" s="15" t="s">
         <v>620</v>
       </c>
-      <c r="E181" s="17" t="s">
+      <c r="E181" s="15" t="s">
         <v>621</v>
       </c>
-      <c r="F181" s="17" t="s">
+      <c r="F181" s="15" t="s">
         <v>622</v>
       </c>
-      <c r="G181" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H181" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I181" s="18"/>
+      <c r="G181" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H181" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I181" s="16"/>
     </row>
     <row r="182" spans="1:9" ht="28.3">
-      <c r="A182" s="15" t="s">
+      <c r="A182" s="13" t="s">
         <v>623</v>
       </c>
-      <c r="B182" s="16">
+      <c r="B182" s="14">
         <v>17</v>
       </c>
-      <c r="C182" s="17" t="s">
+      <c r="C182" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D182" s="17" t="s">
+      <c r="D182" s="15" t="s">
         <v>624</v>
       </c>
-      <c r="E182" s="17" t="s">
+      <c r="E182" s="15" t="s">
         <v>625</v>
       </c>
-      <c r="F182" s="17" t="s">
+      <c r="F182" s="15" t="s">
         <v>626</v>
       </c>
-      <c r="G182" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H182" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I182" s="18"/>
+      <c r="G182" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H182" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I182" s="16"/>
     </row>
     <row r="183" spans="1:9">
-      <c r="A183" s="15" t="s">
+      <c r="A183" s="13" t="s">
         <v>627</v>
       </c>
-      <c r="B183" s="16">
+      <c r="B183" s="14">
         <v>17</v>
       </c>
-      <c r="C183" s="17" t="s">
+      <c r="C183" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D183" s="17" t="s">
+      <c r="D183" s="15" t="s">
         <v>624</v>
       </c>
-      <c r="E183" s="17" t="s">
+      <c r="E183" s="15" t="s">
         <v>628</v>
       </c>
-      <c r="F183" s="17" t="s">
+      <c r="F183" s="15" t="s">
         <v>629</v>
       </c>
-      <c r="G183" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H183" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I183" s="18"/>
+      <c r="G183" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H183" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I183" s="16"/>
     </row>
     <row r="184" spans="1:9" ht="28.3">
-      <c r="A184" s="15" t="s">
+      <c r="A184" s="13" t="s">
         <v>630</v>
       </c>
-      <c r="B184" s="16">
+      <c r="B184" s="14">
         <v>17</v>
       </c>
-      <c r="C184" s="17" t="s">
+      <c r="C184" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D184" s="17" t="s">
+      <c r="D184" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="E184" s="17" t="s">
+      <c r="E184" s="15" t="s">
         <v>631</v>
       </c>
-      <c r="F184" s="17" t="s">
+      <c r="F184" s="15" t="s">
         <v>632</v>
       </c>
-      <c r="G184" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H184" s="17" t="s">
+      <c r="G184" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H184" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I184" s="18"/>
+      <c r="I184" s="16"/>
     </row>
     <row r="185" spans="1:9">
-      <c r="A185" s="15" t="s">
+      <c r="A185" s="13" t="s">
         <v>633</v>
       </c>
-      <c r="B185" s="16">
+      <c r="B185" s="14">
         <v>17</v>
       </c>
-      <c r="C185" s="17" t="s">
+      <c r="C185" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D185" s="17" t="s">
+      <c r="D185" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E185" s="17" t="s">
+      <c r="E185" s="15" t="s">
         <v>634</v>
       </c>
-      <c r="F185" s="17" t="s">
+      <c r="F185" s="15" t="s">
         <v>635</v>
       </c>
-      <c r="G185" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H185" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I185" s="18"/>
+      <c r="G185" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H185" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I185" s="16"/>
     </row>
     <row r="186" spans="1:9" ht="28.3">
-      <c r="A186" s="15" t="s">
+      <c r="A186" s="13" t="s">
         <v>636</v>
       </c>
-      <c r="B186" s="16">
+      <c r="B186" s="14">
         <v>18</v>
       </c>
-      <c r="C186" s="17" t="s">
+      <c r="C186" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D186" s="17" t="s">
+      <c r="D186" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="E186" s="17" t="s">
+      <c r="E186" s="15" t="s">
         <v>637</v>
       </c>
-      <c r="F186" s="17" t="s">
+      <c r="F186" s="15" t="s">
         <v>638</v>
       </c>
-      <c r="G186" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H186" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I186" s="18"/>
+      <c r="G186" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H186" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I186" s="16"/>
     </row>
     <row r="187" spans="1:9" ht="28.3">
-      <c r="A187" s="15" t="s">
+      <c r="A187" s="13" t="s">
         <v>639</v>
       </c>
-      <c r="B187" s="16">
+      <c r="B187" s="14">
         <v>18</v>
       </c>
-      <c r="C187" s="17" t="s">
+      <c r="C187" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D187" s="17" t="s">
+      <c r="D187" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="E187" s="17" t="s">
+      <c r="E187" s="15" t="s">
         <v>640</v>
       </c>
-      <c r="F187" s="17" t="s">
+      <c r="F187" s="15" t="s">
         <v>641</v>
       </c>
-      <c r="G187" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H187" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I187" s="18"/>
+      <c r="G187" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H187" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I187" s="16"/>
     </row>
     <row r="188" spans="1:9" ht="28.3">
-      <c r="A188" s="15" t="s">
+      <c r="A188" s="13" t="s">
         <v>642</v>
       </c>
-      <c r="B188" s="16">
+      <c r="B188" s="14">
         <v>18</v>
       </c>
-      <c r="C188" s="17" t="s">
+      <c r="C188" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D188" s="17" t="s">
+      <c r="D188" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E188" s="17" t="s">
+      <c r="E188" s="15" t="s">
         <v>643</v>
       </c>
-      <c r="F188" s="17" t="s">
+      <c r="F188" s="15" t="s">
         <v>644</v>
       </c>
-      <c r="G188" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H188" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I188" s="18"/>
+      <c r="G188" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H188" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I188" s="16"/>
     </row>
     <row r="189" spans="1:9">
-      <c r="A189" s="15" t="s">
+      <c r="A189" s="13" t="s">
         <v>645</v>
       </c>
-      <c r="B189" s="16">
+      <c r="B189" s="14">
         <v>18</v>
       </c>
-      <c r="C189" s="17" t="s">
+      <c r="C189" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D189" s="17" t="s">
+      <c r="D189" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E189" s="17" t="s">
+      <c r="E189" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="F189" s="17" t="s">
+      <c r="F189" s="15" t="s">
         <v>647</v>
       </c>
-      <c r="G189" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H189" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I189" s="18"/>
+      <c r="G189" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H189" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I189" s="16"/>
     </row>
     <row r="190" spans="1:9">
-      <c r="A190" s="15" t="s">
+      <c r="A190" s="13" t="s">
         <v>648</v>
       </c>
-      <c r="B190" s="16">
+      <c r="B190" s="14">
         <v>18</v>
       </c>
-      <c r="C190" s="17" t="s">
+      <c r="C190" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D190" s="17" t="s">
+      <c r="D190" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="E190" s="17" t="s">
+      <c r="E190" s="15" t="s">
         <v>649</v>
       </c>
-      <c r="F190" s="17" t="s">
+      <c r="F190" s="15" t="s">
         <v>650</v>
       </c>
-      <c r="G190" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H190" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I190" s="18"/>
+      <c r="G190" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H190" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I190" s="16"/>
     </row>
     <row r="191" spans="1:9" ht="28.3">
-      <c r="A191" s="15" t="s">
+      <c r="A191" s="13" t="s">
         <v>651</v>
       </c>
-      <c r="B191" s="16">
+      <c r="B191" s="14">
         <v>18</v>
       </c>
-      <c r="C191" s="17" t="s">
+      <c r="C191" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D191" s="17" t="s">
+      <c r="D191" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="E191" s="17" t="s">
+      <c r="E191" s="15" t="s">
         <v>652</v>
       </c>
-      <c r="F191" s="17" t="s">
+      <c r="F191" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="G191" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H191" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I191" s="18"/>
+      <c r="G191" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H191" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I191" s="16"/>
     </row>
     <row r="192" spans="1:9" ht="28.3">
-      <c r="A192" s="15" t="s">
+      <c r="A192" s="13" t="s">
         <v>653</v>
       </c>
-      <c r="B192" s="16">
+      <c r="B192" s="14">
         <v>18</v>
       </c>
-      <c r="C192" s="17" t="s">
+      <c r="C192" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D192" s="17" t="s">
+      <c r="D192" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E192" s="17" t="s">
+      <c r="E192" s="15" t="s">
         <v>654</v>
       </c>
-      <c r="F192" s="17" t="s">
+      <c r="F192" s="15" t="s">
         <v>655</v>
       </c>
-      <c r="G192" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H192" s="17" t="s">
+      <c r="G192" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H192" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I192" s="18"/>
+      <c r="I192" s="16"/>
     </row>
     <row r="193" spans="1:9" ht="28.3">
-      <c r="A193" s="15" t="s">
+      <c r="A193" s="13" t="s">
         <v>656</v>
       </c>
-      <c r="B193" s="16">
+      <c r="B193" s="14">
         <v>18</v>
       </c>
-      <c r="C193" s="17" t="s">
+      <c r="C193" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D193" s="17" t="s">
+      <c r="D193" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="E193" s="17" t="s">
+      <c r="E193" s="15" t="s">
         <v>657</v>
       </c>
-      <c r="F193" s="17" t="s">
+      <c r="F193" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="G193" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H193" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I193" s="18"/>
+      <c r="G193" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H193" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I193" s="16"/>
     </row>
     <row r="194" spans="1:9">
-      <c r="A194" s="15" t="s">
+      <c r="A194" s="13" t="s">
         <v>658</v>
       </c>
-      <c r="B194" s="16">
+      <c r="B194" s="14">
         <v>18</v>
       </c>
-      <c r="C194" s="17" t="s">
+      <c r="C194" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D194" s="17" t="s">
+      <c r="D194" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E194" s="17" t="s">
+      <c r="E194" s="15" t="s">
         <v>659</v>
       </c>
-      <c r="F194" s="17" t="s">
+      <c r="F194" s="15" t="s">
         <v>660</v>
       </c>
-      <c r="G194" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H194" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I194" s="18"/>
+      <c r="G194" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H194" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I194" s="16"/>
     </row>
     <row r="195" spans="1:9" ht="28.3">
-      <c r="A195" s="15" t="s">
+      <c r="A195" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="B195" s="16">
+      <c r="B195" s="14">
         <v>19</v>
       </c>
-      <c r="C195" s="17" t="s">
+      <c r="C195" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D195" s="17" t="s">
+      <c r="D195" s="15" t="s">
         <v>662</v>
       </c>
-      <c r="E195" s="17" t="s">
+      <c r="E195" s="15" t="s">
         <v>663</v>
       </c>
-      <c r="F195" s="17" t="s">
+      <c r="F195" s="15" t="s">
         <v>664</v>
       </c>
-      <c r="G195" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H195" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I195" s="18"/>
+      <c r="G195" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H195" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I195" s="16"/>
     </row>
     <row r="196" spans="1:9" ht="28.3">
-      <c r="A196" s="15" t="s">
+      <c r="A196" s="13" t="s">
         <v>665</v>
       </c>
-      <c r="B196" s="16">
+      <c r="B196" s="14">
         <v>19</v>
       </c>
-      <c r="C196" s="17" t="s">
+      <c r="C196" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D196" s="17" t="s">
+      <c r="D196" s="15" t="s">
         <v>662</v>
       </c>
-      <c r="E196" s="17" t="s">
+      <c r="E196" s="15" t="s">
         <v>666</v>
       </c>
-      <c r="F196" s="17" t="s">
+      <c r="F196" s="15" t="s">
         <v>667</v>
       </c>
-      <c r="G196" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H196" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I196" s="18"/>
+      <c r="G196" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H196" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I196" s="16"/>
     </row>
     <row r="197" spans="1:9">
-      <c r="A197" s="15" t="s">
+      <c r="A197" s="13" t="s">
         <v>668</v>
       </c>
-      <c r="B197" s="16">
+      <c r="B197" s="14">
         <v>19</v>
       </c>
-      <c r="C197" s="17" t="s">
+      <c r="C197" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D197" s="17" t="s">
+      <c r="D197" s="15" t="s">
         <v>662</v>
       </c>
-      <c r="E197" s="17" t="s">
+      <c r="E197" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="F197" s="17" t="s">
+      <c r="F197" s="15" t="s">
         <v>670</v>
       </c>
-      <c r="G197" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H197" s="17" t="s">
+      <c r="G197" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H197" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I197" s="18"/>
+      <c r="I197" s="16"/>
     </row>
     <row r="198" spans="1:9" ht="28.3">
-      <c r="A198" s="15" t="s">
+      <c r="A198" s="13" t="s">
         <v>671</v>
       </c>
-      <c r="B198" s="16">
+      <c r="B198" s="14">
         <v>19</v>
       </c>
-      <c r="C198" s="17" t="s">
+      <c r="C198" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D198" s="17" t="s">
+      <c r="D198" s="15" t="s">
         <v>662</v>
       </c>
-      <c r="E198" s="17" t="s">
+      <c r="E198" s="15" t="s">
         <v>672</v>
       </c>
-      <c r="F198" s="17" t="s">
+      <c r="F198" s="15" t="s">
         <v>673</v>
       </c>
-      <c r="G198" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H198" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I198" s="18"/>
+      <c r="G198" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H198" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I198" s="16"/>
     </row>
     <row r="199" spans="1:9">
-      <c r="A199" s="15" t="s">
+      <c r="A199" s="13" t="s">
         <v>674</v>
       </c>
-      <c r="B199" s="16">
+      <c r="B199" s="14">
         <v>19</v>
       </c>
-      <c r="C199" s="17" t="s">
+      <c r="C199" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D199" s="17" t="s">
+      <c r="D199" s="15" t="s">
         <v>662</v>
       </c>
-      <c r="E199" s="17" t="s">
+      <c r="E199" s="15" t="s">
         <v>675</v>
       </c>
-      <c r="F199" s="17" t="s">
+      <c r="F199" s="15" t="s">
         <v>676</v>
       </c>
-      <c r="G199" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H199" s="17" t="s">
+      <c r="G199" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H199" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I199" s="18"/>
+      <c r="I199" s="16"/>
     </row>
     <row r="200" spans="1:9" ht="28.3">
-      <c r="A200" s="15" t="s">
+      <c r="A200" s="13" t="s">
         <v>677</v>
       </c>
-      <c r="B200" s="16">
+      <c r="B200" s="14">
         <v>19</v>
       </c>
-      <c r="C200" s="17" t="s">
+      <c r="C200" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D200" s="17" t="s">
+      <c r="D200" s="15" t="s">
         <v>678</v>
       </c>
-      <c r="E200" s="17" t="s">
+      <c r="E200" s="15" t="s">
         <v>679</v>
       </c>
-      <c r="F200" s="17" t="s">
+      <c r="F200" s="15" t="s">
         <v>680</v>
       </c>
-      <c r="G200" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H200" s="17" t="s">
+      <c r="G200" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H200" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I200" s="18"/>
+      <c r="I200" s="16"/>
     </row>
     <row r="201" spans="1:9" ht="28.3">
-      <c r="A201" s="15" t="s">
+      <c r="A201" s="13" t="s">
         <v>681</v>
       </c>
-      <c r="B201" s="16">
+      <c r="B201" s="14">
         <v>19</v>
       </c>
-      <c r="C201" s="17" t="s">
+      <c r="C201" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D201" s="17" t="s">
+      <c r="D201" s="15" t="s">
         <v>682</v>
       </c>
-      <c r="E201" s="17" t="s">
+      <c r="E201" s="15" t="s">
         <v>683</v>
       </c>
-      <c r="F201" s="17" t="s">
+      <c r="F201" s="15" t="s">
         <v>684</v>
       </c>
-      <c r="G201" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H201" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I201" s="18"/>
+      <c r="G201" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H201" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I201" s="16"/>
     </row>
     <row r="202" spans="1:9">
-      <c r="A202" s="15" t="s">
+      <c r="A202" s="13" t="s">
         <v>685</v>
       </c>
-      <c r="B202" s="16">
+      <c r="B202" s="14">
         <v>19</v>
       </c>
-      <c r="C202" s="17" t="s">
+      <c r="C202" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D202" s="17" t="s">
+      <c r="D202" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="E202" s="17" t="s">
+      <c r="E202" s="15" t="s">
         <v>686</v>
       </c>
-      <c r="F202" s="17" t="s">
+      <c r="F202" s="15" t="s">
         <v>687</v>
       </c>
-      <c r="G202" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H202" s="17" t="s">
+      <c r="G202" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H202" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I202" s="18"/>
+      <c r="I202" s="16"/>
     </row>
     <row r="203" spans="1:9" ht="28.3">
-      <c r="A203" s="15" t="s">
+      <c r="A203" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="B203" s="16">
+      <c r="B203" s="14">
         <v>19</v>
       </c>
-      <c r="C203" s="17" t="s">
+      <c r="C203" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D203" s="17" t="s">
+      <c r="D203" s="15" t="s">
         <v>689</v>
       </c>
-      <c r="E203" s="17" t="s">
+      <c r="E203" s="15" t="s">
         <v>690</v>
       </c>
-      <c r="F203" s="17" t="s">
+      <c r="F203" s="15" t="s">
         <v>691</v>
       </c>
-      <c r="G203" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H203" s="17" t="s">
+      <c r="G203" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H203" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I203" s="18"/>
+      <c r="I203" s="16"/>
     </row>
     <row r="204" spans="1:9" ht="28.3">
-      <c r="A204" s="15" t="s">
+      <c r="A204" s="13" t="s">
         <v>692</v>
       </c>
-      <c r="B204" s="16">
+      <c r="B204" s="14">
         <v>19</v>
       </c>
-      <c r="C204" s="17" t="s">
+      <c r="C204" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D204" s="17" t="s">
+      <c r="D204" s="15" t="s">
         <v>693</v>
       </c>
-      <c r="E204" s="17" t="s">
+      <c r="E204" s="15" t="s">
         <v>694</v>
       </c>
-      <c r="F204" s="17" t="s">
+      <c r="F204" s="15" t="s">
         <v>695</v>
       </c>
-      <c r="G204" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H204" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I204" s="18"/>
+      <c r="G204" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H204" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I204" s="16"/>
     </row>
     <row r="205" spans="1:9" ht="28.3">
-      <c r="A205" s="15" t="s">
+      <c r="A205" s="13" t="s">
         <v>696</v>
       </c>
-      <c r="B205" s="16">
+      <c r="B205" s="14">
         <v>19</v>
       </c>
-      <c r="C205" s="17" t="s">
+      <c r="C205" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D205" s="17" t="s">
+      <c r="D205" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E205" s="17" t="s">
+      <c r="E205" s="15" t="s">
         <v>697</v>
       </c>
-      <c r="F205" s="17" t="s">
+      <c r="F205" s="15" t="s">
         <v>698</v>
       </c>
-      <c r="G205" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H205" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I205" s="18"/>
+      <c r="G205" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H205" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I205" s="16"/>
     </row>
     <row r="206" spans="1:9" ht="28.3">
-      <c r="A206" s="15" t="s">
+      <c r="A206" s="13" t="s">
         <v>699</v>
       </c>
-      <c r="B206" s="16">
+      <c r="B206" s="14">
         <v>20</v>
       </c>
-      <c r="C206" s="17" t="s">
+      <c r="C206" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D206" s="17" t="s">
+      <c r="D206" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E206" s="17" t="s">
+      <c r="E206" s="15" t="s">
         <v>701</v>
       </c>
-      <c r="F206" s="17" t="s">
+      <c r="F206" s="15" t="s">
         <v>702</v>
       </c>
-      <c r="G206" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H206" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I206" s="18"/>
+      <c r="G206" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H206" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I206" s="16"/>
     </row>
     <row r="207" spans="1:9" ht="28.3">
-      <c r="A207" s="15" t="s">
+      <c r="A207" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="B207" s="16">
+      <c r="B207" s="14">
         <v>20</v>
       </c>
-      <c r="C207" s="17" t="s">
+      <c r="C207" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D207" s="17" t="s">
+      <c r="D207" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E207" s="17" t="s">
+      <c r="E207" s="15" t="s">
         <v>704</v>
       </c>
-      <c r="F207" s="17" t="s">
+      <c r="F207" s="15" t="s">
         <v>705</v>
       </c>
-      <c r="G207" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H207" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I207" s="18"/>
+      <c r="G207" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H207" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I207" s="16"/>
     </row>
     <row r="208" spans="1:9" ht="28.3">
-      <c r="A208" s="15" t="s">
+      <c r="A208" s="13" t="s">
         <v>706</v>
       </c>
-      <c r="B208" s="16">
+      <c r="B208" s="14">
         <v>20</v>
       </c>
-      <c r="C208" s="17" t="s">
+      <c r="C208" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D208" s="17" t="s">
+      <c r="D208" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E208" s="17" t="s">
+      <c r="E208" s="15" t="s">
         <v>707</v>
       </c>
-      <c r="F208" s="17" t="s">
+      <c r="F208" s="15" t="s">
         <v>708</v>
       </c>
-      <c r="G208" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H208" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I208" s="18"/>
+      <c r="G208" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H208" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I208" s="16"/>
     </row>
     <row r="209" spans="1:9" ht="28.3">
-      <c r="A209" s="15" t="s">
+      <c r="A209" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="B209" s="16">
+      <c r="B209" s="14">
         <v>20</v>
       </c>
-      <c r="C209" s="17" t="s">
+      <c r="C209" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D209" s="17" t="s">
+      <c r="D209" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E209" s="17" t="s">
+      <c r="E209" s="15" t="s">
         <v>710</v>
       </c>
-      <c r="F209" s="17" t="s">
+      <c r="F209" s="15" t="s">
         <v>711</v>
       </c>
-      <c r="G209" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H209" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I209" s="18"/>
+      <c r="G209" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H209" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I209" s="16"/>
     </row>
     <row r="210" spans="1:9" ht="28.3">
-      <c r="A210" s="15" t="s">
+      <c r="A210" s="13" t="s">
         <v>712</v>
       </c>
-      <c r="B210" s="16">
+      <c r="B210" s="14">
         <v>20</v>
       </c>
-      <c r="C210" s="17" t="s">
+      <c r="C210" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D210" s="17" t="s">
+      <c r="D210" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E210" s="17" t="s">
+      <c r="E210" s="15" t="s">
         <v>713</v>
       </c>
-      <c r="F210" s="17" t="s">
+      <c r="F210" s="15" t="s">
         <v>714</v>
       </c>
-      <c r="G210" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H210" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I210" s="18"/>
+      <c r="G210" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H210" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I210" s="16"/>
     </row>
     <row r="211" spans="1:9" ht="28.3">
-      <c r="A211" s="15" t="s">
+      <c r="A211" s="13" t="s">
         <v>715</v>
       </c>
-      <c r="B211" s="16">
+      <c r="B211" s="14">
         <v>20</v>
       </c>
-      <c r="C211" s="17" t="s">
+      <c r="C211" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D211" s="17" t="s">
+      <c r="D211" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E211" s="17" t="s">
+      <c r="E211" s="15" t="s">
         <v>716</v>
       </c>
-      <c r="F211" s="17" t="s">
+      <c r="F211" s="15" t="s">
         <v>717</v>
       </c>
-      <c r="G211" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H211" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I211" s="18"/>
+      <c r="G211" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H211" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I211" s="16"/>
     </row>
     <row r="212" spans="1:9" ht="28.3">
-      <c r="A212" s="15" t="s">
+      <c r="A212" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="B212" s="16">
+      <c r="B212" s="14">
         <v>20</v>
       </c>
-      <c r="C212" s="17" t="s">
+      <c r="C212" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D212" s="17" t="s">
+      <c r="D212" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E212" s="17" t="s">
+      <c r="E212" s="15" t="s">
         <v>719</v>
       </c>
-      <c r="F212" s="17" t="s">
+      <c r="F212" s="15" t="s">
         <v>720</v>
       </c>
-      <c r="G212" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H212" s="17" t="s">
+      <c r="G212" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H212" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I212" s="18"/>
+      <c r="I212" s="16"/>
     </row>
     <row r="213" spans="1:9" ht="28.3">
-      <c r="A213" s="15" t="s">
+      <c r="A213" s="13" t="s">
         <v>721</v>
       </c>
-      <c r="B213" s="16">
+      <c r="B213" s="14">
         <v>20</v>
       </c>
-      <c r="C213" s="17" t="s">
+      <c r="C213" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D213" s="17" t="s">
+      <c r="D213" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E213" s="17" t="s">
+      <c r="E213" s="15" t="s">
         <v>722</v>
       </c>
-      <c r="F213" s="17" t="s">
+      <c r="F213" s="15" t="s">
         <v>723</v>
       </c>
-      <c r="G213" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H213" s="17" t="s">
+      <c r="G213" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H213" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I213" s="18"/>
+      <c r="I213" s="16"/>
     </row>
     <row r="214" spans="1:9" ht="28.3">
-      <c r="A214" s="15" t="s">
+      <c r="A214" s="13" t="s">
         <v>724</v>
       </c>
-      <c r="B214" s="16">
+      <c r="B214" s="14">
         <v>20</v>
       </c>
-      <c r="C214" s="17" t="s">
+      <c r="C214" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D214" s="17" t="s">
+      <c r="D214" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E214" s="17" t="s">
+      <c r="E214" s="15" t="s">
         <v>725</v>
       </c>
-      <c r="F214" s="17" t="s">
+      <c r="F214" s="15" t="s">
         <v>726</v>
       </c>
-      <c r="G214" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H214" s="17" t="s">
+      <c r="G214" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H214" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I214" s="18"/>
+      <c r="I214" s="16"/>
     </row>
     <row r="215" spans="1:9" ht="28.3">
-      <c r="A215" s="15" t="s">
+      <c r="A215" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="B215" s="16">
+      <c r="B215" s="14">
         <v>20</v>
       </c>
-      <c r="C215" s="17" t="s">
+      <c r="C215" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D215" s="17" t="s">
+      <c r="D215" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E215" s="17" t="s">
+      <c r="E215" s="15" t="s">
         <v>728</v>
       </c>
-      <c r="F215" s="17" t="s">
+      <c r="F215" s="15" t="s">
         <v>729</v>
       </c>
-      <c r="G215" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H215" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I215" s="18"/>
+      <c r="G215" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H215" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I215" s="16"/>
     </row>
     <row r="216" spans="1:9" ht="28.3">
-      <c r="A216" s="15" t="s">
+      <c r="A216" s="13" t="s">
         <v>730</v>
       </c>
-      <c r="B216" s="16">
+      <c r="B216" s="14">
         <v>20</v>
       </c>
-      <c r="C216" s="17" t="s">
+      <c r="C216" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D216" s="17" t="s">
+      <c r="D216" s="15" t="s">
         <v>731</v>
       </c>
-      <c r="E216" s="17" t="s">
+      <c r="E216" s="15" t="s">
         <v>732</v>
       </c>
-      <c r="F216" s="17" t="s">
+      <c r="F216" s="15" t="s">
         <v>733</v>
       </c>
-      <c r="G216" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H216" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I216" s="18"/>
+      <c r="G216" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H216" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I216" s="16"/>
     </row>
     <row r="217" spans="1:9" ht="28.3">
-      <c r="A217" s="15" t="s">
+      <c r="A217" s="13" t="s">
         <v>734</v>
       </c>
-      <c r="B217" s="16">
+      <c r="B217" s="14">
         <v>20</v>
       </c>
-      <c r="C217" s="17" t="s">
+      <c r="C217" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D217" s="17" t="s">
+      <c r="D217" s="15" t="s">
         <v>735</v>
       </c>
-      <c r="E217" s="17" t="s">
+      <c r="E217" s="15" t="s">
         <v>736</v>
       </c>
-      <c r="F217" s="17" t="s">
+      <c r="F217" s="15" t="s">
         <v>737</v>
       </c>
-      <c r="G217" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H217" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I217" s="18"/>
+      <c r="G217" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H217" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I217" s="16"/>
     </row>
     <row r="218" spans="1:9" ht="28.3">
-      <c r="A218" s="15" t="s">
+      <c r="A218" s="13" t="s">
         <v>738</v>
       </c>
-      <c r="B218" s="16">
+      <c r="B218" s="14">
         <v>20</v>
       </c>
-      <c r="C218" s="17" t="s">
+      <c r="C218" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D218" s="17" t="s">
+      <c r="D218" s="15" t="s">
         <v>735</v>
       </c>
-      <c r="E218" s="17" t="s">
+      <c r="E218" s="15" t="s">
         <v>739</v>
       </c>
-      <c r="F218" s="17" t="s">
+      <c r="F218" s="15" t="s">
         <v>740</v>
       </c>
-      <c r="G218" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H218" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I218" s="18"/>
+      <c r="G218" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H218" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I218" s="16"/>
     </row>
     <row r="219" spans="1:9" ht="28.3">
-      <c r="A219" s="15" t="s">
+      <c r="A219" s="13" t="s">
         <v>741</v>
       </c>
-      <c r="B219" s="16">
+      <c r="B219" s="14">
         <v>20</v>
       </c>
-      <c r="C219" s="17" t="s">
+      <c r="C219" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D219" s="17" t="s">
+      <c r="D219" s="15" t="s">
         <v>735</v>
       </c>
-      <c r="E219" s="17" t="s">
+      <c r="E219" s="15" t="s">
         <v>742</v>
       </c>
-      <c r="F219" s="17" t="s">
+      <c r="F219" s="15" t="s">
         <v>743</v>
       </c>
-      <c r="G219" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="H219" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I219" s="18"/>
+      <c r="G219" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H219" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I219" s="16"/>
     </row>
     <row r="220" spans="1:9" ht="14.6" thickBot="1">
-      <c r="A220" s="19" t="s">
+      <c r="A220" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="B220" s="20">
+      <c r="B220" s="18">
         <v>20</v>
       </c>
-      <c r="C220" s="21" t="s">
+      <c r="C220" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D220" s="21" t="s">
+      <c r="D220" s="19" t="s">
         <v>735</v>
       </c>
-      <c r="E220" s="21" t="s">
+      <c r="E220" s="19" t="s">
         <v>745</v>
       </c>
-      <c r="F220" s="21" t="s">
+      <c r="F220" s="19" t="s">
         <v>746</v>
       </c>
-      <c r="G220" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="H220" s="21" t="s">
+      <c r="G220" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="H220" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="I220" s="22"/>
+      <c r="I220" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G220">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>G5="Complete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>G5="In Progress"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>G5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>G5="Skipped"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10450,32 +10216,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="21" t="s">
         <v>747</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="22" t="s">
         <v>748</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="6" t="s">
@@ -10930,477 +10696,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="14.15"/>
-  <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="43" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="6" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="9" t="s">
-        <v>815</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="6" t="s">
-        <v>816</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>818</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>819</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>820</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.3">
-      <c r="A6" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.3">
-      <c r="A7" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="28.3">
-      <c r="A8" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.3">
-      <c r="A9" s="1" t="s">
-        <v>844</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>845</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>846</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="28.3">
-      <c r="A10" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="D11" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="D12" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>861</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>862</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>863</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>865</v>
-      </c>
-      <c r="B14" t="s">
-        <v>866</v>
-      </c>
-      <c r="C14" t="s">
-        <v>867</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="28.3">
-      <c r="A15" t="s">
-        <v>870</v>
-      </c>
-      <c r="B15" t="s">
-        <v>871</v>
-      </c>
-      <c r="C15" t="s">
-        <v>872</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>876</v>
-      </c>
-      <c r="B16" t="s">
-        <v>877</v>
-      </c>
-      <c r="C16" t="s">
-        <v>878</v>
-      </c>
-      <c r="D16" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>858</v>
-      </c>
-      <c r="B17" t="s">
-        <v>880</v>
-      </c>
-      <c r="C17" t="s">
-        <v>881</v>
-      </c>
-      <c r="D17" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>459</v>
-      </c>
-      <c r="B18" t="s">
-        <v>883</v>
-      </c>
-      <c r="C18" t="s">
-        <v>884</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>885</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>886</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="42.45">
-      <c r="A19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" t="s">
-        <v>888</v>
-      </c>
-      <c r="C19" t="s">
-        <v>889</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>891</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="42.45">
-      <c r="A20" t="s">
-        <v>473</v>
-      </c>
-      <c r="B20" t="s">
-        <v>893</v>
-      </c>
-      <c r="C20" t="s">
-        <v>894</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="42.45">
-      <c r="D21" s="1" t="s">
-        <v>898</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="28.3">
-      <c r="D22" s="1" t="s">
-        <v>900</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="28.3">
-      <c r="A23" s="6" t="s">
-        <v>903</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>904</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="28.3">
-      <c r="A24" t="s">
-        <v>908</v>
-      </c>
-      <c r="B24" t="s">
-        <v>909</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>910</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>911</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="28.3">
-      <c r="A25" t="s">
-        <v>913</v>
-      </c>
-      <c r="B25" t="s">
-        <v>914</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="28.3">
-      <c r="A26" t="s">
-        <v>918</v>
-      </c>
-      <c r="B26" t="s">
-        <v>919</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>920</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>921</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>923</v>
-      </c>
-      <c r="B27" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
-        <v>925</v>
-      </c>
-      <c r="B28" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
-        <v>927</v>
-      </c>
-      <c r="B29" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
-        <v>929</v>
-      </c>
-      <c r="B30" t="s">
-        <v>930</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4006C77F-1040-427D-85E0-68DB34F28C07}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
@@ -11415,54 +10710,54 @@
         <v>477</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>861</v>
+        <v>816</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>862</v>
+        <v>817</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>865</v>
+        <v>818</v>
       </c>
       <c r="B2" t="s">
-        <v>866</v>
+        <v>819</v>
       </c>
       <c r="C2" t="s">
-        <v>867</v>
+        <v>820</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>870</v>
+        <v>821</v>
       </c>
       <c r="B3" t="s">
-        <v>871</v>
+        <v>822</v>
       </c>
       <c r="C3" t="s">
-        <v>872</v>
+        <v>823</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>876</v>
+        <v>824</v>
       </c>
       <c r="B4" t="s">
-        <v>877</v>
+        <v>825</v>
       </c>
       <c r="C4" t="s">
-        <v>878</v>
+        <v>826</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>858</v>
+        <v>815</v>
       </c>
       <c r="B5" t="s">
-        <v>880</v>
+        <v>827</v>
       </c>
       <c r="C5" t="s">
-        <v>881</v>
+        <v>828</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -11470,10 +10765,10 @@
         <v>459</v>
       </c>
       <c r="B6" t="s">
-        <v>883</v>
+        <v>829</v>
       </c>
       <c r="C6" t="s">
-        <v>884</v>
+        <v>830</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -11481,10 +10776,10 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>888</v>
+        <v>831</v>
       </c>
       <c r="C7" t="s">
-        <v>889</v>
+        <v>832</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -11492,74 +10787,74 @@
         <v>473</v>
       </c>
       <c r="B8" t="s">
-        <v>893</v>
+        <v>833</v>
       </c>
       <c r="C8" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="28.3">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
-        <v>903</v>
+        <v>835</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>904</v>
+        <v>836</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>908</v>
+        <v>837</v>
       </c>
       <c r="B12" t="s">
-        <v>909</v>
+        <v>838</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>913</v>
+        <v>839</v>
       </c>
       <c r="B13" t="s">
-        <v>914</v>
+        <v>840</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>918</v>
+        <v>841</v>
       </c>
       <c r="B14" t="s">
-        <v>919</v>
+        <v>842</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>923</v>
+        <v>843</v>
       </c>
       <c r="B15" t="s">
-        <v>924</v>
+        <v>844</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>925</v>
+        <v>845</v>
       </c>
       <c r="B16" t="s">
-        <v>926</v>
+        <v>846</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>927</v>
+        <v>847</v>
       </c>
       <c r="B17" t="s">
-        <v>928</v>
+        <v>848</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>929</v>
+        <v>849</v>
       </c>
       <c r="B18" t="s">
-        <v>930</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>

--- a/NetLabz_Project_Checklist.xlsx
+++ b/NetLabz_Project_Checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NetLabz_Enterprise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E31B397-A22C-4E88-870D-36F7719DAE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27857B8C-BFE4-42B4-94CB-7FB6C0E6D873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="856">
   <si>
     <t>Overall Progress</t>
   </si>
@@ -2595,6 +2595,15 @@
   </si>
   <si>
     <t>Used AI to list file types that are common with VM's so as not to miss any, creating vulnerability.</t>
+  </si>
+  <si>
+    <t>Created all my vswitches 1x External, 3x Internal</t>
+  </si>
+  <si>
+    <t>Would need to install wireshark inside VM to capture arp and icmp unicast replies. Currently only captures broadcasts.</t>
+  </si>
+  <si>
+    <t>No routing capabilities yet, so adding this section later.</t>
   </si>
 </sst>
 </file>
@@ -2915,54 +2924,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2F5597"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2F5597"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -3118,6 +3079,54 @@
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF2F5597"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF2F5597"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3132,7 +3141,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectChecklistTable" displayName="ProjectChecklistTable" ref="A4:I220" totalsRowShown="0" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectChecklistTable" displayName="ProjectChecklistTable" ref="A4:I220" totalsRowShown="0" dataDxfId="13">
   <autoFilter ref="A4:I220" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="6">
       <filters>
@@ -3141,15 +3150,15 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task ID" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phase #" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Phase" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Category" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Task" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Deliverable / Evidence" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Priority" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Notes" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task ID" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phase #" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Phase" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Category" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Task" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Deliverable / Evidence" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Priority" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Notes" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3170,7 +3179,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0DFA51D1-C4E7-4297-A332-2A07FE6908A6}" name="Table3" displayName="Table3" ref="A1:C8" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0DFA51D1-C4E7-4297-A332-2A07FE6908A6}" name="Table3" displayName="Table3" ref="A1:C8" totalsRowShown="0" headerRowDxfId="15">
   <autoFilter ref="A1:C8" xr:uid="{0DFA51D1-C4E7-4297-A332-2A07FE6908A6}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{84782901-9C62-43D0-9F45-B6BDD25C78B2}" name="Network"/>
@@ -3182,7 +3191,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A49B7CAB-322A-4674-B078-48D9A820176E}" name="Table4" displayName="Table4" ref="A11:B18" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A49B7CAB-322A-4674-B078-48D9A820176E}" name="Table4" displayName="Table4" ref="A11:B18" totalsRowShown="0" headerRowDxfId="14">
   <autoFilter ref="A11:B18" xr:uid="{A49B7CAB-322A-4674-B078-48D9A820176E}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{E986A977-7F13-4F5C-AB41-2E2F4CECF81A}" name="Address Range"/>
@@ -3427,7 +3436,7 @@
       </c>
       <c r="B4" s="4">
         <f>IF(B5=0,0,B6/B5)</f>
-        <v>6.9444444444444448E-2</v>
+        <v>8.7962962962962965E-2</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -3457,7 +3466,7 @@
       </c>
       <c r="B6" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -3487,7 +3496,7 @@
       </c>
       <c r="B8" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Blocked")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>6</v>
@@ -3502,7 +3511,7 @@
       </c>
       <c r="B9" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Not Started")</f>
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -3584,7 +3593,7 @@
       </c>
       <c r="E14">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A14,'Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A14,'Project Checklist'!$G$5:$G$220,"In Progress")</f>
@@ -3592,11 +3601,11 @@
       </c>
       <c r="G14">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A14,'Project Checklist'!$G$5:$G$220,"Blocked")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="0"/>
-        <v>0.1111111111111111</v>
+        <v>0.55555555555555558</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4742,7 +4751,7 @@
       </c>
       <c r="I19" s="16"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" ht="28.3">
       <c r="A20" s="13" t="s">
         <v>105</v>
       </c>
@@ -4762,12 +4771,14 @@
         <v>107</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="16"/>
+      <c r="I20" s="16" t="s">
+        <v>853</v>
+      </c>
     </row>
     <row r="21" spans="1:9" ht="28.3">
       <c r="A21" s="13" t="s">
@@ -4789,7 +4800,7 @@
         <v>111</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>54</v>
@@ -4816,7 +4827,7 @@
         <v>115</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>54</v>
@@ -4843,14 +4854,14 @@
         <v>119</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>54</v>
       </c>
       <c r="I23" s="16"/>
     </row>
-    <row r="24" spans="1:9" ht="28.3">
+    <row r="24" spans="1:9" ht="42.45">
       <c r="A24" s="13" t="s">
         <v>120</v>
       </c>
@@ -4870,12 +4881,14 @@
         <v>123</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="16"/>
+      <c r="I24" s="16" t="s">
+        <v>854</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="13" t="s">
@@ -4897,7 +4910,7 @@
         <v>126</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>69</v>
@@ -4924,12 +4937,14 @@
         <v>130</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I26" s="16"/>
+      <c r="I26" s="16" t="s">
+        <v>855</v>
+      </c>
     </row>
     <row r="27" spans="1:9" ht="28.3">
       <c r="A27" s="13" t="s">

--- a/NetLabz_Project_Checklist.xlsx
+++ b/NetLabz_Project_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NetLabz_Enterprise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27857B8C-BFE4-42B4-94CB-7FB6C0E6D873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD08026-734A-4D80-B372-7F2F43914BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2924,6 +2924,54 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF2F5597"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF2F5597"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -3079,54 +3127,6 @@
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2F5597"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2F5597"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3141,24 +3141,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectChecklistTable" displayName="ProjectChecklistTable" ref="A4:I220" totalsRowShown="0" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectChecklistTable" displayName="ProjectChecklistTable" ref="A4:I220" totalsRowShown="0" dataDxfId="15">
   <autoFilter ref="A4:I220" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="6">
       <filters>
+        <filter val="Blocked"/>
         <filter val="Not Started"/>
+        <filter val="Skipped"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phase #" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Phase" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Category" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Task" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Deliverable / Evidence" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Priority" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Notes" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phase #" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Phase" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Category" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Task" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Deliverable / Evidence" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Priority" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Notes" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3179,7 +3181,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0DFA51D1-C4E7-4297-A332-2A07FE6908A6}" name="Table3" displayName="Table3" ref="A1:C8" totalsRowShown="0" headerRowDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0DFA51D1-C4E7-4297-A332-2A07FE6908A6}" name="Table3" displayName="Table3" ref="A1:C8" totalsRowShown="0" headerRowDxfId="5">
   <autoFilter ref="A1:C8" xr:uid="{0DFA51D1-C4E7-4297-A332-2A07FE6908A6}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{84782901-9C62-43D0-9F45-B6BDD25C78B2}" name="Network"/>
@@ -3191,7 +3193,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A49B7CAB-322A-4674-B078-48D9A820176E}" name="Table4" displayName="Table4" ref="A11:B18" totalsRowShown="0" headerRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A49B7CAB-322A-4674-B078-48D9A820176E}" name="Table4" displayName="Table4" ref="A11:B18" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A11:B18" xr:uid="{A49B7CAB-322A-4674-B078-48D9A820176E}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{E986A977-7F13-4F5C-AB41-2E2F4CECF81A}" name="Address Range"/>
@@ -3436,7 +3438,7 @@
       </c>
       <c r="B4" s="4">
         <f>IF(B5=0,0,B6/B5)</f>
-        <v>8.7962962962962965E-2</v>
+        <v>9.2592592592592587E-2</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -3466,7 +3468,7 @@
       </c>
       <c r="B6" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -3511,7 +3513,7 @@
       </c>
       <c r="B9" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Not Started")</f>
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -3593,7 +3595,7 @@
       </c>
       <c r="E14">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A14,'Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A14,'Project Checklist'!$G$5:$G$220,"In Progress")</f>
@@ -3605,7 +3607,7 @@
       </c>
       <c r="H14" s="3">
         <f t="shared" si="0"/>
-        <v>0.55555555555555558</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4751,7 +4753,7 @@
       </c>
       <c r="I19" s="16"/>
     </row>
-    <row r="20" spans="1:9" ht="28.3">
+    <row r="20" spans="1:9" ht="28.3" hidden="1">
       <c r="A20" s="13" t="s">
         <v>105</v>
       </c>
@@ -4780,7 +4782,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="28.3">
+    <row r="21" spans="1:9" ht="28.3" hidden="1">
       <c r="A21" s="13" t="s">
         <v>108</v>
       </c>
@@ -4807,7 +4809,7 @@
       </c>
       <c r="I21" s="16"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" hidden="1">
       <c r="A22" s="13" t="s">
         <v>112</v>
       </c>
@@ -4834,7 +4836,7 @@
       </c>
       <c r="I22" s="16"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" hidden="1">
       <c r="A23" s="13" t="s">
         <v>116</v>
       </c>
@@ -4946,7 +4948,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="28.3">
+    <row r="27" spans="1:9" ht="28.3" hidden="1">
       <c r="A27" s="13" t="s">
         <v>131</v>
       </c>
@@ -4966,7 +4968,7 @@
         <v>133</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>54</v>

--- a/NetLabz_Project_Checklist.xlsx
+++ b/NetLabz_Project_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NetLabz_Enterprise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD08026-734A-4D80-B372-7F2F43914BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AF1A87-C505-4236-905B-8E7348B61BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="857">
   <si>
     <t>Overall Progress</t>
   </si>
@@ -2604,6 +2604,9 @@
   </si>
   <si>
     <t>No routing capabilities yet, so adding this section later.</t>
+  </si>
+  <si>
+    <t>Selecting OPNSense</t>
   </si>
 </sst>
 </file>
@@ -3483,7 +3486,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"In Progress")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>9</v>
@@ -3513,7 +3516,7 @@
       </c>
       <c r="B9" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Not Started")</f>
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -3630,7 +3633,7 @@
       </c>
       <c r="F15">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A15,'Project Checklist'!$G$5:$G$220,"In Progress")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A15,'Project Checklist'!$G$5:$G$220,"Blocked")</f>
@@ -4975,7 +4978,7 @@
       </c>
       <c r="I27" s="16"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" ht="28.3">
       <c r="A28" s="13" t="s">
         <v>134</v>
       </c>
@@ -4995,12 +4998,14 @@
         <v>137</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="16"/>
+      <c r="I28" s="16" t="s">
+        <v>856</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="28.3">
       <c r="A29" s="13" t="s">

--- a/NetLabz_Project_Checklist.xlsx
+++ b/NetLabz_Project_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NetLabz_Enterprise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AF1A87-C505-4236-905B-8E7348B61BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BD4489-8C13-4EF9-B492-48F44840843F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,9 +476,6 @@
     <t>Addressing</t>
   </si>
   <si>
-    <t>Assign initial LAN gateway address 10.10.10.1/24 or approved equivalent.</t>
-  </si>
-  <si>
     <t>Gateway responds from lab host</t>
   </si>
   <si>
@@ -2607,6 +2604,9 @@
   </si>
   <si>
     <t>Selecting OPNSense</t>
+  </si>
+  <si>
+    <t>Assign initial LAN gateway address 10.10.20.1/24</t>
   </si>
 </sst>
 </file>
@@ -3415,7 +3415,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="13.75" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B4" s="4">
         <f>IF(B5=0,0,B6/B5)</f>
-        <v>9.2592592592592587E-2</v>
+        <v>0.11574074074074074</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B6" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B7" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>9</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B9" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Not Started")</f>
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -3629,11 +3629,11 @@
       </c>
       <c r="E15">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A15,'Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A15,'Project Checklist'!$G$5:$G$220,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A15,'Project Checklist'!$G$5:$G$220,"Blocked")</f>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4591,7 +4591,7 @@
         <v>54</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="28.3" hidden="1">
@@ -4782,7 +4782,7 @@
         <v>54</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="28.3" hidden="1">
@@ -4892,7 +4892,7 @@
         <v>69</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -4948,7 +4948,7 @@
         <v>69</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="28.3" hidden="1">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="I27" s="16"/>
     </row>
-    <row r="28" spans="1:9" ht="28.3">
+    <row r="28" spans="1:9">
       <c r="A28" s="13" t="s">
         <v>134</v>
       </c>
@@ -4998,13 +4998,13 @@
         <v>137</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="28.3">
@@ -5027,7 +5027,7 @@
         <v>140</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>54</v>
@@ -5054,14 +5054,14 @@
         <v>143</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>54</v>
       </c>
       <c r="I30" s="16"/>
     </row>
-    <row r="31" spans="1:9" ht="28.3">
+    <row r="31" spans="1:9">
       <c r="A31" s="13" t="s">
         <v>144</v>
       </c>
@@ -5075,13 +5075,13 @@
         <v>145</v>
       </c>
       <c r="E31" s="15" t="s">
+        <v>856</v>
+      </c>
+      <c r="F31" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="F31" s="15" t="s">
-        <v>147</v>
-      </c>
       <c r="G31" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>54</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B32" s="14">
         <v>2</v>
@@ -5099,16 +5099,16 @@
         <v>22</v>
       </c>
       <c r="D32" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="F32" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="F32" s="15" t="s">
-        <v>151</v>
-      </c>
       <c r="G32" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>54</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="33" spans="1:9" ht="28.3">
       <c r="A33" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B33" s="14">
         <v>2</v>
@@ -5126,13 +5126,13 @@
         <v>22</v>
       </c>
       <c r="D33" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="F33" s="15" t="s">
         <v>154</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>155</v>
       </c>
       <c r="G33" s="15" t="s">
         <v>4</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="34" spans="1:9" ht="28.3">
       <c r="A34" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B34" s="14">
         <v>2</v>
@@ -5156,10 +5156,10 @@
         <v>81</v>
       </c>
       <c r="E34" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F34" s="15" t="s">
         <v>157</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>158</v>
       </c>
       <c r="G34" s="15" t="s">
         <v>4</v>
@@ -5171,7 +5171,7 @@
     </row>
     <row r="35" spans="1:9" ht="28.3">
       <c r="A35" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B35" s="14">
         <v>2</v>
@@ -5183,10 +5183,10 @@
         <v>117</v>
       </c>
       <c r="E35" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" s="15" t="s">
         <v>160</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>161</v>
       </c>
       <c r="G35" s="15" t="s">
         <v>4</v>
@@ -5198,7 +5198,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B36" s="14">
         <v>2</v>
@@ -5210,10 +5210,10 @@
         <v>128</v>
       </c>
       <c r="E36" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F36" s="15" t="s">
         <v>163</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>164</v>
       </c>
       <c r="G36" s="15" t="s">
         <v>4</v>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B37" s="14">
         <v>2</v>
@@ -5237,10 +5237,10 @@
         <v>71</v>
       </c>
       <c r="E37" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F37" s="15" t="s">
         <v>166</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>167</v>
       </c>
       <c r="G37" s="15" t="s">
         <v>4</v>
@@ -5252,7 +5252,7 @@
     </row>
     <row r="38" spans="1:9" ht="28.3">
       <c r="A38" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B38" s="14">
         <v>3</v>
@@ -5261,13 +5261,13 @@
         <v>24</v>
       </c>
       <c r="D38" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="E38" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="F38" s="15" t="s">
         <v>170</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>171</v>
       </c>
       <c r="G38" s="15" t="s">
         <v>4</v>
@@ -5279,7 +5279,7 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B39" s="14">
         <v>3</v>
@@ -5291,10 +5291,10 @@
         <v>109</v>
       </c>
       <c r="E39" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" s="15" t="s">
         <v>173</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>174</v>
       </c>
       <c r="G39" s="15" t="s">
         <v>4</v>
@@ -5306,7 +5306,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B40" s="14">
         <v>3</v>
@@ -5318,10 +5318,10 @@
         <v>113</v>
       </c>
       <c r="E40" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="F40" s="15" t="s">
         <v>176</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>177</v>
       </c>
       <c r="G40" s="15" t="s">
         <v>4</v>
@@ -5333,7 +5333,7 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B41" s="14">
         <v>3</v>
@@ -5342,13 +5342,13 @@
         <v>24</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E41" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="F41" s="15" t="s">
         <v>179</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>180</v>
       </c>
       <c r="G41" s="15" t="s">
         <v>4</v>
@@ -5360,7 +5360,7 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B42" s="14">
         <v>3</v>
@@ -5369,13 +5369,13 @@
         <v>24</v>
       </c>
       <c r="D42" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E42" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="F42" s="15" t="s">
         <v>183</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>184</v>
       </c>
       <c r="G42" s="15" t="s">
         <v>4</v>
@@ -5387,7 +5387,7 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B43" s="14">
         <v>3</v>
@@ -5396,13 +5396,13 @@
         <v>24</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E43" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F43" s="15" t="s">
         <v>186</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>187</v>
       </c>
       <c r="G43" s="15" t="s">
         <v>4</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B44" s="14">
         <v>3</v>
@@ -5423,13 +5423,13 @@
         <v>24</v>
       </c>
       <c r="D44" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="F44" s="15" t="s">
         <v>190</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>191</v>
       </c>
       <c r="G44" s="15" t="s">
         <v>4</v>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="45" spans="1:9" ht="28.3">
       <c r="A45" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B45" s="14">
         <v>3</v>
@@ -5450,13 +5450,13 @@
         <v>24</v>
       </c>
       <c r="D45" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E45" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="F45" s="15" t="s">
         <v>194</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>195</v>
       </c>
       <c r="G45" s="15" t="s">
         <v>4</v>
@@ -5468,7 +5468,7 @@
     </row>
     <row r="46" spans="1:9" ht="28.3">
       <c r="A46" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B46" s="14">
         <v>3</v>
@@ -5477,13 +5477,13 @@
         <v>24</v>
       </c>
       <c r="D46" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="F46" s="15" t="s">
         <v>198</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>199</v>
       </c>
       <c r="G46" s="15" t="s">
         <v>4</v>
@@ -5495,7 +5495,7 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B47" s="14">
         <v>3</v>
@@ -5507,10 +5507,10 @@
         <v>71</v>
       </c>
       <c r="E47" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="F47" s="15" t="s">
         <v>201</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>202</v>
       </c>
       <c r="G47" s="15" t="s">
         <v>4</v>
@@ -5522,7 +5522,7 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B48" s="14">
         <v>4</v>
@@ -5534,10 +5534,10 @@
         <v>109</v>
       </c>
       <c r="E48" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="F48" s="15" t="s">
         <v>204</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>205</v>
       </c>
       <c r="G48" s="15" t="s">
         <v>4</v>
@@ -5549,7 +5549,7 @@
     </row>
     <row r="49" spans="1:9" ht="28.3">
       <c r="A49" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B49" s="14">
         <v>4</v>
@@ -5561,10 +5561,10 @@
         <v>113</v>
       </c>
       <c r="E49" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="F49" s="15" t="s">
         <v>207</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>208</v>
       </c>
       <c r="G49" s="15" t="s">
         <v>4</v>
@@ -5576,7 +5576,7 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B50" s="14">
         <v>4</v>
@@ -5585,13 +5585,13 @@
         <v>25</v>
       </c>
       <c r="D50" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="E50" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="F50" s="15" t="s">
         <v>211</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>212</v>
       </c>
       <c r="G50" s="15" t="s">
         <v>4</v>
@@ -5603,7 +5603,7 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B51" s="14">
         <v>4</v>
@@ -5612,13 +5612,13 @@
         <v>25</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E51" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="F51" s="15" t="s">
         <v>214</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>215</v>
       </c>
       <c r="G51" s="15" t="s">
         <v>4</v>
@@ -5630,7 +5630,7 @@
     </row>
     <row r="52" spans="1:9" ht="28.3">
       <c r="A52" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B52" s="14">
         <v>4</v>
@@ -5639,13 +5639,13 @@
         <v>25</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E52" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="F52" s="15" t="s">
         <v>217</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>218</v>
       </c>
       <c r="G52" s="15" t="s">
         <v>4</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B53" s="14">
         <v>4</v>
@@ -5666,13 +5666,13 @@
         <v>25</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E53" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="F53" s="15" t="s">
         <v>220</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>221</v>
       </c>
       <c r="G53" s="15" t="s">
         <v>4</v>
@@ -5684,7 +5684,7 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B54" s="14">
         <v>4</v>
@@ -5693,13 +5693,13 @@
         <v>25</v>
       </c>
       <c r="D54" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E54" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="F54" s="15" t="s">
         <v>224</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>225</v>
       </c>
       <c r="G54" s="15" t="s">
         <v>4</v>
@@ -5711,7 +5711,7 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B55" s="14">
         <v>4</v>
@@ -5720,13 +5720,13 @@
         <v>25</v>
       </c>
       <c r="D55" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="E55" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="F55" s="15" t="s">
         <v>228</v>
-      </c>
-      <c r="F55" s="15" t="s">
-        <v>229</v>
       </c>
       <c r="G55" s="15" t="s">
         <v>4</v>
@@ -5738,7 +5738,7 @@
     </row>
     <row r="56" spans="1:9" ht="28.3">
       <c r="A56" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B56" s="14">
         <v>4</v>
@@ -5750,10 +5750,10 @@
         <v>128</v>
       </c>
       <c r="E56" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="F56" s="15" t="s">
         <v>231</v>
-      </c>
-      <c r="F56" s="15" t="s">
-        <v>232</v>
       </c>
       <c r="G56" s="15" t="s">
         <v>4</v>
@@ -5765,7 +5765,7 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B57" s="14">
         <v>4</v>
@@ -5777,10 +5777,10 @@
         <v>71</v>
       </c>
       <c r="E57" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="F57" s="15" t="s">
         <v>234</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>235</v>
       </c>
       <c r="G57" s="15" t="s">
         <v>4</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="58" spans="1:9" ht="28.3">
       <c r="A58" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B58" s="14">
         <v>5</v>
@@ -5801,13 +5801,13 @@
         <v>26</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E58" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F58" s="15" t="s">
         <v>237</v>
-      </c>
-      <c r="F58" s="15" t="s">
-        <v>238</v>
       </c>
       <c r="G58" s="15" t="s">
         <v>4</v>
@@ -5819,7 +5819,7 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B59" s="14">
         <v>5</v>
@@ -5828,13 +5828,13 @@
         <v>26</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E59" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="F59" s="15" t="s">
         <v>240</v>
-      </c>
-      <c r="F59" s="15" t="s">
-        <v>241</v>
       </c>
       <c r="G59" s="15" t="s">
         <v>4</v>
@@ -5846,7 +5846,7 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B60" s="14">
         <v>5</v>
@@ -5855,13 +5855,13 @@
         <v>26</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E60" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="F60" s="15" t="s">
         <v>243</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>244</v>
       </c>
       <c r="G60" s="15" t="s">
         <v>4</v>
@@ -5873,7 +5873,7 @@
     </row>
     <row r="61" spans="1:9" ht="28.3">
       <c r="A61" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B61" s="14">
         <v>5</v>
@@ -5885,10 +5885,10 @@
         <v>121</v>
       </c>
       <c r="E61" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F61" s="15" t="s">
         <v>246</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>247</v>
       </c>
       <c r="G61" s="15" t="s">
         <v>4</v>
@@ -5900,7 +5900,7 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B62" s="14">
         <v>5</v>
@@ -5909,13 +5909,13 @@
         <v>26</v>
       </c>
       <c r="D62" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="E62" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="E62" s="15" t="s">
+      <c r="F62" s="15" t="s">
         <v>250</v>
-      </c>
-      <c r="F62" s="15" t="s">
-        <v>251</v>
       </c>
       <c r="G62" s="15" t="s">
         <v>4</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B63" s="14">
         <v>5</v>
@@ -5936,13 +5936,13 @@
         <v>26</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E63" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="F63" s="15" t="s">
         <v>253</v>
-      </c>
-      <c r="F63" s="15" t="s">
-        <v>254</v>
       </c>
       <c r="G63" s="15" t="s">
         <v>4</v>
@@ -5954,7 +5954,7 @@
     </row>
     <row r="64" spans="1:9" ht="28.3">
       <c r="A64" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B64" s="14">
         <v>5</v>
@@ -5963,13 +5963,13 @@
         <v>26</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E64" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="F64" s="15" t="s">
         <v>256</v>
-      </c>
-      <c r="F64" s="15" t="s">
-        <v>257</v>
       </c>
       <c r="G64" s="15" t="s">
         <v>4</v>
@@ -5981,7 +5981,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B65" s="14">
         <v>5</v>
@@ -5993,10 +5993,10 @@
         <v>121</v>
       </c>
       <c r="E65" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="F65" s="15" t="s">
         <v>259</v>
-      </c>
-      <c r="F65" s="15" t="s">
-        <v>260</v>
       </c>
       <c r="G65" s="15" t="s">
         <v>4</v>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="66" spans="1:9" ht="28.3">
       <c r="A66" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B66" s="14">
         <v>5</v>
@@ -6020,10 +6020,10 @@
         <v>128</v>
       </c>
       <c r="E66" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="F66" s="15" t="s">
         <v>262</v>
-      </c>
-      <c r="F66" s="15" t="s">
-        <v>263</v>
       </c>
       <c r="G66" s="15" t="s">
         <v>4</v>
@@ -6035,7 +6035,7 @@
     </row>
     <row r="67" spans="1:9" ht="28.3">
       <c r="A67" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B67" s="14">
         <v>5</v>
@@ -6047,10 +6047,10 @@
         <v>71</v>
       </c>
       <c r="E67" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="F67" s="15" t="s">
         <v>265</v>
-      </c>
-      <c r="F67" s="15" t="s">
-        <v>266</v>
       </c>
       <c r="G67" s="15" t="s">
         <v>4</v>
@@ -6062,7 +6062,7 @@
     </row>
     <row r="68" spans="1:9" ht="28.3">
       <c r="A68" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B68" s="14">
         <v>6</v>
@@ -6071,13 +6071,13 @@
         <v>27</v>
       </c>
       <c r="D68" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="E68" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="E68" s="15" t="s">
+      <c r="F68" s="15" t="s">
         <v>269</v>
-      </c>
-      <c r="F68" s="15" t="s">
-        <v>270</v>
       </c>
       <c r="G68" s="15" t="s">
         <v>4</v>
@@ -6089,7 +6089,7 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B69" s="14">
         <v>6</v>
@@ -6098,13 +6098,13 @@
         <v>27</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E69" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="F69" s="15" t="s">
         <v>272</v>
-      </c>
-      <c r="F69" s="15" t="s">
-        <v>273</v>
       </c>
       <c r="G69" s="15" t="s">
         <v>4</v>
@@ -6116,7 +6116,7 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B70" s="14">
         <v>6</v>
@@ -6125,13 +6125,13 @@
         <v>27</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E70" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="F70" s="15" t="s">
         <v>275</v>
-      </c>
-      <c r="F70" s="15" t="s">
-        <v>276</v>
       </c>
       <c r="G70" s="15" t="s">
         <v>4</v>
@@ -6143,7 +6143,7 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B71" s="14">
         <v>6</v>
@@ -6155,10 +6155,10 @@
         <v>117</v>
       </c>
       <c r="E71" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="F71" s="15" t="s">
         <v>278</v>
-      </c>
-      <c r="F71" s="15" t="s">
-        <v>279</v>
       </c>
       <c r="G71" s="15" t="s">
         <v>4</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B72" s="14">
         <v>6</v>
@@ -6179,13 +6179,13 @@
         <v>27</v>
       </c>
       <c r="D72" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="E72" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="E72" s="15" t="s">
+      <c r="F72" s="15" t="s">
         <v>282</v>
-      </c>
-      <c r="F72" s="15" t="s">
-        <v>283</v>
       </c>
       <c r="G72" s="15" t="s">
         <v>4</v>
@@ -6197,7 +6197,7 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B73" s="14">
         <v>6</v>
@@ -6209,10 +6209,10 @@
         <v>135</v>
       </c>
       <c r="E73" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="F73" s="15" t="s">
         <v>285</v>
-      </c>
-      <c r="F73" s="15" t="s">
-        <v>286</v>
       </c>
       <c r="G73" s="15" t="s">
         <v>4</v>
@@ -6224,7 +6224,7 @@
     </row>
     <row r="74" spans="1:9" ht="28.3">
       <c r="A74" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B74" s="14">
         <v>6</v>
@@ -6236,10 +6236,10 @@
         <v>121</v>
       </c>
       <c r="E74" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="F74" s="15" t="s">
         <v>288</v>
-      </c>
-      <c r="F74" s="15" t="s">
-        <v>289</v>
       </c>
       <c r="G74" s="15" t="s">
         <v>4</v>
@@ -6251,7 +6251,7 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B75" s="14">
         <v>6</v>
@@ -6263,10 +6263,10 @@
         <v>128</v>
       </c>
       <c r="E75" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="F75" s="15" t="s">
         <v>291</v>
-      </c>
-      <c r="F75" s="15" t="s">
-        <v>292</v>
       </c>
       <c r="G75" s="15" t="s">
         <v>4</v>
@@ -6278,7 +6278,7 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B76" s="14">
         <v>6</v>
@@ -6287,13 +6287,13 @@
         <v>27</v>
       </c>
       <c r="D76" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="E76" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="F76" s="15" t="s">
         <v>295</v>
-      </c>
-      <c r="F76" s="15" t="s">
-        <v>296</v>
       </c>
       <c r="G76" s="15" t="s">
         <v>4</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B77" s="14">
         <v>6</v>
@@ -6317,10 +6317,10 @@
         <v>71</v>
       </c>
       <c r="E77" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="F77" s="15" t="s">
         <v>298</v>
-      </c>
-      <c r="F77" s="15" t="s">
-        <v>299</v>
       </c>
       <c r="G77" s="15" t="s">
         <v>4</v>
@@ -6332,7 +6332,7 @@
     </row>
     <row r="78" spans="1:9" ht="28.3">
       <c r="A78" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B78" s="14">
         <v>7</v>
@@ -6344,10 +6344,10 @@
         <v>109</v>
       </c>
       <c r="E78" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="F78" s="15" t="s">
         <v>301</v>
-      </c>
-      <c r="F78" s="15" t="s">
-        <v>302</v>
       </c>
       <c r="G78" s="15" t="s">
         <v>4</v>
@@ -6359,7 +6359,7 @@
     </row>
     <row r="79" spans="1:9" ht="28.3">
       <c r="A79" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B79" s="14">
         <v>7</v>
@@ -6368,13 +6368,13 @@
         <v>28</v>
       </c>
       <c r="D79" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="E79" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E79" s="15" t="s">
+      <c r="F79" s="15" t="s">
         <v>305</v>
-      </c>
-      <c r="F79" s="15" t="s">
-        <v>306</v>
       </c>
       <c r="G79" s="15" t="s">
         <v>4</v>
@@ -6386,7 +6386,7 @@
     </row>
     <row r="80" spans="1:9" ht="28.3">
       <c r="A80" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B80" s="14">
         <v>7</v>
@@ -6395,13 +6395,13 @@
         <v>28</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E80" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="F80" s="15" t="s">
         <v>308</v>
-      </c>
-      <c r="F80" s="15" t="s">
-        <v>309</v>
       </c>
       <c r="G80" s="15" t="s">
         <v>4</v>
@@ -6413,7 +6413,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B81" s="14">
         <v>7</v>
@@ -6422,13 +6422,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E81" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="F81" s="15" t="s">
         <v>311</v>
-      </c>
-      <c r="F81" s="15" t="s">
-        <v>312</v>
       </c>
       <c r="G81" s="15" t="s">
         <v>4</v>
@@ -6440,7 +6440,7 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B82" s="14">
         <v>7</v>
@@ -6449,13 +6449,13 @@
         <v>28</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E82" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="F82" s="15" t="s">
         <v>314</v>
-      </c>
-      <c r="F82" s="15" t="s">
-        <v>315</v>
       </c>
       <c r="G82" s="15" t="s">
         <v>4</v>
@@ -6467,7 +6467,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B83" s="14">
         <v>7</v>
@@ -6476,13 +6476,13 @@
         <v>28</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E83" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="F83" s="15" t="s">
         <v>317</v>
-      </c>
-      <c r="F83" s="15" t="s">
-        <v>318</v>
       </c>
       <c r="G83" s="15" t="s">
         <v>4</v>
@@ -6494,7 +6494,7 @@
     </row>
     <row r="84" spans="1:9" ht="28.3">
       <c r="A84" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B84" s="14">
         <v>7</v>
@@ -6506,10 +6506,10 @@
         <v>81</v>
       </c>
       <c r="E84" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="F84" s="15" t="s">
         <v>320</v>
-      </c>
-      <c r="F84" s="15" t="s">
-        <v>321</v>
       </c>
       <c r="G84" s="15" t="s">
         <v>4</v>
@@ -6521,7 +6521,7 @@
     </row>
     <row r="85" spans="1:9" ht="28.3">
       <c r="A85" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B85" s="14">
         <v>7</v>
@@ -6533,10 +6533,10 @@
         <v>121</v>
       </c>
       <c r="E85" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="F85" s="15" t="s">
         <v>323</v>
-      </c>
-      <c r="F85" s="15" t="s">
-        <v>324</v>
       </c>
       <c r="G85" s="15" t="s">
         <v>4</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B86" s="14">
         <v>7</v>
@@ -6560,10 +6560,10 @@
         <v>128</v>
       </c>
       <c r="E86" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="F86" s="15" t="s">
         <v>326</v>
-      </c>
-      <c r="F86" s="15" t="s">
-        <v>327</v>
       </c>
       <c r="G86" s="15" t="s">
         <v>4</v>
@@ -6575,7 +6575,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B87" s="14">
         <v>7</v>
@@ -6587,10 +6587,10 @@
         <v>71</v>
       </c>
       <c r="E87" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="F87" s="15" t="s">
         <v>329</v>
-      </c>
-      <c r="F87" s="15" t="s">
-        <v>330</v>
       </c>
       <c r="G87" s="15" t="s">
         <v>4</v>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="88" spans="1:9" ht="28.3">
       <c r="A88" s="13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B88" s="14">
         <v>8</v>
@@ -6614,10 +6614,10 @@
         <v>102</v>
       </c>
       <c r="E88" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="F88" s="15" t="s">
         <v>332</v>
-      </c>
-      <c r="F88" s="15" t="s">
-        <v>333</v>
       </c>
       <c r="G88" s="15" t="s">
         <v>4</v>
@@ -6629,7 +6629,7 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B89" s="14">
         <v>8</v>
@@ -6638,13 +6638,13 @@
         <v>29</v>
       </c>
       <c r="D89" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="E89" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="E89" s="15" t="s">
+      <c r="F89" s="15" t="s">
         <v>336</v>
-      </c>
-      <c r="F89" s="15" t="s">
-        <v>337</v>
       </c>
       <c r="G89" s="15" t="s">
         <v>4</v>
@@ -6656,7 +6656,7 @@
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B90" s="14">
         <v>8</v>
@@ -6665,13 +6665,13 @@
         <v>29</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E90" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="F90" s="15" t="s">
         <v>339</v>
-      </c>
-      <c r="F90" s="15" t="s">
-        <v>340</v>
       </c>
       <c r="G90" s="15" t="s">
         <v>4</v>
@@ -6683,7 +6683,7 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B91" s="14">
         <v>8</v>
@@ -6692,13 +6692,13 @@
         <v>29</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E91" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="F91" s="15" t="s">
         <v>342</v>
-      </c>
-      <c r="F91" s="15" t="s">
-        <v>343</v>
       </c>
       <c r="G91" s="15" t="s">
         <v>4</v>
@@ -6710,7 +6710,7 @@
     </row>
     <row r="92" spans="1:9" ht="28.3">
       <c r="A92" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B92" s="14">
         <v>8</v>
@@ -6719,13 +6719,13 @@
         <v>29</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E92" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F92" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="F92" s="15" t="s">
-        <v>346</v>
       </c>
       <c r="G92" s="15" t="s">
         <v>4</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B93" s="14">
         <v>8</v>
@@ -6746,13 +6746,13 @@
         <v>29</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E93" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="F93" s="15" t="s">
         <v>348</v>
-      </c>
-      <c r="F93" s="15" t="s">
-        <v>349</v>
       </c>
       <c r="G93" s="15" t="s">
         <v>4</v>
@@ -6764,7 +6764,7 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B94" s="14">
         <v>8</v>
@@ -6773,13 +6773,13 @@
         <v>29</v>
       </c>
       <c r="D94" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="E94" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="E94" s="15" t="s">
+      <c r="F94" s="15" t="s">
         <v>352</v>
-      </c>
-      <c r="F94" s="15" t="s">
-        <v>353</v>
       </c>
       <c r="G94" s="15" t="s">
         <v>4</v>
@@ -6791,7 +6791,7 @@
     </row>
     <row r="95" spans="1:9" ht="28.3">
       <c r="A95" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B95" s="14">
         <v>8</v>
@@ -6803,10 +6803,10 @@
         <v>81</v>
       </c>
       <c r="E95" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="F95" s="15" t="s">
         <v>355</v>
-      </c>
-      <c r="F95" s="15" t="s">
-        <v>356</v>
       </c>
       <c r="G95" s="15" t="s">
         <v>4</v>
@@ -6818,7 +6818,7 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B96" s="14">
         <v>8</v>
@@ -6830,10 +6830,10 @@
         <v>128</v>
       </c>
       <c r="E96" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="F96" s="15" t="s">
         <v>358</v>
-      </c>
-      <c r="F96" s="15" t="s">
-        <v>359</v>
       </c>
       <c r="G96" s="15" t="s">
         <v>4</v>
@@ -6845,7 +6845,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B97" s="14">
         <v>8</v>
@@ -6857,10 +6857,10 @@
         <v>71</v>
       </c>
       <c r="E97" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="F97" s="15" t="s">
         <v>361</v>
-      </c>
-      <c r="F97" s="15" t="s">
-        <v>362</v>
       </c>
       <c r="G97" s="15" t="s">
         <v>4</v>
@@ -6872,7 +6872,7 @@
     </row>
     <row r="98" spans="1:9" ht="28.3">
       <c r="A98" s="13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B98" s="14">
         <v>9</v>
@@ -6881,13 +6881,13 @@
         <v>30</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E98" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="F98" s="15" t="s">
         <v>364</v>
-      </c>
-      <c r="F98" s="15" t="s">
-        <v>365</v>
       </c>
       <c r="G98" s="15" t="s">
         <v>4</v>
@@ -6899,7 +6899,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B99" s="14">
         <v>9</v>
@@ -6911,10 +6911,10 @@
         <v>113</v>
       </c>
       <c r="E99" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="F99" s="15" t="s">
         <v>367</v>
-      </c>
-      <c r="F99" s="15" t="s">
-        <v>368</v>
       </c>
       <c r="G99" s="15" t="s">
         <v>4</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B100" s="14">
         <v>9</v>
@@ -6935,13 +6935,13 @@
         <v>30</v>
       </c>
       <c r="D100" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="E100" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="E100" s="15" t="s">
+      <c r="F100" s="15" t="s">
         <v>371</v>
-      </c>
-      <c r="F100" s="15" t="s">
-        <v>372</v>
       </c>
       <c r="G100" s="15" t="s">
         <v>4</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="101" spans="1:9" ht="28.3">
       <c r="A101" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B101" s="14">
         <v>9</v>
@@ -6965,10 +6965,10 @@
         <v>135</v>
       </c>
       <c r="E101" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="F101" s="15" t="s">
         <v>374</v>
-      </c>
-      <c r="F101" s="15" t="s">
-        <v>375</v>
       </c>
       <c r="G101" s="15" t="s">
         <v>4</v>
@@ -6980,7 +6980,7 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B102" s="14">
         <v>9</v>
@@ -6992,10 +6992,10 @@
         <v>81</v>
       </c>
       <c r="E102" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="F102" s="15" t="s">
         <v>377</v>
-      </c>
-      <c r="F102" s="15" t="s">
-        <v>378</v>
       </c>
       <c r="G102" s="15" t="s">
         <v>4</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="103" spans="1:9" ht="28.3">
       <c r="A103" s="13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B103" s="14">
         <v>9</v>
@@ -7019,10 +7019,10 @@
         <v>117</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F103" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G103" s="15" t="s">
         <v>4</v>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B104" s="14">
         <v>9</v>
@@ -7043,13 +7043,13 @@
         <v>30</v>
       </c>
       <c r="D104" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="E104" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="E104" s="15" t="s">
+      <c r="F104" s="15" t="s">
         <v>383</v>
-      </c>
-      <c r="F104" s="15" t="s">
-        <v>384</v>
       </c>
       <c r="G104" s="15" t="s">
         <v>4</v>
@@ -7061,7 +7061,7 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B105" s="14">
         <v>9</v>
@@ -7073,10 +7073,10 @@
         <v>121</v>
       </c>
       <c r="E105" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="F105" s="15" t="s">
         <v>386</v>
-      </c>
-      <c r="F105" s="15" t="s">
-        <v>387</v>
       </c>
       <c r="G105" s="15" t="s">
         <v>4</v>
@@ -7088,7 +7088,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B106" s="14">
         <v>9</v>
@@ -7100,10 +7100,10 @@
         <v>128</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F106" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G106" s="15" t="s">
         <v>4</v>
@@ -7115,7 +7115,7 @@
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B107" s="14">
         <v>9</v>
@@ -7127,10 +7127,10 @@
         <v>71</v>
       </c>
       <c r="E107" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="F107" s="15" t="s">
         <v>391</v>
-      </c>
-      <c r="F107" s="15" t="s">
-        <v>392</v>
       </c>
       <c r="G107" s="15" t="s">
         <v>4</v>
@@ -7142,7 +7142,7 @@
     </row>
     <row r="108" spans="1:9" ht="28.3">
       <c r="A108" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B108" s="14">
         <v>10</v>
@@ -7154,10 +7154,10 @@
         <v>102</v>
       </c>
       <c r="E108" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="F108" s="15" t="s">
         <v>394</v>
-      </c>
-      <c r="F108" s="15" t="s">
-        <v>395</v>
       </c>
       <c r="G108" s="15" t="s">
         <v>4</v>
@@ -7169,7 +7169,7 @@
     </row>
     <row r="109" spans="1:9" ht="28.3">
       <c r="A109" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B109" s="14">
         <v>10</v>
@@ -7178,13 +7178,13 @@
         <v>31</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E109" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="F109" s="15" t="s">
         <v>397</v>
-      </c>
-      <c r="F109" s="15" t="s">
-        <v>398</v>
       </c>
       <c r="G109" s="15" t="s">
         <v>4</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="13" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B110" s="14">
         <v>10</v>
@@ -7208,10 +7208,10 @@
         <v>59</v>
       </c>
       <c r="E110" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="F110" s="15" t="s">
         <v>400</v>
-      </c>
-      <c r="F110" s="15" t="s">
-        <v>401</v>
       </c>
       <c r="G110" s="15" t="s">
         <v>4</v>
@@ -7223,7 +7223,7 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B111" s="14">
         <v>10</v>
@@ -7235,10 +7235,10 @@
         <v>59</v>
       </c>
       <c r="E111" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="F111" s="15" t="s">
         <v>403</v>
-      </c>
-      <c r="F111" s="15" t="s">
-        <v>404</v>
       </c>
       <c r="G111" s="15" t="s">
         <v>4</v>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B112" s="14">
         <v>10</v>
@@ -7262,10 +7262,10 @@
         <v>135</v>
       </c>
       <c r="E112" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="F112" s="15" t="s">
         <v>406</v>
-      </c>
-      <c r="F112" s="15" t="s">
-        <v>407</v>
       </c>
       <c r="G112" s="15" t="s">
         <v>4</v>
@@ -7277,7 +7277,7 @@
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B113" s="14">
         <v>10</v>
@@ -7289,10 +7289,10 @@
         <v>117</v>
       </c>
       <c r="E113" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="F113" s="15" t="s">
         <v>409</v>
-      </c>
-      <c r="F113" s="15" t="s">
-        <v>410</v>
       </c>
       <c r="G113" s="15" t="s">
         <v>4</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B114" s="14">
         <v>10</v>
@@ -7316,10 +7316,10 @@
         <v>128</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G114" s="15" t="s">
         <v>4</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B115" s="14">
         <v>10</v>
@@ -7340,13 +7340,13 @@
         <v>31</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E115" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="F115" s="15" t="s">
         <v>414</v>
-      </c>
-      <c r="F115" s="15" t="s">
-        <v>415</v>
       </c>
       <c r="G115" s="15" t="s">
         <v>4</v>
@@ -7358,7 +7358,7 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B116" s="14">
         <v>10</v>
@@ -7370,10 +7370,10 @@
         <v>121</v>
       </c>
       <c r="E116" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="F116" s="15" t="s">
         <v>417</v>
-      </c>
-      <c r="F116" s="15" t="s">
-        <v>418</v>
       </c>
       <c r="G116" s="15" t="s">
         <v>4</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="117" spans="1:9" ht="28.3">
       <c r="A117" s="13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B117" s="14">
         <v>10</v>
@@ -7394,13 +7394,13 @@
         <v>31</v>
       </c>
       <c r="D117" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="E117" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="E117" s="15" t="s">
+      <c r="F117" s="15" t="s">
         <v>421</v>
-      </c>
-      <c r="F117" s="15" t="s">
-        <v>422</v>
       </c>
       <c r="G117" s="15" t="s">
         <v>4</v>
@@ -7412,7 +7412,7 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="13" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B118" s="14">
         <v>10</v>
@@ -7424,10 +7424,10 @@
         <v>71</v>
       </c>
       <c r="E118" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="F118" s="15" t="s">
         <v>424</v>
-      </c>
-      <c r="F118" s="15" t="s">
-        <v>425</v>
       </c>
       <c r="G118" s="15" t="s">
         <v>4</v>
@@ -7439,7 +7439,7 @@
     </row>
     <row r="119" spans="1:9" ht="28.3">
       <c r="A119" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B119" s="14">
         <v>11</v>
@@ -7451,10 +7451,10 @@
         <v>102</v>
       </c>
       <c r="E119" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="F119" s="15" t="s">
         <v>427</v>
-      </c>
-      <c r="F119" s="15" t="s">
-        <v>428</v>
       </c>
       <c r="G119" s="15" t="s">
         <v>4</v>
@@ -7466,7 +7466,7 @@
     </row>
     <row r="120" spans="1:9" ht="28.3">
       <c r="A120" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B120" s="14">
         <v>11</v>
@@ -7478,10 +7478,10 @@
         <v>145</v>
       </c>
       <c r="E120" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="F120" s="15" t="s">
         <v>430</v>
-      </c>
-      <c r="F120" s="15" t="s">
-        <v>431</v>
       </c>
       <c r="G120" s="15" t="s">
         <v>4</v>
@@ -7493,7 +7493,7 @@
     </row>
     <row r="121" spans="1:9" ht="28.3">
       <c r="A121" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B121" s="14">
         <v>11</v>
@@ -7505,10 +7505,10 @@
         <v>113</v>
       </c>
       <c r="E121" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="F121" s="15" t="s">
         <v>433</v>
-      </c>
-      <c r="F121" s="15" t="s">
-        <v>434</v>
       </c>
       <c r="G121" s="15" t="s">
         <v>4</v>
@@ -7520,7 +7520,7 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="13" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B122" s="14">
         <v>11</v>
@@ -7529,13 +7529,13 @@
         <v>33</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E122" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="F122" s="15" t="s">
         <v>436</v>
-      </c>
-      <c r="F122" s="15" t="s">
-        <v>437</v>
       </c>
       <c r="G122" s="15" t="s">
         <v>4</v>
@@ -7547,7 +7547,7 @@
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B123" s="14">
         <v>11</v>
@@ -7556,13 +7556,13 @@
         <v>33</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E123" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="F123" s="15" t="s">
         <v>439</v>
-      </c>
-      <c r="F123" s="15" t="s">
-        <v>440</v>
       </c>
       <c r="G123" s="15" t="s">
         <v>4</v>
@@ -7574,7 +7574,7 @@
     </row>
     <row r="124" spans="1:9" ht="28.3">
       <c r="A124" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B124" s="14">
         <v>11</v>
@@ -7583,13 +7583,13 @@
         <v>33</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E124" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="F124" s="15" t="s">
         <v>442</v>
-      </c>
-      <c r="F124" s="15" t="s">
-        <v>443</v>
       </c>
       <c r="G124" s="15" t="s">
         <v>4</v>
@@ -7601,7 +7601,7 @@
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B125" s="14">
         <v>11</v>
@@ -7613,10 +7613,10 @@
         <v>121</v>
       </c>
       <c r="E125" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="F125" s="15" t="s">
         <v>445</v>
-      </c>
-      <c r="F125" s="15" t="s">
-        <v>446</v>
       </c>
       <c r="G125" s="15" t="s">
         <v>4</v>
@@ -7628,7 +7628,7 @@
     </row>
     <row r="126" spans="1:9" ht="28.3">
       <c r="A126" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B126" s="14">
         <v>11</v>
@@ -7640,10 +7640,10 @@
         <v>81</v>
       </c>
       <c r="E126" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="F126" s="15" t="s">
         <v>448</v>
-      </c>
-      <c r="F126" s="15" t="s">
-        <v>449</v>
       </c>
       <c r="G126" s="15" t="s">
         <v>4</v>
@@ -7655,7 +7655,7 @@
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B127" s="14">
         <v>11</v>
@@ -7667,10 +7667,10 @@
         <v>128</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F127" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G127" s="15" t="s">
         <v>4</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B128" s="14">
         <v>11</v>
@@ -7694,10 +7694,10 @@
         <v>71</v>
       </c>
       <c r="E128" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="F128" s="15" t="s">
         <v>453</v>
-      </c>
-      <c r="F128" s="15" t="s">
-        <v>454</v>
       </c>
       <c r="G128" s="15" t="s">
         <v>4</v>
@@ -7709,7 +7709,7 @@
     </row>
     <row r="129" spans="1:9" ht="28.3">
       <c r="A129" s="13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B129" s="14">
         <v>12</v>
@@ -7718,13 +7718,13 @@
         <v>34</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E129" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="F129" s="15" t="s">
         <v>456</v>
-      </c>
-      <c r="F129" s="15" t="s">
-        <v>457</v>
       </c>
       <c r="G129" s="15" t="s">
         <v>4</v>
@@ -7736,7 +7736,7 @@
     </row>
     <row r="130" spans="1:9" ht="28.3">
       <c r="A130" s="13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B130" s="14">
         <v>12</v>
@@ -7745,13 +7745,13 @@
         <v>34</v>
       </c>
       <c r="D130" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="E130" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="E130" s="15" t="s">
+      <c r="F130" s="15" t="s">
         <v>460</v>
-      </c>
-      <c r="F130" s="15" t="s">
-        <v>461</v>
       </c>
       <c r="G130" s="15" t="s">
         <v>4</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B131" s="14">
         <v>12</v>
@@ -7772,13 +7772,13 @@
         <v>34</v>
       </c>
       <c r="D131" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="E131" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="E131" s="15" t="s">
+      <c r="F131" s="15" t="s">
         <v>464</v>
-      </c>
-      <c r="F131" s="15" t="s">
-        <v>465</v>
       </c>
       <c r="G131" s="15" t="s">
         <v>4</v>
@@ -7790,7 +7790,7 @@
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B132" s="14">
         <v>12</v>
@@ -7799,13 +7799,13 @@
         <v>34</v>
       </c>
       <c r="D132" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E132" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="F132" s="15" t="s">
         <v>467</v>
-      </c>
-      <c r="F132" s="15" t="s">
-        <v>468</v>
       </c>
       <c r="G132" s="15" t="s">
         <v>4</v>
@@ -7817,7 +7817,7 @@
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="13" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B133" s="14">
         <v>12</v>
@@ -7829,10 +7829,10 @@
         <v>135</v>
       </c>
       <c r="E133" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="F133" s="15" t="s">
         <v>470</v>
-      </c>
-      <c r="F133" s="15" t="s">
-        <v>471</v>
       </c>
       <c r="G133" s="15" t="s">
         <v>4</v>
@@ -7844,7 +7844,7 @@
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="13" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B134" s="14">
         <v>12</v>
@@ -7853,13 +7853,13 @@
         <v>34</v>
       </c>
       <c r="D134" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="E134" s="15" t="s">
         <v>473</v>
       </c>
-      <c r="E134" s="15" t="s">
+      <c r="F134" s="15" t="s">
         <v>474</v>
-      </c>
-      <c r="F134" s="15" t="s">
-        <v>475</v>
       </c>
       <c r="G134" s="15" t="s">
         <v>4</v>
@@ -7871,7 +7871,7 @@
     </row>
     <row r="135" spans="1:9" ht="28.3">
       <c r="A135" s="13" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B135" s="14">
         <v>12</v>
@@ -7880,13 +7880,13 @@
         <v>34</v>
       </c>
       <c r="D135" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="E135" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="E135" s="15" t="s">
+      <c r="F135" s="15" t="s">
         <v>478</v>
-      </c>
-      <c r="F135" s="15" t="s">
-        <v>479</v>
       </c>
       <c r="G135" s="15" t="s">
         <v>4</v>
@@ -7898,7 +7898,7 @@
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B136" s="14">
         <v>12</v>
@@ -7907,13 +7907,13 @@
         <v>34</v>
       </c>
       <c r="D136" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="E136" s="15" t="s">
         <v>481</v>
       </c>
-      <c r="E136" s="15" t="s">
+      <c r="F136" s="15" t="s">
         <v>482</v>
-      </c>
-      <c r="F136" s="15" t="s">
-        <v>483</v>
       </c>
       <c r="G136" s="15" t="s">
         <v>4</v>
@@ -7925,7 +7925,7 @@
     </row>
     <row r="137" spans="1:9" ht="28.3">
       <c r="A137" s="13" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B137" s="14">
         <v>12</v>
@@ -7934,13 +7934,13 @@
         <v>34</v>
       </c>
       <c r="D137" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="E137" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="E137" s="15" t="s">
+      <c r="F137" s="15" t="s">
         <v>486</v>
-      </c>
-      <c r="F137" s="15" t="s">
-        <v>487</v>
       </c>
       <c r="G137" s="15" t="s">
         <v>4</v>
@@ -7952,7 +7952,7 @@
     </row>
     <row r="138" spans="1:9" ht="28.3">
       <c r="A138" s="13" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B138" s="14">
         <v>12</v>
@@ -7964,10 +7964,10 @@
         <v>71</v>
       </c>
       <c r="E138" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="F138" s="15" t="s">
         <v>489</v>
-      </c>
-      <c r="F138" s="15" t="s">
-        <v>490</v>
       </c>
       <c r="G138" s="15" t="s">
         <v>4</v>
@@ -7979,7 +7979,7 @@
     </row>
     <row r="139" spans="1:9" ht="28.3">
       <c r="A139" s="13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B139" s="14">
         <v>13</v>
@@ -7988,13 +7988,13 @@
         <v>35</v>
       </c>
       <c r="D139" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="E139" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="E139" s="15" t="s">
+      <c r="F139" s="15" t="s">
         <v>493</v>
-      </c>
-      <c r="F139" s="15" t="s">
-        <v>494</v>
       </c>
       <c r="G139" s="15" t="s">
         <v>4</v>
@@ -8006,7 +8006,7 @@
     </row>
     <row r="140" spans="1:9" ht="28.3">
       <c r="A140" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B140" s="14">
         <v>13</v>
@@ -8015,13 +8015,13 @@
         <v>35</v>
       </c>
       <c r="D140" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E140" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="F140" s="15" t="s">
         <v>496</v>
-      </c>
-      <c r="F140" s="15" t="s">
-        <v>497</v>
       </c>
       <c r="G140" s="15" t="s">
         <v>4</v>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="141" spans="1:9" ht="28.3">
       <c r="A141" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B141" s="14">
         <v>13</v>
@@ -8042,13 +8042,13 @@
         <v>35</v>
       </c>
       <c r="D141" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E141" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="F141" s="15" t="s">
         <v>499</v>
-      </c>
-      <c r="F141" s="15" t="s">
-        <v>500</v>
       </c>
       <c r="G141" s="15" t="s">
         <v>4</v>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="142" spans="1:9" ht="28.3">
       <c r="A142" s="13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B142" s="14">
         <v>13</v>
@@ -8069,13 +8069,13 @@
         <v>35</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E142" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="F142" s="15" t="s">
         <v>502</v>
-      </c>
-      <c r="F142" s="15" t="s">
-        <v>503</v>
       </c>
       <c r="G142" s="15" t="s">
         <v>4</v>
@@ -8087,7 +8087,7 @@
     </row>
     <row r="143" spans="1:9">
       <c r="A143" s="13" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B143" s="14">
         <v>13</v>
@@ -8096,13 +8096,13 @@
         <v>35</v>
       </c>
       <c r="D143" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E143" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="F143" s="15" t="s">
         <v>505</v>
-      </c>
-      <c r="F143" s="15" t="s">
-        <v>506</v>
       </c>
       <c r="G143" s="15" t="s">
         <v>4</v>
@@ -8114,7 +8114,7 @@
     </row>
     <row r="144" spans="1:9" ht="28.3">
       <c r="A144" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B144" s="14">
         <v>13</v>
@@ -8123,13 +8123,13 @@
         <v>35</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E144" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="F144" s="15" t="s">
         <v>508</v>
-      </c>
-      <c r="F144" s="15" t="s">
-        <v>509</v>
       </c>
       <c r="G144" s="15" t="s">
         <v>4</v>
@@ -8141,7 +8141,7 @@
     </row>
     <row r="145" spans="1:9">
       <c r="A145" s="13" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B145" s="14">
         <v>13</v>
@@ -8153,10 +8153,10 @@
         <v>71</v>
       </c>
       <c r="E145" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="F145" s="15" t="s">
         <v>511</v>
-      </c>
-      <c r="F145" s="15" t="s">
-        <v>512</v>
       </c>
       <c r="G145" s="15" t="s">
         <v>4</v>
@@ -8168,7 +8168,7 @@
     </row>
     <row r="146" spans="1:9">
       <c r="A146" s="13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B146" s="14">
         <v>13</v>
@@ -8180,10 +8180,10 @@
         <v>117</v>
       </c>
       <c r="E146" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="F146" s="15" t="s">
         <v>514</v>
-      </c>
-      <c r="F146" s="15" t="s">
-        <v>515</v>
       </c>
       <c r="G146" s="15" t="s">
         <v>4</v>
@@ -8195,7 +8195,7 @@
     </row>
     <row r="147" spans="1:9" ht="28.3">
       <c r="A147" s="13" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B147" s="14">
         <v>13</v>
@@ -8207,10 +8207,10 @@
         <v>98</v>
       </c>
       <c r="E147" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="F147" s="15" t="s">
         <v>517</v>
-      </c>
-      <c r="F147" s="15" t="s">
-        <v>518</v>
       </c>
       <c r="G147" s="15" t="s">
         <v>4</v>
@@ -8222,7 +8222,7 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B148" s="14">
         <v>13</v>
@@ -8234,10 +8234,10 @@
         <v>71</v>
       </c>
       <c r="E148" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="F148" s="15" t="s">
         <v>520</v>
-      </c>
-      <c r="F148" s="15" t="s">
-        <v>521</v>
       </c>
       <c r="G148" s="15" t="s">
         <v>4</v>
@@ -8249,7 +8249,7 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B149" s="14">
         <v>14</v>
@@ -8258,13 +8258,13 @@
         <v>36</v>
       </c>
       <c r="D149" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="E149" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="E149" s="15" t="s">
+      <c r="F149" s="15" t="s">
         <v>524</v>
-      </c>
-      <c r="F149" s="15" t="s">
-        <v>525</v>
       </c>
       <c r="G149" s="15" t="s">
         <v>4</v>
@@ -8276,7 +8276,7 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="13" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B150" s="14">
         <v>14</v>
@@ -8285,13 +8285,13 @@
         <v>36</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E150" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="F150" s="15" t="s">
         <v>527</v>
-      </c>
-      <c r="F150" s="15" t="s">
-        <v>528</v>
       </c>
       <c r="G150" s="15" t="s">
         <v>4</v>
@@ -8303,7 +8303,7 @@
     </row>
     <row r="151" spans="1:9">
       <c r="A151" s="13" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B151" s="14">
         <v>14</v>
@@ -8312,13 +8312,13 @@
         <v>36</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E151" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="F151" s="15" t="s">
         <v>530</v>
-      </c>
-      <c r="F151" s="15" t="s">
-        <v>531</v>
       </c>
       <c r="G151" s="15" t="s">
         <v>4</v>
@@ -8330,7 +8330,7 @@
     </row>
     <row r="152" spans="1:9">
       <c r="A152" s="13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B152" s="14">
         <v>14</v>
@@ -8339,13 +8339,13 @@
         <v>36</v>
       </c>
       <c r="D152" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E152" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="F152" s="15" t="s">
         <v>533</v>
-      </c>
-      <c r="F152" s="15" t="s">
-        <v>534</v>
       </c>
       <c r="G152" s="15" t="s">
         <v>4</v>
@@ -8357,7 +8357,7 @@
     </row>
     <row r="153" spans="1:9">
       <c r="A153" s="13" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B153" s="14">
         <v>14</v>
@@ -8366,13 +8366,13 @@
         <v>36</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G153" s="15" t="s">
         <v>4</v>
@@ -8384,7 +8384,7 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="13" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B154" s="14">
         <v>14</v>
@@ -8393,13 +8393,13 @@
         <v>36</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E154" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="F154" s="15" t="s">
         <v>538</v>
-      </c>
-      <c r="F154" s="15" t="s">
-        <v>539</v>
       </c>
       <c r="G154" s="15" t="s">
         <v>4</v>
@@ -8411,7 +8411,7 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="13" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B155" s="14">
         <v>14</v>
@@ -8423,10 +8423,10 @@
         <v>128</v>
       </c>
       <c r="E155" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="F155" s="15" t="s">
         <v>541</v>
-      </c>
-      <c r="F155" s="15" t="s">
-        <v>542</v>
       </c>
       <c r="G155" s="15" t="s">
         <v>4</v>
@@ -8438,7 +8438,7 @@
     </row>
     <row r="156" spans="1:9">
       <c r="A156" s="13" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B156" s="14">
         <v>14</v>
@@ -8450,10 +8450,10 @@
         <v>71</v>
       </c>
       <c r="E156" s="15" t="s">
+        <v>543</v>
+      </c>
+      <c r="F156" s="15" t="s">
         <v>544</v>
-      </c>
-      <c r="F156" s="15" t="s">
-        <v>545</v>
       </c>
       <c r="G156" s="15" t="s">
         <v>4</v>
@@ -8465,7 +8465,7 @@
     </row>
     <row r="157" spans="1:9">
       <c r="A157" s="13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B157" s="14">
         <v>15</v>
@@ -8474,13 +8474,13 @@
         <v>37</v>
       </c>
       <c r="D157" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="E157" s="15" t="s">
         <v>547</v>
       </c>
-      <c r="E157" s="15" t="s">
+      <c r="F157" s="15" t="s">
         <v>548</v>
-      </c>
-      <c r="F157" s="15" t="s">
-        <v>549</v>
       </c>
       <c r="G157" s="15" t="s">
         <v>4</v>
@@ -8492,7 +8492,7 @@
     </row>
     <row r="158" spans="1:9">
       <c r="A158" s="13" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B158" s="14">
         <v>15</v>
@@ -8501,13 +8501,13 @@
         <v>37</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E158" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="F158" s="15" t="s">
         <v>551</v>
-      </c>
-      <c r="F158" s="15" t="s">
-        <v>552</v>
       </c>
       <c r="G158" s="15" t="s">
         <v>4</v>
@@ -8519,7 +8519,7 @@
     </row>
     <row r="159" spans="1:9" ht="28.3">
       <c r="A159" s="13" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B159" s="14">
         <v>15</v>
@@ -8528,13 +8528,13 @@
         <v>37</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E159" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="F159" s="15" t="s">
         <v>554</v>
-      </c>
-      <c r="F159" s="15" t="s">
-        <v>555</v>
       </c>
       <c r="G159" s="15" t="s">
         <v>4</v>
@@ -8546,7 +8546,7 @@
     </row>
     <row r="160" spans="1:9" ht="28.3">
       <c r="A160" s="13" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B160" s="14">
         <v>15</v>
@@ -8555,13 +8555,13 @@
         <v>37</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E160" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="F160" s="15" t="s">
         <v>557</v>
-      </c>
-      <c r="F160" s="15" t="s">
-        <v>558</v>
       </c>
       <c r="G160" s="15" t="s">
         <v>4</v>
@@ -8573,7 +8573,7 @@
     </row>
     <row r="161" spans="1:9">
       <c r="A161" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B161" s="14">
         <v>15</v>
@@ -8582,13 +8582,13 @@
         <v>37</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E161" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="F161" s="15" t="s">
         <v>560</v>
-      </c>
-      <c r="F161" s="15" t="s">
-        <v>561</v>
       </c>
       <c r="G161" s="15" t="s">
         <v>4</v>
@@ -8600,7 +8600,7 @@
     </row>
     <row r="162" spans="1:9">
       <c r="A162" s="13" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B162" s="14">
         <v>15</v>
@@ -8609,13 +8609,13 @@
         <v>37</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E162" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="F162" s="15" t="s">
         <v>563</v>
-      </c>
-      <c r="F162" s="15" t="s">
-        <v>564</v>
       </c>
       <c r="G162" s="15" t="s">
         <v>4</v>
@@ -8627,7 +8627,7 @@
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="13" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B163" s="14">
         <v>15</v>
@@ -8639,10 +8639,10 @@
         <v>117</v>
       </c>
       <c r="E163" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="F163" s="15" t="s">
         <v>566</v>
-      </c>
-      <c r="F163" s="15" t="s">
-        <v>567</v>
       </c>
       <c r="G163" s="15" t="s">
         <v>4</v>
@@ -8654,7 +8654,7 @@
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="13" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B164" s="14">
         <v>15</v>
@@ -8666,10 +8666,10 @@
         <v>81</v>
       </c>
       <c r="E164" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="F164" s="15" t="s">
         <v>569</v>
-      </c>
-      <c r="F164" s="15" t="s">
-        <v>570</v>
       </c>
       <c r="G164" s="15" t="s">
         <v>4</v>
@@ -8681,7 +8681,7 @@
     </row>
     <row r="165" spans="1:9">
       <c r="A165" s="13" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B165" s="14">
         <v>15</v>
@@ -8693,10 +8693,10 @@
         <v>71</v>
       </c>
       <c r="E165" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="F165" s="15" t="s">
         <v>572</v>
-      </c>
-      <c r="F165" s="15" t="s">
-        <v>573</v>
       </c>
       <c r="G165" s="15" t="s">
         <v>4</v>
@@ -8708,7 +8708,7 @@
     </row>
     <row r="166" spans="1:9">
       <c r="A166" s="13" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B166" s="14">
         <v>16</v>
@@ -8720,10 +8720,10 @@
         <v>38</v>
       </c>
       <c r="E166" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="F166" s="15" t="s">
         <v>575</v>
-      </c>
-      <c r="F166" s="15" t="s">
-        <v>576</v>
       </c>
       <c r="G166" s="15" t="s">
         <v>4</v>
@@ -8735,7 +8735,7 @@
     </row>
     <row r="167" spans="1:9">
       <c r="A167" s="13" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B167" s="14">
         <v>16</v>
@@ -8747,10 +8747,10 @@
         <v>38</v>
       </c>
       <c r="E167" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="F167" s="15" t="s">
         <v>578</v>
-      </c>
-      <c r="F167" s="15" t="s">
-        <v>579</v>
       </c>
       <c r="G167" s="15" t="s">
         <v>4</v>
@@ -8762,7 +8762,7 @@
     </row>
     <row r="168" spans="1:9">
       <c r="A168" s="13" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B168" s="14">
         <v>16</v>
@@ -8774,10 +8774,10 @@
         <v>38</v>
       </c>
       <c r="E168" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="F168" s="15" t="s">
         <v>581</v>
-      </c>
-      <c r="F168" s="15" t="s">
-        <v>582</v>
       </c>
       <c r="G168" s="15" t="s">
         <v>4</v>
@@ -8789,7 +8789,7 @@
     </row>
     <row r="169" spans="1:9" ht="28.3">
       <c r="A169" s="13" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B169" s="14">
         <v>16</v>
@@ -8801,10 +8801,10 @@
         <v>38</v>
       </c>
       <c r="E169" s="15" t="s">
+        <v>583</v>
+      </c>
+      <c r="F169" s="15" t="s">
         <v>584</v>
-      </c>
-      <c r="F169" s="15" t="s">
-        <v>585</v>
       </c>
       <c r="G169" s="15" t="s">
         <v>4</v>
@@ -8816,7 +8816,7 @@
     </row>
     <row r="170" spans="1:9" ht="28.3">
       <c r="A170" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B170" s="14">
         <v>16</v>
@@ -8828,10 +8828,10 @@
         <v>38</v>
       </c>
       <c r="E170" s="15" t="s">
+        <v>586</v>
+      </c>
+      <c r="F170" s="15" t="s">
         <v>587</v>
-      </c>
-      <c r="F170" s="15" t="s">
-        <v>588</v>
       </c>
       <c r="G170" s="15" t="s">
         <v>4</v>
@@ -8843,7 +8843,7 @@
     </row>
     <row r="171" spans="1:9">
       <c r="A171" s="13" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B171" s="14">
         <v>16</v>
@@ -8855,10 +8855,10 @@
         <v>38</v>
       </c>
       <c r="E171" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="F171" s="15" t="s">
         <v>590</v>
-      </c>
-      <c r="F171" s="15" t="s">
-        <v>591</v>
       </c>
       <c r="G171" s="15" t="s">
         <v>4</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="172" spans="1:9" ht="28.3">
       <c r="A172" s="13" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B172" s="14">
         <v>16</v>
@@ -8882,10 +8882,10 @@
         <v>38</v>
       </c>
       <c r="E172" s="15" t="s">
+        <v>592</v>
+      </c>
+      <c r="F172" s="15" t="s">
         <v>593</v>
-      </c>
-      <c r="F172" s="15" t="s">
-        <v>594</v>
       </c>
       <c r="G172" s="15" t="s">
         <v>4</v>
@@ -8897,7 +8897,7 @@
     </row>
     <row r="173" spans="1:9" ht="28.3">
       <c r="A173" s="13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B173" s="14">
         <v>16</v>
@@ -8909,10 +8909,10 @@
         <v>38</v>
       </c>
       <c r="E173" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="F173" s="15" t="s">
         <v>596</v>
-      </c>
-      <c r="F173" s="15" t="s">
-        <v>597</v>
       </c>
       <c r="G173" s="15" t="s">
         <v>4</v>
@@ -8924,7 +8924,7 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" s="13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B174" s="14">
         <v>16</v>
@@ -8936,10 +8936,10 @@
         <v>128</v>
       </c>
       <c r="E174" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="F174" s="15" t="s">
         <v>599</v>
-      </c>
-      <c r="F174" s="15" t="s">
-        <v>600</v>
       </c>
       <c r="G174" s="15" t="s">
         <v>4</v>
@@ -8951,7 +8951,7 @@
     </row>
     <row r="175" spans="1:9">
       <c r="A175" s="13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B175" s="14">
         <v>16</v>
@@ -8963,10 +8963,10 @@
         <v>71</v>
       </c>
       <c r="E175" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="F175" s="15" t="s">
         <v>602</v>
-      </c>
-      <c r="F175" s="15" t="s">
-        <v>603</v>
       </c>
       <c r="G175" s="15" t="s">
         <v>4</v>
@@ -8978,7 +8978,7 @@
     </row>
     <row r="176" spans="1:9">
       <c r="A176" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B176" s="14">
         <v>17</v>
@@ -8987,13 +8987,13 @@
         <v>39</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E176" s="15" t="s">
+        <v>604</v>
+      </c>
+      <c r="F176" s="15" t="s">
         <v>605</v>
-      </c>
-      <c r="F176" s="15" t="s">
-        <v>606</v>
       </c>
       <c r="G176" s="15" t="s">
         <v>4</v>
@@ -9005,7 +9005,7 @@
     </row>
     <row r="177" spans="1:9">
       <c r="A177" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B177" s="14">
         <v>17</v>
@@ -9017,10 +9017,10 @@
         <v>59</v>
       </c>
       <c r="E177" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="F177" s="15" t="s">
         <v>608</v>
-      </c>
-      <c r="F177" s="15" t="s">
-        <v>609</v>
       </c>
       <c r="G177" s="15" t="s">
         <v>4</v>
@@ -9032,7 +9032,7 @@
     </row>
     <row r="178" spans="1:9" ht="28.3">
       <c r="A178" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B178" s="14">
         <v>17</v>
@@ -9041,13 +9041,13 @@
         <v>39</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E178" s="15" t="s">
+        <v>610</v>
+      </c>
+      <c r="F178" s="15" t="s">
         <v>611</v>
-      </c>
-      <c r="F178" s="15" t="s">
-        <v>612</v>
       </c>
       <c r="G178" s="15" t="s">
         <v>4</v>
@@ -9059,7 +9059,7 @@
     </row>
     <row r="179" spans="1:9">
       <c r="A179" s="13" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B179" s="14">
         <v>17</v>
@@ -9068,13 +9068,13 @@
         <v>39</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E179" s="15" t="s">
+        <v>613</v>
+      </c>
+      <c r="F179" s="15" t="s">
         <v>614</v>
-      </c>
-      <c r="F179" s="15" t="s">
-        <v>615</v>
       </c>
       <c r="G179" s="15" t="s">
         <v>4</v>
@@ -9086,7 +9086,7 @@
     </row>
     <row r="180" spans="1:9">
       <c r="A180" s="13" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B180" s="14">
         <v>17</v>
@@ -9095,13 +9095,13 @@
         <v>39</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E180" s="15" t="s">
+        <v>616</v>
+      </c>
+      <c r="F180" s="15" t="s">
         <v>617</v>
-      </c>
-      <c r="F180" s="15" t="s">
-        <v>618</v>
       </c>
       <c r="G180" s="15" t="s">
         <v>4</v>
@@ -9113,7 +9113,7 @@
     </row>
     <row r="181" spans="1:9" ht="28.3">
       <c r="A181" s="13" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B181" s="14">
         <v>17</v>
@@ -9122,13 +9122,13 @@
         <v>39</v>
       </c>
       <c r="D181" s="15" t="s">
+        <v>619</v>
+      </c>
+      <c r="E181" s="15" t="s">
         <v>620</v>
       </c>
-      <c r="E181" s="15" t="s">
+      <c r="F181" s="15" t="s">
         <v>621</v>
-      </c>
-      <c r="F181" s="15" t="s">
-        <v>622</v>
       </c>
       <c r="G181" s="15" t="s">
         <v>4</v>
@@ -9140,7 +9140,7 @@
     </row>
     <row r="182" spans="1:9" ht="28.3">
       <c r="A182" s="13" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B182" s="14">
         <v>17</v>
@@ -9149,13 +9149,13 @@
         <v>39</v>
       </c>
       <c r="D182" s="15" t="s">
+        <v>623</v>
+      </c>
+      <c r="E182" s="15" t="s">
         <v>624</v>
       </c>
-      <c r="E182" s="15" t="s">
+      <c r="F182" s="15" t="s">
         <v>625</v>
-      </c>
-      <c r="F182" s="15" t="s">
-        <v>626</v>
       </c>
       <c r="G182" s="15" t="s">
         <v>4</v>
@@ -9167,7 +9167,7 @@
     </row>
     <row r="183" spans="1:9">
       <c r="A183" s="13" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B183" s="14">
         <v>17</v>
@@ -9176,13 +9176,13 @@
         <v>39</v>
       </c>
       <c r="D183" s="15" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E183" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="F183" s="15" t="s">
         <v>628</v>
-      </c>
-      <c r="F183" s="15" t="s">
-        <v>629</v>
       </c>
       <c r="G183" s="15" t="s">
         <v>4</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="184" spans="1:9" ht="28.3">
       <c r="A184" s="13" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B184" s="14">
         <v>17</v>
@@ -9203,13 +9203,13 @@
         <v>39</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E184" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="F184" s="15" t="s">
         <v>631</v>
-      </c>
-      <c r="F184" s="15" t="s">
-        <v>632</v>
       </c>
       <c r="G184" s="15" t="s">
         <v>4</v>
@@ -9221,7 +9221,7 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="13" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B185" s="14">
         <v>17</v>
@@ -9233,10 +9233,10 @@
         <v>71</v>
       </c>
       <c r="E185" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="F185" s="15" t="s">
         <v>634</v>
-      </c>
-      <c r="F185" s="15" t="s">
-        <v>635</v>
       </c>
       <c r="G185" s="15" t="s">
         <v>4</v>
@@ -9248,7 +9248,7 @@
     </row>
     <row r="186" spans="1:9" ht="28.3">
       <c r="A186" s="13" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B186" s="14">
         <v>18</v>
@@ -9260,10 +9260,10 @@
         <v>102</v>
       </c>
       <c r="E186" s="15" t="s">
+        <v>636</v>
+      </c>
+      <c r="F186" s="15" t="s">
         <v>637</v>
-      </c>
-      <c r="F186" s="15" t="s">
-        <v>638</v>
       </c>
       <c r="G186" s="15" t="s">
         <v>4</v>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="187" spans="1:9" ht="28.3">
       <c r="A187" s="13" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B187" s="14">
         <v>18</v>
@@ -9284,13 +9284,13 @@
         <v>40</v>
       </c>
       <c r="D187" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E187" s="15" t="s">
+        <v>639</v>
+      </c>
+      <c r="F187" s="15" t="s">
         <v>640</v>
-      </c>
-      <c r="F187" s="15" t="s">
-        <v>641</v>
       </c>
       <c r="G187" s="15" t="s">
         <v>4</v>
@@ -9302,7 +9302,7 @@
     </row>
     <row r="188" spans="1:9" ht="28.3">
       <c r="A188" s="13" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B188" s="14">
         <v>18</v>
@@ -9314,10 +9314,10 @@
         <v>135</v>
       </c>
       <c r="E188" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="F188" s="15" t="s">
         <v>643</v>
-      </c>
-      <c r="F188" s="15" t="s">
-        <v>644</v>
       </c>
       <c r="G188" s="15" t="s">
         <v>4</v>
@@ -9329,7 +9329,7 @@
     </row>
     <row r="189" spans="1:9">
       <c r="A189" s="13" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B189" s="14">
         <v>18</v>
@@ -9338,13 +9338,13 @@
         <v>40</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E189" s="15" t="s">
+        <v>645</v>
+      </c>
+      <c r="F189" s="15" t="s">
         <v>646</v>
-      </c>
-      <c r="F189" s="15" t="s">
-        <v>647</v>
       </c>
       <c r="G189" s="15" t="s">
         <v>4</v>
@@ -9356,7 +9356,7 @@
     </row>
     <row r="190" spans="1:9">
       <c r="A190" s="13" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B190" s="14">
         <v>18</v>
@@ -9368,10 +9368,10 @@
         <v>81</v>
       </c>
       <c r="E190" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="F190" s="15" t="s">
         <v>649</v>
-      </c>
-      <c r="F190" s="15" t="s">
-        <v>650</v>
       </c>
       <c r="G190" s="15" t="s">
         <v>4</v>
@@ -9383,7 +9383,7 @@
     </row>
     <row r="191" spans="1:9" ht="28.3">
       <c r="A191" s="13" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B191" s="14">
         <v>18</v>
@@ -9395,10 +9395,10 @@
         <v>117</v>
       </c>
       <c r="E191" s="15" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F191" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G191" s="15" t="s">
         <v>4</v>
@@ -9410,7 +9410,7 @@
     </row>
     <row r="192" spans="1:9" ht="28.3">
       <c r="A192" s="13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B192" s="14">
         <v>18</v>
@@ -9422,10 +9422,10 @@
         <v>121</v>
       </c>
       <c r="E192" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="F192" s="15" t="s">
         <v>654</v>
-      </c>
-      <c r="F192" s="15" t="s">
-        <v>655</v>
       </c>
       <c r="G192" s="15" t="s">
         <v>4</v>
@@ -9437,7 +9437,7 @@
     </row>
     <row r="193" spans="1:9" ht="28.3">
       <c r="A193" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B193" s="14">
         <v>18</v>
@@ -9449,10 +9449,10 @@
         <v>128</v>
       </c>
       <c r="E193" s="15" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F193" s="15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G193" s="15" t="s">
         <v>4</v>
@@ -9464,7 +9464,7 @@
     </row>
     <row r="194" spans="1:9">
       <c r="A194" s="13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B194" s="14">
         <v>18</v>
@@ -9476,10 +9476,10 @@
         <v>71</v>
       </c>
       <c r="E194" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="F194" s="15" t="s">
         <v>659</v>
-      </c>
-      <c r="F194" s="15" t="s">
-        <v>660</v>
       </c>
       <c r="G194" s="15" t="s">
         <v>4</v>
@@ -9491,7 +9491,7 @@
     </row>
     <row r="195" spans="1:9" ht="28.3">
       <c r="A195" s="13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B195" s="14">
         <v>19</v>
@@ -9500,13 +9500,13 @@
         <v>41</v>
       </c>
       <c r="D195" s="15" t="s">
+        <v>661</v>
+      </c>
+      <c r="E195" s="15" t="s">
         <v>662</v>
       </c>
-      <c r="E195" s="15" t="s">
+      <c r="F195" s="15" t="s">
         <v>663</v>
-      </c>
-      <c r="F195" s="15" t="s">
-        <v>664</v>
       </c>
       <c r="G195" s="15" t="s">
         <v>4</v>
@@ -9518,7 +9518,7 @@
     </row>
     <row r="196" spans="1:9" ht="28.3">
       <c r="A196" s="13" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B196" s="14">
         <v>19</v>
@@ -9527,13 +9527,13 @@
         <v>41</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E196" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="F196" s="15" t="s">
         <v>666</v>
-      </c>
-      <c r="F196" s="15" t="s">
-        <v>667</v>
       </c>
       <c r="G196" s="15" t="s">
         <v>4</v>
@@ -9545,7 +9545,7 @@
     </row>
     <row r="197" spans="1:9">
       <c r="A197" s="13" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B197" s="14">
         <v>19</v>
@@ -9554,13 +9554,13 @@
         <v>41</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E197" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="F197" s="15" t="s">
         <v>669</v>
-      </c>
-      <c r="F197" s="15" t="s">
-        <v>670</v>
       </c>
       <c r="G197" s="15" t="s">
         <v>4</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="198" spans="1:9" ht="28.3">
       <c r="A198" s="13" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B198" s="14">
         <v>19</v>
@@ -9581,13 +9581,13 @@
         <v>41</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E198" s="15" t="s">
+        <v>671</v>
+      </c>
+      <c r="F198" s="15" t="s">
         <v>672</v>
-      </c>
-      <c r="F198" s="15" t="s">
-        <v>673</v>
       </c>
       <c r="G198" s="15" t="s">
         <v>4</v>
@@ -9599,7 +9599,7 @@
     </row>
     <row r="199" spans="1:9">
       <c r="A199" s="13" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B199" s="14">
         <v>19</v>
@@ -9608,13 +9608,13 @@
         <v>41</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E199" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="F199" s="15" t="s">
         <v>675</v>
-      </c>
-      <c r="F199" s="15" t="s">
-        <v>676</v>
       </c>
       <c r="G199" s="15" t="s">
         <v>4</v>
@@ -9626,7 +9626,7 @@
     </row>
     <row r="200" spans="1:9" ht="28.3">
       <c r="A200" s="13" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B200" s="14">
         <v>19</v>
@@ -9635,13 +9635,13 @@
         <v>41</v>
       </c>
       <c r="D200" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="E200" s="15" t="s">
         <v>678</v>
       </c>
-      <c r="E200" s="15" t="s">
+      <c r="F200" s="15" t="s">
         <v>679</v>
-      </c>
-      <c r="F200" s="15" t="s">
-        <v>680</v>
       </c>
       <c r="G200" s="15" t="s">
         <v>4</v>
@@ -9653,7 +9653,7 @@
     </row>
     <row r="201" spans="1:9" ht="28.3">
       <c r="A201" s="13" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B201" s="14">
         <v>19</v>
@@ -9662,13 +9662,13 @@
         <v>41</v>
       </c>
       <c r="D201" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="E201" s="15" t="s">
         <v>682</v>
       </c>
-      <c r="E201" s="15" t="s">
+      <c r="F201" s="15" t="s">
         <v>683</v>
-      </c>
-      <c r="F201" s="15" t="s">
-        <v>684</v>
       </c>
       <c r="G201" s="15" t="s">
         <v>4</v>
@@ -9680,7 +9680,7 @@
     </row>
     <row r="202" spans="1:9">
       <c r="A202" s="13" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B202" s="14">
         <v>19</v>
@@ -9689,13 +9689,13 @@
         <v>41</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E202" s="15" t="s">
+        <v>685</v>
+      </c>
+      <c r="F202" s="15" t="s">
         <v>686</v>
-      </c>
-      <c r="F202" s="15" t="s">
-        <v>687</v>
       </c>
       <c r="G202" s="15" t="s">
         <v>4</v>
@@ -9707,7 +9707,7 @@
     </row>
     <row r="203" spans="1:9" ht="28.3">
       <c r="A203" s="13" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B203" s="14">
         <v>19</v>
@@ -9716,13 +9716,13 @@
         <v>41</v>
       </c>
       <c r="D203" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="E203" s="15" t="s">
         <v>689</v>
       </c>
-      <c r="E203" s="15" t="s">
+      <c r="F203" s="15" t="s">
         <v>690</v>
-      </c>
-      <c r="F203" s="15" t="s">
-        <v>691</v>
       </c>
       <c r="G203" s="15" t="s">
         <v>4</v>
@@ -9734,7 +9734,7 @@
     </row>
     <row r="204" spans="1:9" ht="28.3">
       <c r="A204" s="13" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B204" s="14">
         <v>19</v>
@@ -9743,13 +9743,13 @@
         <v>41</v>
       </c>
       <c r="D204" s="15" t="s">
+        <v>692</v>
+      </c>
+      <c r="E204" s="15" t="s">
         <v>693</v>
       </c>
-      <c r="E204" s="15" t="s">
+      <c r="F204" s="15" t="s">
         <v>694</v>
-      </c>
-      <c r="F204" s="15" t="s">
-        <v>695</v>
       </c>
       <c r="G204" s="15" t="s">
         <v>4</v>
@@ -9761,7 +9761,7 @@
     </row>
     <row r="205" spans="1:9" ht="28.3">
       <c r="A205" s="13" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B205" s="14">
         <v>19</v>
@@ -9773,10 +9773,10 @@
         <v>71</v>
       </c>
       <c r="E205" s="15" t="s">
+        <v>696</v>
+      </c>
+      <c r="F205" s="15" t="s">
         <v>697</v>
-      </c>
-      <c r="F205" s="15" t="s">
-        <v>698</v>
       </c>
       <c r="G205" s="15" t="s">
         <v>4</v>
@@ -9788,7 +9788,7 @@
     </row>
     <row r="206" spans="1:9" ht="28.3">
       <c r="A206" s="13" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B206" s="14">
         <v>20</v>
@@ -9797,13 +9797,13 @@
         <v>42</v>
       </c>
       <c r="D206" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="E206" s="15" t="s">
         <v>700</v>
       </c>
-      <c r="E206" s="15" t="s">
+      <c r="F206" s="15" t="s">
         <v>701</v>
-      </c>
-      <c r="F206" s="15" t="s">
-        <v>702</v>
       </c>
       <c r="G206" s="15" t="s">
         <v>4</v>
@@ -9815,7 +9815,7 @@
     </row>
     <row r="207" spans="1:9" ht="28.3">
       <c r="A207" s="13" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B207" s="14">
         <v>20</v>
@@ -9824,13 +9824,13 @@
         <v>42</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E207" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="F207" s="15" t="s">
         <v>704</v>
-      </c>
-      <c r="F207" s="15" t="s">
-        <v>705</v>
       </c>
       <c r="G207" s="15" t="s">
         <v>4</v>
@@ -9842,7 +9842,7 @@
     </row>
     <row r="208" spans="1:9" ht="28.3">
       <c r="A208" s="13" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B208" s="14">
         <v>20</v>
@@ -9851,13 +9851,13 @@
         <v>42</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E208" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="F208" s="15" t="s">
         <v>707</v>
-      </c>
-      <c r="F208" s="15" t="s">
-        <v>708</v>
       </c>
       <c r="G208" s="15" t="s">
         <v>4</v>
@@ -9869,7 +9869,7 @@
     </row>
     <row r="209" spans="1:9" ht="28.3">
       <c r="A209" s="13" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B209" s="14">
         <v>20</v>
@@ -9878,13 +9878,13 @@
         <v>42</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E209" s="15" t="s">
+        <v>709</v>
+      </c>
+      <c r="F209" s="15" t="s">
         <v>710</v>
-      </c>
-      <c r="F209" s="15" t="s">
-        <v>711</v>
       </c>
       <c r="G209" s="15" t="s">
         <v>4</v>
@@ -9896,7 +9896,7 @@
     </row>
     <row r="210" spans="1:9" ht="28.3">
       <c r="A210" s="13" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B210" s="14">
         <v>20</v>
@@ -9905,13 +9905,13 @@
         <v>42</v>
       </c>
       <c r="D210" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E210" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="F210" s="15" t="s">
         <v>713</v>
-      </c>
-      <c r="F210" s="15" t="s">
-        <v>714</v>
       </c>
       <c r="G210" s="15" t="s">
         <v>4</v>
@@ -9923,7 +9923,7 @@
     </row>
     <row r="211" spans="1:9" ht="28.3">
       <c r="A211" s="13" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B211" s="14">
         <v>20</v>
@@ -9932,13 +9932,13 @@
         <v>42</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E211" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="F211" s="15" t="s">
         <v>716</v>
-      </c>
-      <c r="F211" s="15" t="s">
-        <v>717</v>
       </c>
       <c r="G211" s="15" t="s">
         <v>4</v>
@@ -9950,7 +9950,7 @@
     </row>
     <row r="212" spans="1:9" ht="28.3">
       <c r="A212" s="13" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B212" s="14">
         <v>20</v>
@@ -9959,13 +9959,13 @@
         <v>42</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E212" s="15" t="s">
+        <v>718</v>
+      </c>
+      <c r="F212" s="15" t="s">
         <v>719</v>
-      </c>
-      <c r="F212" s="15" t="s">
-        <v>720</v>
       </c>
       <c r="G212" s="15" t="s">
         <v>4</v>
@@ -9977,7 +9977,7 @@
     </row>
     <row r="213" spans="1:9" ht="28.3">
       <c r="A213" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B213" s="14">
         <v>20</v>
@@ -9986,13 +9986,13 @@
         <v>42</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E213" s="15" t="s">
+        <v>721</v>
+      </c>
+      <c r="F213" s="15" t="s">
         <v>722</v>
-      </c>
-      <c r="F213" s="15" t="s">
-        <v>723</v>
       </c>
       <c r="G213" s="15" t="s">
         <v>4</v>
@@ -10004,7 +10004,7 @@
     </row>
     <row r="214" spans="1:9" ht="28.3">
       <c r="A214" s="13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B214" s="14">
         <v>20</v>
@@ -10013,13 +10013,13 @@
         <v>42</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E214" s="15" t="s">
+        <v>724</v>
+      </c>
+      <c r="F214" s="15" t="s">
         <v>725</v>
-      </c>
-      <c r="F214" s="15" t="s">
-        <v>726</v>
       </c>
       <c r="G214" s="15" t="s">
         <v>4</v>
@@ -10031,7 +10031,7 @@
     </row>
     <row r="215" spans="1:9" ht="28.3">
       <c r="A215" s="13" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B215" s="14">
         <v>20</v>
@@ -10040,13 +10040,13 @@
         <v>42</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E215" s="15" t="s">
+        <v>727</v>
+      </c>
+      <c r="F215" s="15" t="s">
         <v>728</v>
-      </c>
-      <c r="F215" s="15" t="s">
-        <v>729</v>
       </c>
       <c r="G215" s="15" t="s">
         <v>4</v>
@@ -10058,7 +10058,7 @@
     </row>
     <row r="216" spans="1:9" ht="28.3">
       <c r="A216" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B216" s="14">
         <v>20</v>
@@ -10067,13 +10067,13 @@
         <v>42</v>
       </c>
       <c r="D216" s="15" t="s">
+        <v>730</v>
+      </c>
+      <c r="E216" s="15" t="s">
         <v>731</v>
       </c>
-      <c r="E216" s="15" t="s">
+      <c r="F216" s="15" t="s">
         <v>732</v>
-      </c>
-      <c r="F216" s="15" t="s">
-        <v>733</v>
       </c>
       <c r="G216" s="15" t="s">
         <v>4</v>
@@ -10085,7 +10085,7 @@
     </row>
     <row r="217" spans="1:9" ht="28.3">
       <c r="A217" s="13" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B217" s="14">
         <v>20</v>
@@ -10094,13 +10094,13 @@
         <v>42</v>
       </c>
       <c r="D217" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="E217" s="15" t="s">
         <v>735</v>
       </c>
-      <c r="E217" s="15" t="s">
+      <c r="F217" s="15" t="s">
         <v>736</v>
-      </c>
-      <c r="F217" s="15" t="s">
-        <v>737</v>
       </c>
       <c r="G217" s="15" t="s">
         <v>4</v>
@@ -10112,7 +10112,7 @@
     </row>
     <row r="218" spans="1:9" ht="28.3">
       <c r="A218" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B218" s="14">
         <v>20</v>
@@ -10121,13 +10121,13 @@
         <v>42</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E218" s="15" t="s">
+        <v>738</v>
+      </c>
+      <c r="F218" s="15" t="s">
         <v>739</v>
-      </c>
-      <c r="F218" s="15" t="s">
-        <v>740</v>
       </c>
       <c r="G218" s="15" t="s">
         <v>4</v>
@@ -10139,7 +10139,7 @@
     </row>
     <row r="219" spans="1:9" ht="28.3">
       <c r="A219" s="13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B219" s="14">
         <v>20</v>
@@ -10148,13 +10148,13 @@
         <v>42</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E219" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="F219" s="15" t="s">
         <v>742</v>
-      </c>
-      <c r="F219" s="15" t="s">
-        <v>743</v>
       </c>
       <c r="G219" s="15" t="s">
         <v>4</v>
@@ -10166,7 +10166,7 @@
     </row>
     <row r="220" spans="1:9" ht="14.6" thickBot="1">
       <c r="A220" s="17" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B220" s="18">
         <v>20</v>
@@ -10175,13 +10175,13 @@
         <v>42</v>
       </c>
       <c r="D220" s="19" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E220" s="19" t="s">
+        <v>744</v>
+      </c>
+      <c r="F220" s="19" t="s">
         <v>745</v>
-      </c>
-      <c r="F220" s="19" t="s">
-        <v>746</v>
       </c>
       <c r="G220" s="19" t="s">
         <v>4</v>
@@ -10239,7 +10239,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="21" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -10257,7 +10257,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="22" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -10273,16 +10273,16 @@
         <v>15</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>749</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>750</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27.45" customHeight="1">
@@ -10293,16 +10293,16 @@
         <v>19</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>752</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>753</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="27.45" customHeight="1">
@@ -10313,16 +10313,16 @@
         <v>21</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>755</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>756</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="27.45" customHeight="1">
@@ -10333,16 +10333,16 @@
         <v>22</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>758</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>759</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27.45" customHeight="1">
@@ -10353,16 +10353,16 @@
         <v>24</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>761</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>762</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="27.45" customHeight="1">
@@ -10373,16 +10373,16 @@
         <v>25</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>764</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>765</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="27.45" customHeight="1">
@@ -10393,16 +10393,16 @@
         <v>26</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>767</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>768</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="27.45" customHeight="1">
@@ -10413,16 +10413,16 @@
         <v>27</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>770</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>771</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="27.45" customHeight="1">
@@ -10433,16 +10433,16 @@
         <v>28</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>773</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>774</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="27.45" customHeight="1">
@@ -10453,16 +10453,16 @@
         <v>29</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>776</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>777</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="27.45" customHeight="1">
@@ -10473,16 +10473,16 @@
         <v>30</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>779</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>780</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="27.45" customHeight="1">
@@ -10493,16 +10493,16 @@
         <v>31</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>782</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>783</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="27.45" customHeight="1">
@@ -10513,16 +10513,16 @@
         <v>33</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>785</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>786</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="27.45" customHeight="1">
@@ -10533,16 +10533,16 @@
         <v>34</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>788</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>789</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="27.45" customHeight="1">
@@ -10553,16 +10553,16 @@
         <v>35</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>791</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>792</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="27.45" customHeight="1">
@@ -10573,16 +10573,16 @@
         <v>36</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>793</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>794</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>795</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="27.45" customHeight="1">
@@ -10593,16 +10593,16 @@
         <v>37</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>797</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>798</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="27.45" customHeight="1">
@@ -10613,16 +10613,16 @@
         <v>38</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>800</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>801</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="27.45" customHeight="1">
@@ -10633,16 +10633,16 @@
         <v>39</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>803</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>804</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="27.45" customHeight="1">
@@ -10653,16 +10653,16 @@
         <v>40</v>
       </c>
       <c r="C24" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>806</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>807</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="27.45" customHeight="1">
@@ -10673,16 +10673,16 @@
         <v>41</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>809</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>810</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="27.45" customHeight="1">
@@ -10693,16 +10693,16 @@
         <v>42</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>812</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>813</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>32</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -10729,68 +10729,68 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>816</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B2" t="s">
         <v>818</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>819</v>
-      </c>
-      <c r="C2" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B3" t="s">
         <v>821</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>822</v>
-      </c>
-      <c r="C3" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>823</v>
+      </c>
+      <c r="B4" t="s">
         <v>824</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>825</v>
-      </c>
-      <c r="C4" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B5" t="s">
+        <v>826</v>
+      </c>
+      <c r="C5" t="s">
         <v>827</v>
-      </c>
-      <c r="C5" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B6" t="s">
+        <v>828</v>
+      </c>
+      <c r="C6" t="s">
         <v>829</v>
-      </c>
-      <c r="C6" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -10798,85 +10798,85 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
+        <v>830</v>
+      </c>
+      <c r="C7" t="s">
         <v>831</v>
-      </c>
-      <c r="C7" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C8" t="s">
         <v>833</v>
-      </c>
-      <c r="C8" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>835</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
+        <v>836</v>
+      </c>
+      <c r="B12" t="s">
         <v>837</v>
-      </c>
-      <c r="B12" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>838</v>
+      </c>
+      <c r="B13" t="s">
         <v>839</v>
-      </c>
-      <c r="B13" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>840</v>
+      </c>
+      <c r="B14" t="s">
         <v>841</v>
-      </c>
-      <c r="B14" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>842</v>
+      </c>
+      <c r="B15" t="s">
         <v>843</v>
-      </c>
-      <c r="B15" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>844</v>
+      </c>
+      <c r="B16" t="s">
         <v>845</v>
-      </c>
-      <c r="B16" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>846</v>
+      </c>
+      <c r="B17" t="s">
         <v>847</v>
-      </c>
-      <c r="B17" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
+        <v>848</v>
+      </c>
+      <c r="B18" t="s">
         <v>849</v>
-      </c>
-      <c r="B18" t="s">
-        <v>850</v>
       </c>
     </row>
   </sheetData>

--- a/NetLabz_Project_Checklist.xlsx
+++ b/NetLabz_Project_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NetLabz_Enterprise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BD4489-8C13-4EF9-B492-48F44840843F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36C65DA-6DEF-4765-8000-3E18F316CE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B4" s="4">
         <f>IF(B5=0,0,B6/B5)</f>
-        <v>0.11574074074074074</v>
+        <v>0.12962962962962962</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B6" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B9" s="5">
         <f>COUNTIF('Project Checklist'!$G$5:$G$220,"Not Started")</f>
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>12</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="E15">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A15,'Project Checklist'!$G$5:$G$220,"Complete")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F15">
         <f>COUNTIFS('Project Checklist'!$B$5:$B$220,A15,'Project Checklist'!$G$5:$G$220,"In Progress")</f>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="H15" s="3">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="I27" s="16"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" hidden="1">
       <c r="A28" s="13" t="s">
         <v>134</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="28.3">
+    <row r="29" spans="1:9" ht="28.3" hidden="1">
       <c r="A29" s="13" t="s">
         <v>138</v>
       </c>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="I29" s="16"/>
     </row>
-    <row r="30" spans="1:9" ht="28.3">
+    <row r="30" spans="1:9" ht="28.3" hidden="1">
       <c r="A30" s="13" t="s">
         <v>141</v>
       </c>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="I30" s="16"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" hidden="1">
       <c r="A31" s="13" t="s">
         <v>144</v>
       </c>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="I31" s="16"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" hidden="1">
       <c r="A32" s="13" t="s">
         <v>147</v>
       </c>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="I32" s="16"/>
     </row>
-    <row r="33" spans="1:9" ht="28.3">
+    <row r="33" spans="1:9" ht="28.3" hidden="1">
       <c r="A33" s="13" t="s">
         <v>151</v>
       </c>
@@ -5135,14 +5135,14 @@
         <v>154</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H33" s="15" t="s">
         <v>54</v>
       </c>
       <c r="I33" s="16"/>
     </row>
-    <row r="34" spans="1:9" ht="28.3">
+    <row r="34" spans="1:9" ht="28.3" hidden="1">
       <c r="A34" s="13" t="s">
         <v>155</v>
       </c>
@@ -5162,14 +5162,14 @@
         <v>157</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>54</v>
       </c>
       <c r="I34" s="16"/>
     </row>
-    <row r="35" spans="1:9" ht="28.3">
+    <row r="35" spans="1:9" ht="28.3" hidden="1">
       <c r="A35" s="13" t="s">
         <v>158</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>160</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H35" s="15" t="s">
         <v>54</v>
